--- a/ضبط_رواتب_الموظفين.xlsx
+++ b/ضبط_رواتب_الموظفين.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CB11E48-F832-4424-87CF-1D5291CCEFA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="الملخص السنوي" sheetId="1" r:id="rId1"/>
@@ -897,13 +897,37 @@
     <xf numFmtId="1" fontId="11" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="32" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -925,30 +949,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1227,46 +1227,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="58" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58"/>
-      <c r="G1" s="58"/>
-      <c r="H1" s="58"/>
-      <c r="I1" s="58"/>
-      <c r="J1" s="58"/>
-      <c r="K1" s="58"/>
-      <c r="L1" s="58"/>
-      <c r="M1" s="58"/>
-      <c r="N1" s="58"/>
-      <c r="O1" s="58"/>
-      <c r="P1" s="58"/>
-      <c r="Q1" s="58"/>
+      <c r="A1" s="54" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="54"/>
+      <c r="K1" s="54"/>
+      <c r="L1" s="54"/>
+      <c r="M1" s="54"/>
+      <c r="N1" s="54"/>
+      <c r="O1" s="54"/>
+      <c r="P1" s="54"/>
+      <c r="Q1" s="54"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="59" t="s">
+      <c r="A2" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="59"/>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="59"/>
-      <c r="H2" s="59"/>
-      <c r="I2" s="59"/>
-      <c r="J2" s="59"/>
-      <c r="K2" s="59"/>
-      <c r="L2" s="59"/>
-      <c r="M2" s="59"/>
-      <c r="N2" s="59"/>
-      <c r="O2" s="59"/>
-      <c r="P2" s="59"/>
-      <c r="Q2" s="59"/>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="55"/>
+      <c r="N2" s="55"/>
+      <c r="O2" s="55"/>
+      <c r="P2" s="55"/>
+      <c r="Q2" s="55"/>
     </row>
     <row r="3" spans="1:17" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:17" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2013,10 +2013,10 @@
       </c>
     </row>
     <row r="15" spans="1:17" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="60" t="s">
+      <c r="A15" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="60"/>
+      <c r="B15" s="56"/>
       <c r="C15" s="11">
         <f t="shared" ref="C15:Q15" si="1">IFERROR(SUM(C5:C14),0)</f>
         <v>15300000</v>
@@ -2103,92 +2103,92 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="49" t="s">
         <v>86</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
-      <c r="L1" s="50"/>
-      <c r="M1" s="50"/>
-      <c r="N1" s="50"/>
-      <c r="O1" s="50"/>
-      <c r="P1" s="50"/>
-      <c r="Q1" s="50"/>
-      <c r="R1" s="50"/>
-      <c r="S1" s="50"/>
-      <c r="T1" s="50"/>
-      <c r="U1" s="50"/>
-      <c r="V1" s="50"/>
-      <c r="W1" s="50"/>
-      <c r="X1" s="50"/>
-      <c r="Y1" s="50"/>
-      <c r="Z1" s="50"/>
-      <c r="AA1" s="50"/>
-      <c r="AB1" s="50"/>
-      <c r="AC1" s="50"/>
-      <c r="AD1" s="50"/>
-      <c r="AE1" s="50"/>
-      <c r="AF1" s="50"/>
-      <c r="AG1" s="50"/>
-      <c r="AH1" s="50"/>
-      <c r="AI1" s="50"/>
-      <c r="AJ1" s="50"/>
-      <c r="AK1" s="50"/>
-      <c r="AL1" s="50"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
+      <c r="M1" s="49"/>
+      <c r="N1" s="49"/>
+      <c r="O1" s="49"/>
+      <c r="P1" s="49"/>
+      <c r="Q1" s="49"/>
+      <c r="R1" s="49"/>
+      <c r="S1" s="49"/>
+      <c r="T1" s="49"/>
+      <c r="U1" s="49"/>
+      <c r="V1" s="49"/>
+      <c r="W1" s="49"/>
+      <c r="X1" s="49"/>
+      <c r="Y1" s="49"/>
+      <c r="Z1" s="49"/>
+      <c r="AA1" s="49"/>
+      <c r="AB1" s="49"/>
+      <c r="AC1" s="49"/>
+      <c r="AD1" s="49"/>
+      <c r="AE1" s="49"/>
+      <c r="AF1" s="49"/>
+      <c r="AG1" s="49"/>
+      <c r="AH1" s="49"/>
+      <c r="AI1" s="49"/>
+      <c r="AJ1" s="49"/>
+      <c r="AK1" s="49"/>
+      <c r="AL1" s="49"/>
     </row>
     <row r="2" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="59" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="51"/>
-      <c r="J2" s="51"/>
-      <c r="K2" s="51"/>
-      <c r="L2" s="51"/>
-      <c r="M2" s="51"/>
-      <c r="N2" s="51"/>
-      <c r="O2" s="51"/>
-      <c r="P2" s="51"/>
-      <c r="Q2" s="51"/>
-      <c r="R2" s="51"/>
-      <c r="S2" s="51"/>
-      <c r="T2" s="51"/>
-      <c r="U2" s="51"/>
-      <c r="V2" s="51"/>
-      <c r="W2" s="51"/>
-      <c r="X2" s="51"/>
-      <c r="Y2" s="51"/>
-      <c r="Z2" s="51"/>
-      <c r="AA2" s="51"/>
-      <c r="AB2" s="51"/>
-      <c r="AC2" s="51"/>
-      <c r="AD2" s="51"/>
-      <c r="AE2" s="51"/>
-      <c r="AF2" s="51"/>
-      <c r="AG2" s="51"/>
-      <c r="AH2" s="51"/>
-      <c r="AI2" s="51"/>
-      <c r="AJ2" s="51"/>
-      <c r="AK2" s="51"/>
-      <c r="AL2" s="51"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="59"/>
+      <c r="L2" s="59"/>
+      <c r="M2" s="59"/>
+      <c r="N2" s="59"/>
+      <c r="O2" s="59"/>
+      <c r="P2" s="59"/>
+      <c r="Q2" s="59"/>
+      <c r="R2" s="59"/>
+      <c r="S2" s="59"/>
+      <c r="T2" s="59"/>
+      <c r="U2" s="59"/>
+      <c r="V2" s="59"/>
+      <c r="W2" s="59"/>
+      <c r="X2" s="59"/>
+      <c r="Y2" s="59"/>
+      <c r="Z2" s="59"/>
+      <c r="AA2" s="59"/>
+      <c r="AB2" s="59"/>
+      <c r="AC2" s="59"/>
+      <c r="AD2" s="59"/>
+      <c r="AE2" s="59"/>
+      <c r="AF2" s="59"/>
+      <c r="AG2" s="59"/>
+      <c r="AH2" s="59"/>
+      <c r="AI2" s="59"/>
+      <c r="AJ2" s="59"/>
+      <c r="AK2" s="59"/>
+      <c r="AL2" s="59"/>
     </row>
     <row r="3" spans="1:38" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="60" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="29" t="s">
@@ -2284,27 +2284,27 @@
       <c r="AF4" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="AG4" s="53" t="s">
+      <c r="AG4" s="61" t="s">
         <v>54</v>
       </c>
-      <c r="AH4" s="54" t="s">
+      <c r="AH4" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="AI4" s="55" t="s">
+      <c r="AI4" s="63" t="s">
         <v>56</v>
       </c>
-      <c r="AJ4" s="56" t="s">
+      <c r="AJ4" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="AK4" s="57" t="s">
+      <c r="AK4" s="65" t="s">
         <v>58</v>
       </c>
-      <c r="AL4" s="56" t="s">
+      <c r="AL4" s="64" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:38" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="52"/>
+      <c r="A5" s="60"/>
       <c r="B5" s="31">
         <v>1</v>
       </c>
@@ -2398,12 +2398,12 @@
       <c r="AF5" s="31">
         <v>31</v>
       </c>
-      <c r="AG5" s="53"/>
-      <c r="AH5" s="53"/>
-      <c r="AI5" s="53"/>
-      <c r="AJ5" s="53"/>
-      <c r="AK5" s="53"/>
-      <c r="AL5" s="53"/>
+      <c r="AG5" s="61"/>
+      <c r="AH5" s="61"/>
+      <c r="AI5" s="61"/>
+      <c r="AJ5" s="61"/>
+      <c r="AK5" s="61"/>
+      <c r="AL5" s="61"/>
     </row>
     <row r="6" spans="1:38" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="1:38" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3168,46 +3168,46 @@
     </row>
     <row r="18" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="1:38" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="48" t="s">
+      <c r="A19" s="57" t="s">
         <v>88</v>
       </c>
-      <c r="B19" s="48"/>
-      <c r="C19" s="48"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="48"/>
-      <c r="F19" s="48"/>
-      <c r="G19" s="48"/>
-      <c r="H19" s="48"/>
-      <c r="I19" s="48"/>
-      <c r="J19" s="48"/>
-      <c r="K19" s="48"/>
-      <c r="L19" s="48"/>
-      <c r="M19" s="48"/>
-      <c r="N19" s="48"/>
-      <c r="O19" s="48"/>
-      <c r="P19" s="48"/>
-      <c r="Q19" s="48"/>
-      <c r="R19" s="48"/>
-      <c r="S19" s="48"/>
-      <c r="T19" s="48"/>
-      <c r="U19" s="48"/>
-      <c r="V19" s="48"/>
-      <c r="W19" s="48"/>
-      <c r="X19" s="48"/>
-      <c r="Y19" s="48"/>
-      <c r="Z19" s="48"/>
-      <c r="AA19" s="48"/>
-      <c r="AB19" s="48"/>
-      <c r="AC19" s="48"/>
-      <c r="AD19" s="48"/>
-      <c r="AE19" s="48"/>
-      <c r="AF19" s="48"/>
-      <c r="AG19" s="48"/>
-      <c r="AH19" s="48"/>
-      <c r="AI19" s="48"/>
-      <c r="AJ19" s="48"/>
-      <c r="AK19" s="48"/>
-      <c r="AL19" s="48"/>
+      <c r="B19" s="57"/>
+      <c r="C19" s="57"/>
+      <c r="D19" s="57"/>
+      <c r="E19" s="57"/>
+      <c r="F19" s="57"/>
+      <c r="G19" s="57"/>
+      <c r="H19" s="57"/>
+      <c r="I19" s="57"/>
+      <c r="J19" s="57"/>
+      <c r="K19" s="57"/>
+      <c r="L19" s="57"/>
+      <c r="M19" s="57"/>
+      <c r="N19" s="57"/>
+      <c r="O19" s="57"/>
+      <c r="P19" s="57"/>
+      <c r="Q19" s="57"/>
+      <c r="R19" s="57"/>
+      <c r="S19" s="57"/>
+      <c r="T19" s="57"/>
+      <c r="U19" s="57"/>
+      <c r="V19" s="57"/>
+      <c r="W19" s="57"/>
+      <c r="X19" s="57"/>
+      <c r="Y19" s="57"/>
+      <c r="Z19" s="57"/>
+      <c r="AA19" s="57"/>
+      <c r="AB19" s="57"/>
+      <c r="AC19" s="57"/>
+      <c r="AD19" s="57"/>
+      <c r="AE19" s="57"/>
+      <c r="AF19" s="57"/>
+      <c r="AG19" s="57"/>
+      <c r="AH19" s="57"/>
+      <c r="AI19" s="57"/>
+      <c r="AJ19" s="57"/>
+      <c r="AK19" s="57"/>
+      <c r="AL19" s="57"/>
     </row>
     <row r="20" spans="1:38" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
@@ -3566,10 +3566,10 @@
       </c>
     </row>
     <row r="31" spans="1:38" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="49" t="s">
+      <c r="A31" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="B31" s="49"/>
+      <c r="B31" s="58"/>
       <c r="C31" s="11">
         <f t="shared" ref="C31:H31" si="8">SUM(C21:C30)</f>
         <v>15300000</v>
@@ -3628,90 +3628,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="49" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
-      <c r="L1" s="50"/>
-      <c r="M1" s="50"/>
-      <c r="N1" s="50"/>
-      <c r="O1" s="50"/>
-      <c r="P1" s="50"/>
-      <c r="Q1" s="50"/>
-      <c r="R1" s="50"/>
-      <c r="S1" s="50"/>
-      <c r="T1" s="50"/>
-      <c r="U1" s="50"/>
-      <c r="V1" s="50"/>
-      <c r="W1" s="50"/>
-      <c r="X1" s="50"/>
-      <c r="Y1" s="50"/>
-      <c r="Z1" s="50"/>
-      <c r="AA1" s="50"/>
-      <c r="AB1" s="50"/>
-      <c r="AC1" s="50"/>
-      <c r="AD1" s="50"/>
-      <c r="AE1" s="50"/>
-      <c r="AF1" s="50"/>
-      <c r="AG1" s="50"/>
-      <c r="AH1" s="50"/>
-      <c r="AI1" s="50"/>
-      <c r="AJ1" s="50"/>
-      <c r="AK1" s="50"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
+      <c r="M1" s="49"/>
+      <c r="N1" s="49"/>
+      <c r="O1" s="49"/>
+      <c r="P1" s="49"/>
+      <c r="Q1" s="49"/>
+      <c r="R1" s="49"/>
+      <c r="S1" s="49"/>
+      <c r="T1" s="49"/>
+      <c r="U1" s="49"/>
+      <c r="V1" s="49"/>
+      <c r="W1" s="49"/>
+      <c r="X1" s="49"/>
+      <c r="Y1" s="49"/>
+      <c r="Z1" s="49"/>
+      <c r="AA1" s="49"/>
+      <c r="AB1" s="49"/>
+      <c r="AC1" s="49"/>
+      <c r="AD1" s="49"/>
+      <c r="AE1" s="49"/>
+      <c r="AF1" s="49"/>
+      <c r="AG1" s="49"/>
+      <c r="AH1" s="49"/>
+      <c r="AI1" s="49"/>
+      <c r="AJ1" s="49"/>
+      <c r="AK1" s="49"/>
     </row>
     <row r="2" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="59" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="51"/>
-      <c r="J2" s="51"/>
-      <c r="K2" s="51"/>
-      <c r="L2" s="51"/>
-      <c r="M2" s="51"/>
-      <c r="N2" s="51"/>
-      <c r="O2" s="51"/>
-      <c r="P2" s="51"/>
-      <c r="Q2" s="51"/>
-      <c r="R2" s="51"/>
-      <c r="S2" s="51"/>
-      <c r="T2" s="51"/>
-      <c r="U2" s="51"/>
-      <c r="V2" s="51"/>
-      <c r="W2" s="51"/>
-      <c r="X2" s="51"/>
-      <c r="Y2" s="51"/>
-      <c r="Z2" s="51"/>
-      <c r="AA2" s="51"/>
-      <c r="AB2" s="51"/>
-      <c r="AC2" s="51"/>
-      <c r="AD2" s="51"/>
-      <c r="AE2" s="51"/>
-      <c r="AF2" s="51"/>
-      <c r="AG2" s="51"/>
-      <c r="AH2" s="51"/>
-      <c r="AI2" s="51"/>
-      <c r="AJ2" s="51"/>
-      <c r="AK2" s="51"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="59"/>
+      <c r="L2" s="59"/>
+      <c r="M2" s="59"/>
+      <c r="N2" s="59"/>
+      <c r="O2" s="59"/>
+      <c r="P2" s="59"/>
+      <c r="Q2" s="59"/>
+      <c r="R2" s="59"/>
+      <c r="S2" s="59"/>
+      <c r="T2" s="59"/>
+      <c r="U2" s="59"/>
+      <c r="V2" s="59"/>
+      <c r="W2" s="59"/>
+      <c r="X2" s="59"/>
+      <c r="Y2" s="59"/>
+      <c r="Z2" s="59"/>
+      <c r="AA2" s="59"/>
+      <c r="AB2" s="59"/>
+      <c r="AC2" s="59"/>
+      <c r="AD2" s="59"/>
+      <c r="AE2" s="59"/>
+      <c r="AF2" s="59"/>
+      <c r="AG2" s="59"/>
+      <c r="AH2" s="59"/>
+      <c r="AI2" s="59"/>
+      <c r="AJ2" s="59"/>
+      <c r="AK2" s="59"/>
     </row>
     <row r="3" spans="1:37" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:37" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="60" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="29" t="s">
@@ -3804,27 +3804,27 @@
       <c r="AE4" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="AF4" s="53" t="s">
+      <c r="AF4" s="61" t="s">
         <v>54</v>
       </c>
-      <c r="AG4" s="54" t="s">
+      <c r="AG4" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="AH4" s="55" t="s">
+      <c r="AH4" s="63" t="s">
         <v>56</v>
       </c>
-      <c r="AI4" s="56" t="s">
+      <c r="AI4" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="AJ4" s="57" t="s">
+      <c r="AJ4" s="65" t="s">
         <v>58</v>
       </c>
-      <c r="AK4" s="56" t="s">
+      <c r="AK4" s="64" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:37" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="52"/>
+      <c r="A5" s="60"/>
       <c r="B5" s="31">
         <v>1</v>
       </c>
@@ -3915,12 +3915,12 @@
       <c r="AE5" s="31">
         <v>30</v>
       </c>
-      <c r="AF5" s="53"/>
-      <c r="AG5" s="53"/>
-      <c r="AH5" s="53"/>
-      <c r="AI5" s="53"/>
-      <c r="AJ5" s="53"/>
-      <c r="AK5" s="53"/>
+      <c r="AF5" s="61"/>
+      <c r="AG5" s="61"/>
+      <c r="AH5" s="61"/>
+      <c r="AI5" s="61"/>
+      <c r="AJ5" s="61"/>
+      <c r="AK5" s="61"/>
     </row>
     <row r="6" spans="1:37" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="1:37" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4671,45 +4671,45 @@
     </row>
     <row r="18" spans="1:37" ht="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="1:37" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="48" t="s">
+      <c r="A19" s="57" t="s">
         <v>91</v>
       </c>
-      <c r="B19" s="48"/>
-      <c r="C19" s="48"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="48"/>
-      <c r="F19" s="48"/>
-      <c r="G19" s="48"/>
-      <c r="H19" s="48"/>
-      <c r="I19" s="48"/>
-      <c r="J19" s="48"/>
-      <c r="K19" s="48"/>
-      <c r="L19" s="48"/>
-      <c r="M19" s="48"/>
-      <c r="N19" s="48"/>
-      <c r="O19" s="48"/>
-      <c r="P19" s="48"/>
-      <c r="Q19" s="48"/>
-      <c r="R19" s="48"/>
-      <c r="S19" s="48"/>
-      <c r="T19" s="48"/>
-      <c r="U19" s="48"/>
-      <c r="V19" s="48"/>
-      <c r="W19" s="48"/>
-      <c r="X19" s="48"/>
-      <c r="Y19" s="48"/>
-      <c r="Z19" s="48"/>
-      <c r="AA19" s="48"/>
-      <c r="AB19" s="48"/>
-      <c r="AC19" s="48"/>
-      <c r="AD19" s="48"/>
-      <c r="AE19" s="48"/>
-      <c r="AF19" s="48"/>
-      <c r="AG19" s="48"/>
-      <c r="AH19" s="48"/>
-      <c r="AI19" s="48"/>
-      <c r="AJ19" s="48"/>
-      <c r="AK19" s="48"/>
+      <c r="B19" s="57"/>
+      <c r="C19" s="57"/>
+      <c r="D19" s="57"/>
+      <c r="E19" s="57"/>
+      <c r="F19" s="57"/>
+      <c r="G19" s="57"/>
+      <c r="H19" s="57"/>
+      <c r="I19" s="57"/>
+      <c r="J19" s="57"/>
+      <c r="K19" s="57"/>
+      <c r="L19" s="57"/>
+      <c r="M19" s="57"/>
+      <c r="N19" s="57"/>
+      <c r="O19" s="57"/>
+      <c r="P19" s="57"/>
+      <c r="Q19" s="57"/>
+      <c r="R19" s="57"/>
+      <c r="S19" s="57"/>
+      <c r="T19" s="57"/>
+      <c r="U19" s="57"/>
+      <c r="V19" s="57"/>
+      <c r="W19" s="57"/>
+      <c r="X19" s="57"/>
+      <c r="Y19" s="57"/>
+      <c r="Z19" s="57"/>
+      <c r="AA19" s="57"/>
+      <c r="AB19" s="57"/>
+      <c r="AC19" s="57"/>
+      <c r="AD19" s="57"/>
+      <c r="AE19" s="57"/>
+      <c r="AF19" s="57"/>
+      <c r="AG19" s="57"/>
+      <c r="AH19" s="57"/>
+      <c r="AI19" s="57"/>
+      <c r="AJ19" s="57"/>
+      <c r="AK19" s="57"/>
     </row>
     <row r="20" spans="1:37" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
@@ -5068,10 +5068,10 @@
       </c>
     </row>
     <row r="31" spans="1:37" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="49" t="s">
+      <c r="A31" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="B31" s="49"/>
+      <c r="B31" s="58"/>
       <c r="C31" s="11">
         <f t="shared" ref="C31:H31" si="8">SUM(C21:C30)</f>
         <v>15300000</v>
@@ -5130,92 +5130,92 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="49" t="s">
         <v>92</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
-      <c r="L1" s="50"/>
-      <c r="M1" s="50"/>
-      <c r="N1" s="50"/>
-      <c r="O1" s="50"/>
-      <c r="P1" s="50"/>
-      <c r="Q1" s="50"/>
-      <c r="R1" s="50"/>
-      <c r="S1" s="50"/>
-      <c r="T1" s="50"/>
-      <c r="U1" s="50"/>
-      <c r="V1" s="50"/>
-      <c r="W1" s="50"/>
-      <c r="X1" s="50"/>
-      <c r="Y1" s="50"/>
-      <c r="Z1" s="50"/>
-      <c r="AA1" s="50"/>
-      <c r="AB1" s="50"/>
-      <c r="AC1" s="50"/>
-      <c r="AD1" s="50"/>
-      <c r="AE1" s="50"/>
-      <c r="AF1" s="50"/>
-      <c r="AG1" s="50"/>
-      <c r="AH1" s="50"/>
-      <c r="AI1" s="50"/>
-      <c r="AJ1" s="50"/>
-      <c r="AK1" s="50"/>
-      <c r="AL1" s="50"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
+      <c r="M1" s="49"/>
+      <c r="N1" s="49"/>
+      <c r="O1" s="49"/>
+      <c r="P1" s="49"/>
+      <c r="Q1" s="49"/>
+      <c r="R1" s="49"/>
+      <c r="S1" s="49"/>
+      <c r="T1" s="49"/>
+      <c r="U1" s="49"/>
+      <c r="V1" s="49"/>
+      <c r="W1" s="49"/>
+      <c r="X1" s="49"/>
+      <c r="Y1" s="49"/>
+      <c r="Z1" s="49"/>
+      <c r="AA1" s="49"/>
+      <c r="AB1" s="49"/>
+      <c r="AC1" s="49"/>
+      <c r="AD1" s="49"/>
+      <c r="AE1" s="49"/>
+      <c r="AF1" s="49"/>
+      <c r="AG1" s="49"/>
+      <c r="AH1" s="49"/>
+      <c r="AI1" s="49"/>
+      <c r="AJ1" s="49"/>
+      <c r="AK1" s="49"/>
+      <c r="AL1" s="49"/>
     </row>
     <row r="2" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="59" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="51"/>
-      <c r="J2" s="51"/>
-      <c r="K2" s="51"/>
-      <c r="L2" s="51"/>
-      <c r="M2" s="51"/>
-      <c r="N2" s="51"/>
-      <c r="O2" s="51"/>
-      <c r="P2" s="51"/>
-      <c r="Q2" s="51"/>
-      <c r="R2" s="51"/>
-      <c r="S2" s="51"/>
-      <c r="T2" s="51"/>
-      <c r="U2" s="51"/>
-      <c r="V2" s="51"/>
-      <c r="W2" s="51"/>
-      <c r="X2" s="51"/>
-      <c r="Y2" s="51"/>
-      <c r="Z2" s="51"/>
-      <c r="AA2" s="51"/>
-      <c r="AB2" s="51"/>
-      <c r="AC2" s="51"/>
-      <c r="AD2" s="51"/>
-      <c r="AE2" s="51"/>
-      <c r="AF2" s="51"/>
-      <c r="AG2" s="51"/>
-      <c r="AH2" s="51"/>
-      <c r="AI2" s="51"/>
-      <c r="AJ2" s="51"/>
-      <c r="AK2" s="51"/>
-      <c r="AL2" s="51"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="59"/>
+      <c r="L2" s="59"/>
+      <c r="M2" s="59"/>
+      <c r="N2" s="59"/>
+      <c r="O2" s="59"/>
+      <c r="P2" s="59"/>
+      <c r="Q2" s="59"/>
+      <c r="R2" s="59"/>
+      <c r="S2" s="59"/>
+      <c r="T2" s="59"/>
+      <c r="U2" s="59"/>
+      <c r="V2" s="59"/>
+      <c r="W2" s="59"/>
+      <c r="X2" s="59"/>
+      <c r="Y2" s="59"/>
+      <c r="Z2" s="59"/>
+      <c r="AA2" s="59"/>
+      <c r="AB2" s="59"/>
+      <c r="AC2" s="59"/>
+      <c r="AD2" s="59"/>
+      <c r="AE2" s="59"/>
+      <c r="AF2" s="59"/>
+      <c r="AG2" s="59"/>
+      <c r="AH2" s="59"/>
+      <c r="AI2" s="59"/>
+      <c r="AJ2" s="59"/>
+      <c r="AK2" s="59"/>
+      <c r="AL2" s="59"/>
     </row>
     <row r="3" spans="1:38" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="60" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="29" t="s">
@@ -5311,27 +5311,27 @@
       <c r="AF4" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="AG4" s="53" t="s">
+      <c r="AG4" s="61" t="s">
         <v>54</v>
       </c>
-      <c r="AH4" s="54" t="s">
+      <c r="AH4" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="AI4" s="55" t="s">
+      <c r="AI4" s="63" t="s">
         <v>56</v>
       </c>
-      <c r="AJ4" s="56" t="s">
+      <c r="AJ4" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="AK4" s="57" t="s">
+      <c r="AK4" s="65" t="s">
         <v>58</v>
       </c>
-      <c r="AL4" s="56" t="s">
+      <c r="AL4" s="64" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:38" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="52"/>
+      <c r="A5" s="60"/>
       <c r="B5" s="31">
         <v>1</v>
       </c>
@@ -5425,12 +5425,12 @@
       <c r="AF5" s="31">
         <v>31</v>
       </c>
-      <c r="AG5" s="53"/>
-      <c r="AH5" s="53"/>
-      <c r="AI5" s="53"/>
-      <c r="AJ5" s="53"/>
-      <c r="AK5" s="53"/>
-      <c r="AL5" s="53"/>
+      <c r="AG5" s="61"/>
+      <c r="AH5" s="61"/>
+      <c r="AI5" s="61"/>
+      <c r="AJ5" s="61"/>
+      <c r="AK5" s="61"/>
+      <c r="AL5" s="61"/>
     </row>
     <row r="6" spans="1:38" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="1:38" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6195,46 +6195,46 @@
     </row>
     <row r="18" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="1:38" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="48" t="s">
+      <c r="A19" s="57" t="s">
         <v>94</v>
       </c>
-      <c r="B19" s="48"/>
-      <c r="C19" s="48"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="48"/>
-      <c r="F19" s="48"/>
-      <c r="G19" s="48"/>
-      <c r="H19" s="48"/>
-      <c r="I19" s="48"/>
-      <c r="J19" s="48"/>
-      <c r="K19" s="48"/>
-      <c r="L19" s="48"/>
-      <c r="M19" s="48"/>
-      <c r="N19" s="48"/>
-      <c r="O19" s="48"/>
-      <c r="P19" s="48"/>
-      <c r="Q19" s="48"/>
-      <c r="R19" s="48"/>
-      <c r="S19" s="48"/>
-      <c r="T19" s="48"/>
-      <c r="U19" s="48"/>
-      <c r="V19" s="48"/>
-      <c r="W19" s="48"/>
-      <c r="X19" s="48"/>
-      <c r="Y19" s="48"/>
-      <c r="Z19" s="48"/>
-      <c r="AA19" s="48"/>
-      <c r="AB19" s="48"/>
-      <c r="AC19" s="48"/>
-      <c r="AD19" s="48"/>
-      <c r="AE19" s="48"/>
-      <c r="AF19" s="48"/>
-      <c r="AG19" s="48"/>
-      <c r="AH19" s="48"/>
-      <c r="AI19" s="48"/>
-      <c r="AJ19" s="48"/>
-      <c r="AK19" s="48"/>
-      <c r="AL19" s="48"/>
+      <c r="B19" s="57"/>
+      <c r="C19" s="57"/>
+      <c r="D19" s="57"/>
+      <c r="E19" s="57"/>
+      <c r="F19" s="57"/>
+      <c r="G19" s="57"/>
+      <c r="H19" s="57"/>
+      <c r="I19" s="57"/>
+      <c r="J19" s="57"/>
+      <c r="K19" s="57"/>
+      <c r="L19" s="57"/>
+      <c r="M19" s="57"/>
+      <c r="N19" s="57"/>
+      <c r="O19" s="57"/>
+      <c r="P19" s="57"/>
+      <c r="Q19" s="57"/>
+      <c r="R19" s="57"/>
+      <c r="S19" s="57"/>
+      <c r="T19" s="57"/>
+      <c r="U19" s="57"/>
+      <c r="V19" s="57"/>
+      <c r="W19" s="57"/>
+      <c r="X19" s="57"/>
+      <c r="Y19" s="57"/>
+      <c r="Z19" s="57"/>
+      <c r="AA19" s="57"/>
+      <c r="AB19" s="57"/>
+      <c r="AC19" s="57"/>
+      <c r="AD19" s="57"/>
+      <c r="AE19" s="57"/>
+      <c r="AF19" s="57"/>
+      <c r="AG19" s="57"/>
+      <c r="AH19" s="57"/>
+      <c r="AI19" s="57"/>
+      <c r="AJ19" s="57"/>
+      <c r="AK19" s="57"/>
+      <c r="AL19" s="57"/>
     </row>
     <row r="20" spans="1:38" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
@@ -6593,10 +6593,10 @@
       </c>
     </row>
     <row r="31" spans="1:38" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="49" t="s">
+      <c r="A31" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="B31" s="49"/>
+      <c r="B31" s="58"/>
       <c r="C31" s="11">
         <f t="shared" ref="C31:H31" si="8">SUM(C21:C30)</f>
         <v>15300000</v>
@@ -6655,90 +6655,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="49" t="s">
         <v>95</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
-      <c r="L1" s="50"/>
-      <c r="M1" s="50"/>
-      <c r="N1" s="50"/>
-      <c r="O1" s="50"/>
-      <c r="P1" s="50"/>
-      <c r="Q1" s="50"/>
-      <c r="R1" s="50"/>
-      <c r="S1" s="50"/>
-      <c r="T1" s="50"/>
-      <c r="U1" s="50"/>
-      <c r="V1" s="50"/>
-      <c r="W1" s="50"/>
-      <c r="X1" s="50"/>
-      <c r="Y1" s="50"/>
-      <c r="Z1" s="50"/>
-      <c r="AA1" s="50"/>
-      <c r="AB1" s="50"/>
-      <c r="AC1" s="50"/>
-      <c r="AD1" s="50"/>
-      <c r="AE1" s="50"/>
-      <c r="AF1" s="50"/>
-      <c r="AG1" s="50"/>
-      <c r="AH1" s="50"/>
-      <c r="AI1" s="50"/>
-      <c r="AJ1" s="50"/>
-      <c r="AK1" s="50"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
+      <c r="M1" s="49"/>
+      <c r="N1" s="49"/>
+      <c r="O1" s="49"/>
+      <c r="P1" s="49"/>
+      <c r="Q1" s="49"/>
+      <c r="R1" s="49"/>
+      <c r="S1" s="49"/>
+      <c r="T1" s="49"/>
+      <c r="U1" s="49"/>
+      <c r="V1" s="49"/>
+      <c r="W1" s="49"/>
+      <c r="X1" s="49"/>
+      <c r="Y1" s="49"/>
+      <c r="Z1" s="49"/>
+      <c r="AA1" s="49"/>
+      <c r="AB1" s="49"/>
+      <c r="AC1" s="49"/>
+      <c r="AD1" s="49"/>
+      <c r="AE1" s="49"/>
+      <c r="AF1" s="49"/>
+      <c r="AG1" s="49"/>
+      <c r="AH1" s="49"/>
+      <c r="AI1" s="49"/>
+      <c r="AJ1" s="49"/>
+      <c r="AK1" s="49"/>
     </row>
     <row r="2" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="59" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="51"/>
-      <c r="J2" s="51"/>
-      <c r="K2" s="51"/>
-      <c r="L2" s="51"/>
-      <c r="M2" s="51"/>
-      <c r="N2" s="51"/>
-      <c r="O2" s="51"/>
-      <c r="P2" s="51"/>
-      <c r="Q2" s="51"/>
-      <c r="R2" s="51"/>
-      <c r="S2" s="51"/>
-      <c r="T2" s="51"/>
-      <c r="U2" s="51"/>
-      <c r="V2" s="51"/>
-      <c r="W2" s="51"/>
-      <c r="X2" s="51"/>
-      <c r="Y2" s="51"/>
-      <c r="Z2" s="51"/>
-      <c r="AA2" s="51"/>
-      <c r="AB2" s="51"/>
-      <c r="AC2" s="51"/>
-      <c r="AD2" s="51"/>
-      <c r="AE2" s="51"/>
-      <c r="AF2" s="51"/>
-      <c r="AG2" s="51"/>
-      <c r="AH2" s="51"/>
-      <c r="AI2" s="51"/>
-      <c r="AJ2" s="51"/>
-      <c r="AK2" s="51"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="59"/>
+      <c r="L2" s="59"/>
+      <c r="M2" s="59"/>
+      <c r="N2" s="59"/>
+      <c r="O2" s="59"/>
+      <c r="P2" s="59"/>
+      <c r="Q2" s="59"/>
+      <c r="R2" s="59"/>
+      <c r="S2" s="59"/>
+      <c r="T2" s="59"/>
+      <c r="U2" s="59"/>
+      <c r="V2" s="59"/>
+      <c r="W2" s="59"/>
+      <c r="X2" s="59"/>
+      <c r="Y2" s="59"/>
+      <c r="Z2" s="59"/>
+      <c r="AA2" s="59"/>
+      <c r="AB2" s="59"/>
+      <c r="AC2" s="59"/>
+      <c r="AD2" s="59"/>
+      <c r="AE2" s="59"/>
+      <c r="AF2" s="59"/>
+      <c r="AG2" s="59"/>
+      <c r="AH2" s="59"/>
+      <c r="AI2" s="59"/>
+      <c r="AJ2" s="59"/>
+      <c r="AK2" s="59"/>
     </row>
     <row r="3" spans="1:37" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:37" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="60" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="29" t="s">
@@ -6831,27 +6831,27 @@
       <c r="AE4" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="AF4" s="53" t="s">
+      <c r="AF4" s="61" t="s">
         <v>54</v>
       </c>
-      <c r="AG4" s="54" t="s">
+      <c r="AG4" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="AH4" s="55" t="s">
+      <c r="AH4" s="63" t="s">
         <v>56</v>
       </c>
-      <c r="AI4" s="56" t="s">
+      <c r="AI4" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="AJ4" s="57" t="s">
+      <c r="AJ4" s="65" t="s">
         <v>58</v>
       </c>
-      <c r="AK4" s="56" t="s">
+      <c r="AK4" s="64" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:37" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="52"/>
+      <c r="A5" s="60"/>
       <c r="B5" s="31">
         <v>1</v>
       </c>
@@ -6942,12 +6942,12 @@
       <c r="AE5" s="31">
         <v>30</v>
       </c>
-      <c r="AF5" s="53"/>
-      <c r="AG5" s="53"/>
-      <c r="AH5" s="53"/>
-      <c r="AI5" s="53"/>
-      <c r="AJ5" s="53"/>
-      <c r="AK5" s="53"/>
+      <c r="AF5" s="61"/>
+      <c r="AG5" s="61"/>
+      <c r="AH5" s="61"/>
+      <c r="AI5" s="61"/>
+      <c r="AJ5" s="61"/>
+      <c r="AK5" s="61"/>
     </row>
     <row r="6" spans="1:37" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="1:37" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7698,45 +7698,45 @@
     </row>
     <row r="18" spans="1:37" ht="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="1:37" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="48" t="s">
+      <c r="A19" s="57" t="s">
         <v>97</v>
       </c>
-      <c r="B19" s="48"/>
-      <c r="C19" s="48"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="48"/>
-      <c r="F19" s="48"/>
-      <c r="G19" s="48"/>
-      <c r="H19" s="48"/>
-      <c r="I19" s="48"/>
-      <c r="J19" s="48"/>
-      <c r="K19" s="48"/>
-      <c r="L19" s="48"/>
-      <c r="M19" s="48"/>
-      <c r="N19" s="48"/>
-      <c r="O19" s="48"/>
-      <c r="P19" s="48"/>
-      <c r="Q19" s="48"/>
-      <c r="R19" s="48"/>
-      <c r="S19" s="48"/>
-      <c r="T19" s="48"/>
-      <c r="U19" s="48"/>
-      <c r="V19" s="48"/>
-      <c r="W19" s="48"/>
-      <c r="X19" s="48"/>
-      <c r="Y19" s="48"/>
-      <c r="Z19" s="48"/>
-      <c r="AA19" s="48"/>
-      <c r="AB19" s="48"/>
-      <c r="AC19" s="48"/>
-      <c r="AD19" s="48"/>
-      <c r="AE19" s="48"/>
-      <c r="AF19" s="48"/>
-      <c r="AG19" s="48"/>
-      <c r="AH19" s="48"/>
-      <c r="AI19" s="48"/>
-      <c r="AJ19" s="48"/>
-      <c r="AK19" s="48"/>
+      <c r="B19" s="57"/>
+      <c r="C19" s="57"/>
+      <c r="D19" s="57"/>
+      <c r="E19" s="57"/>
+      <c r="F19" s="57"/>
+      <c r="G19" s="57"/>
+      <c r="H19" s="57"/>
+      <c r="I19" s="57"/>
+      <c r="J19" s="57"/>
+      <c r="K19" s="57"/>
+      <c r="L19" s="57"/>
+      <c r="M19" s="57"/>
+      <c r="N19" s="57"/>
+      <c r="O19" s="57"/>
+      <c r="P19" s="57"/>
+      <c r="Q19" s="57"/>
+      <c r="R19" s="57"/>
+      <c r="S19" s="57"/>
+      <c r="T19" s="57"/>
+      <c r="U19" s="57"/>
+      <c r="V19" s="57"/>
+      <c r="W19" s="57"/>
+      <c r="X19" s="57"/>
+      <c r="Y19" s="57"/>
+      <c r="Z19" s="57"/>
+      <c r="AA19" s="57"/>
+      <c r="AB19" s="57"/>
+      <c r="AC19" s="57"/>
+      <c r="AD19" s="57"/>
+      <c r="AE19" s="57"/>
+      <c r="AF19" s="57"/>
+      <c r="AG19" s="57"/>
+      <c r="AH19" s="57"/>
+      <c r="AI19" s="57"/>
+      <c r="AJ19" s="57"/>
+      <c r="AK19" s="57"/>
     </row>
     <row r="20" spans="1:37" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
@@ -8095,10 +8095,10 @@
       </c>
     </row>
     <row r="31" spans="1:37" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="49" t="s">
+      <c r="A31" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="B31" s="49"/>
+      <c r="B31" s="58"/>
       <c r="C31" s="11">
         <f t="shared" ref="C31:H31" si="8">SUM(C21:C30)</f>
         <v>15300000</v>
@@ -8157,92 +8157,92 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="49" t="s">
         <v>98</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
-      <c r="L1" s="50"/>
-      <c r="M1" s="50"/>
-      <c r="N1" s="50"/>
-      <c r="O1" s="50"/>
-      <c r="P1" s="50"/>
-      <c r="Q1" s="50"/>
-      <c r="R1" s="50"/>
-      <c r="S1" s="50"/>
-      <c r="T1" s="50"/>
-      <c r="U1" s="50"/>
-      <c r="V1" s="50"/>
-      <c r="W1" s="50"/>
-      <c r="X1" s="50"/>
-      <c r="Y1" s="50"/>
-      <c r="Z1" s="50"/>
-      <c r="AA1" s="50"/>
-      <c r="AB1" s="50"/>
-      <c r="AC1" s="50"/>
-      <c r="AD1" s="50"/>
-      <c r="AE1" s="50"/>
-      <c r="AF1" s="50"/>
-      <c r="AG1" s="50"/>
-      <c r="AH1" s="50"/>
-      <c r="AI1" s="50"/>
-      <c r="AJ1" s="50"/>
-      <c r="AK1" s="50"/>
-      <c r="AL1" s="50"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
+      <c r="M1" s="49"/>
+      <c r="N1" s="49"/>
+      <c r="O1" s="49"/>
+      <c r="P1" s="49"/>
+      <c r="Q1" s="49"/>
+      <c r="R1" s="49"/>
+      <c r="S1" s="49"/>
+      <c r="T1" s="49"/>
+      <c r="U1" s="49"/>
+      <c r="V1" s="49"/>
+      <c r="W1" s="49"/>
+      <c r="X1" s="49"/>
+      <c r="Y1" s="49"/>
+      <c r="Z1" s="49"/>
+      <c r="AA1" s="49"/>
+      <c r="AB1" s="49"/>
+      <c r="AC1" s="49"/>
+      <c r="AD1" s="49"/>
+      <c r="AE1" s="49"/>
+      <c r="AF1" s="49"/>
+      <c r="AG1" s="49"/>
+      <c r="AH1" s="49"/>
+      <c r="AI1" s="49"/>
+      <c r="AJ1" s="49"/>
+      <c r="AK1" s="49"/>
+      <c r="AL1" s="49"/>
     </row>
     <row r="2" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="59" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="51"/>
-      <c r="J2" s="51"/>
-      <c r="K2" s="51"/>
-      <c r="L2" s="51"/>
-      <c r="M2" s="51"/>
-      <c r="N2" s="51"/>
-      <c r="O2" s="51"/>
-      <c r="P2" s="51"/>
-      <c r="Q2" s="51"/>
-      <c r="R2" s="51"/>
-      <c r="S2" s="51"/>
-      <c r="T2" s="51"/>
-      <c r="U2" s="51"/>
-      <c r="V2" s="51"/>
-      <c r="W2" s="51"/>
-      <c r="X2" s="51"/>
-      <c r="Y2" s="51"/>
-      <c r="Z2" s="51"/>
-      <c r="AA2" s="51"/>
-      <c r="AB2" s="51"/>
-      <c r="AC2" s="51"/>
-      <c r="AD2" s="51"/>
-      <c r="AE2" s="51"/>
-      <c r="AF2" s="51"/>
-      <c r="AG2" s="51"/>
-      <c r="AH2" s="51"/>
-      <c r="AI2" s="51"/>
-      <c r="AJ2" s="51"/>
-      <c r="AK2" s="51"/>
-      <c r="AL2" s="51"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="59"/>
+      <c r="L2" s="59"/>
+      <c r="M2" s="59"/>
+      <c r="N2" s="59"/>
+      <c r="O2" s="59"/>
+      <c r="P2" s="59"/>
+      <c r="Q2" s="59"/>
+      <c r="R2" s="59"/>
+      <c r="S2" s="59"/>
+      <c r="T2" s="59"/>
+      <c r="U2" s="59"/>
+      <c r="V2" s="59"/>
+      <c r="W2" s="59"/>
+      <c r="X2" s="59"/>
+      <c r="Y2" s="59"/>
+      <c r="Z2" s="59"/>
+      <c r="AA2" s="59"/>
+      <c r="AB2" s="59"/>
+      <c r="AC2" s="59"/>
+      <c r="AD2" s="59"/>
+      <c r="AE2" s="59"/>
+      <c r="AF2" s="59"/>
+      <c r="AG2" s="59"/>
+      <c r="AH2" s="59"/>
+      <c r="AI2" s="59"/>
+      <c r="AJ2" s="59"/>
+      <c r="AK2" s="59"/>
+      <c r="AL2" s="59"/>
     </row>
     <row r="3" spans="1:38" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="60" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="29" t="s">
@@ -8338,27 +8338,27 @@
       <c r="AF4" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="AG4" s="53" t="s">
+      <c r="AG4" s="61" t="s">
         <v>54</v>
       </c>
-      <c r="AH4" s="54" t="s">
+      <c r="AH4" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="AI4" s="55" t="s">
+      <c r="AI4" s="63" t="s">
         <v>56</v>
       </c>
-      <c r="AJ4" s="56" t="s">
+      <c r="AJ4" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="AK4" s="57" t="s">
+      <c r="AK4" s="65" t="s">
         <v>58</v>
       </c>
-      <c r="AL4" s="56" t="s">
+      <c r="AL4" s="64" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:38" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="52"/>
+      <c r="A5" s="60"/>
       <c r="B5" s="31">
         <v>1</v>
       </c>
@@ -8452,12 +8452,12 @@
       <c r="AF5" s="31">
         <v>31</v>
       </c>
-      <c r="AG5" s="53"/>
-      <c r="AH5" s="53"/>
-      <c r="AI5" s="53"/>
-      <c r="AJ5" s="53"/>
-      <c r="AK5" s="53"/>
-      <c r="AL5" s="53"/>
+      <c r="AG5" s="61"/>
+      <c r="AH5" s="61"/>
+      <c r="AI5" s="61"/>
+      <c r="AJ5" s="61"/>
+      <c r="AK5" s="61"/>
+      <c r="AL5" s="61"/>
     </row>
     <row r="6" spans="1:38" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="1:38" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -9222,46 +9222,46 @@
     </row>
     <row r="18" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="1:38" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="48" t="s">
+      <c r="A19" s="57" t="s">
         <v>100</v>
       </c>
-      <c r="B19" s="48"/>
-      <c r="C19" s="48"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="48"/>
-      <c r="F19" s="48"/>
-      <c r="G19" s="48"/>
-      <c r="H19" s="48"/>
-      <c r="I19" s="48"/>
-      <c r="J19" s="48"/>
-      <c r="K19" s="48"/>
-      <c r="L19" s="48"/>
-      <c r="M19" s="48"/>
-      <c r="N19" s="48"/>
-      <c r="O19" s="48"/>
-      <c r="P19" s="48"/>
-      <c r="Q19" s="48"/>
-      <c r="R19" s="48"/>
-      <c r="S19" s="48"/>
-      <c r="T19" s="48"/>
-      <c r="U19" s="48"/>
-      <c r="V19" s="48"/>
-      <c r="W19" s="48"/>
-      <c r="X19" s="48"/>
-      <c r="Y19" s="48"/>
-      <c r="Z19" s="48"/>
-      <c r="AA19" s="48"/>
-      <c r="AB19" s="48"/>
-      <c r="AC19" s="48"/>
-      <c r="AD19" s="48"/>
-      <c r="AE19" s="48"/>
-      <c r="AF19" s="48"/>
-      <c r="AG19" s="48"/>
-      <c r="AH19" s="48"/>
-      <c r="AI19" s="48"/>
-      <c r="AJ19" s="48"/>
-      <c r="AK19" s="48"/>
-      <c r="AL19" s="48"/>
+      <c r="B19" s="57"/>
+      <c r="C19" s="57"/>
+      <c r="D19" s="57"/>
+      <c r="E19" s="57"/>
+      <c r="F19" s="57"/>
+      <c r="G19" s="57"/>
+      <c r="H19" s="57"/>
+      <c r="I19" s="57"/>
+      <c r="J19" s="57"/>
+      <c r="K19" s="57"/>
+      <c r="L19" s="57"/>
+      <c r="M19" s="57"/>
+      <c r="N19" s="57"/>
+      <c r="O19" s="57"/>
+      <c r="P19" s="57"/>
+      <c r="Q19" s="57"/>
+      <c r="R19" s="57"/>
+      <c r="S19" s="57"/>
+      <c r="T19" s="57"/>
+      <c r="U19" s="57"/>
+      <c r="V19" s="57"/>
+      <c r="W19" s="57"/>
+      <c r="X19" s="57"/>
+      <c r="Y19" s="57"/>
+      <c r="Z19" s="57"/>
+      <c r="AA19" s="57"/>
+      <c r="AB19" s="57"/>
+      <c r="AC19" s="57"/>
+      <c r="AD19" s="57"/>
+      <c r="AE19" s="57"/>
+      <c r="AF19" s="57"/>
+      <c r="AG19" s="57"/>
+      <c r="AH19" s="57"/>
+      <c r="AI19" s="57"/>
+      <c r="AJ19" s="57"/>
+      <c r="AK19" s="57"/>
+      <c r="AL19" s="57"/>
     </row>
     <row r="20" spans="1:38" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
@@ -9620,10 +9620,10 @@
       </c>
     </row>
     <row r="31" spans="1:38" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="49" t="s">
+      <c r="A31" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="B31" s="49"/>
+      <c r="B31" s="58"/>
       <c r="C31" s="11">
         <f t="shared" ref="C31:H31" si="8">SUM(C21:C30)</f>
         <v>15300000</v>
@@ -9684,30 +9684,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="49" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
     </row>
     <row r="2" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="62" t="s">
+      <c r="B2" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="62"/>
-      <c r="D2" s="63" t="s">
+      <c r="C2" s="50"/>
+      <c r="D2" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="63"/>
-      <c r="F2" s="63"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
       <c r="G2" s="14">
         <v>9</v>
       </c>
@@ -9878,74 +9878,74 @@
     </row>
     <row r="16" spans="1:8" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="17" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="64" t="s">
+      <c r="A17" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="B17" s="64"/>
-      <c r="C17" s="64"/>
-      <c r="D17" s="64"/>
-      <c r="E17" s="64"/>
-      <c r="F17" s="64"/>
+      <c r="B17" s="52"/>
+      <c r="C17" s="52"/>
+      <c r="D17" s="52"/>
+      <c r="E17" s="52"/>
+      <c r="F17" s="52"/>
     </row>
     <row r="18" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="65" t="s">
+      <c r="B18" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="65"/>
-      <c r="D18" s="65"/>
-      <c r="E18" s="65"/>
-      <c r="F18" s="65"/>
+      <c r="C18" s="53"/>
+      <c r="D18" s="53"/>
+      <c r="E18" s="53"/>
+      <c r="F18" s="53"/>
     </row>
     <row r="19" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="61" t="s">
+      <c r="B19" s="48" t="s">
         <v>38</v>
       </c>
-      <c r="C19" s="61"/>
-      <c r="D19" s="61"/>
-      <c r="E19" s="61"/>
-      <c r="F19" s="61"/>
+      <c r="C19" s="48"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="48"/>
     </row>
     <row r="20" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="61" t="s">
+      <c r="B20" s="48" t="s">
         <v>40</v>
       </c>
-      <c r="C20" s="61"/>
-      <c r="D20" s="61"/>
-      <c r="E20" s="61"/>
-      <c r="F20" s="61"/>
+      <c r="C20" s="48"/>
+      <c r="D20" s="48"/>
+      <c r="E20" s="48"/>
+      <c r="F20" s="48"/>
     </row>
     <row r="21" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="61" t="s">
+      <c r="B21" s="48" t="s">
         <v>42</v>
       </c>
-      <c r="C21" s="61"/>
-      <c r="D21" s="61"/>
-      <c r="E21" s="61"/>
-      <c r="F21" s="61"/>
+      <c r="C21" s="48"/>
+      <c r="D21" s="48"/>
+      <c r="E21" s="48"/>
+      <c r="F21" s="48"/>
     </row>
     <row r="22" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="61" t="s">
+      <c r="B22" s="48" t="s">
         <v>44</v>
       </c>
-      <c r="C22" s="61"/>
-      <c r="D22" s="61"/>
-      <c r="E22" s="61"/>
-      <c r="F22" s="61"/>
+      <c r="C22" s="48"/>
+      <c r="D22" s="48"/>
+      <c r="E22" s="48"/>
+      <c r="F22" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -9988,92 +9988,92 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="49" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
-      <c r="L1" s="50"/>
-      <c r="M1" s="50"/>
-      <c r="N1" s="50"/>
-      <c r="O1" s="50"/>
-      <c r="P1" s="50"/>
-      <c r="Q1" s="50"/>
-      <c r="R1" s="50"/>
-      <c r="S1" s="50"/>
-      <c r="T1" s="50"/>
-      <c r="U1" s="50"/>
-      <c r="V1" s="50"/>
-      <c r="W1" s="50"/>
-      <c r="X1" s="50"/>
-      <c r="Y1" s="50"/>
-      <c r="Z1" s="50"/>
-      <c r="AA1" s="50"/>
-      <c r="AB1" s="50"/>
-      <c r="AC1" s="50"/>
-      <c r="AD1" s="50"/>
-      <c r="AE1" s="50"/>
-      <c r="AF1" s="50"/>
-      <c r="AG1" s="50"/>
-      <c r="AH1" s="50"/>
-      <c r="AI1" s="50"/>
-      <c r="AJ1" s="50"/>
-      <c r="AK1" s="50"/>
-      <c r="AL1" s="50"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
+      <c r="M1" s="49"/>
+      <c r="N1" s="49"/>
+      <c r="O1" s="49"/>
+      <c r="P1" s="49"/>
+      <c r="Q1" s="49"/>
+      <c r="R1" s="49"/>
+      <c r="S1" s="49"/>
+      <c r="T1" s="49"/>
+      <c r="U1" s="49"/>
+      <c r="V1" s="49"/>
+      <c r="W1" s="49"/>
+      <c r="X1" s="49"/>
+      <c r="Y1" s="49"/>
+      <c r="Z1" s="49"/>
+      <c r="AA1" s="49"/>
+      <c r="AB1" s="49"/>
+      <c r="AC1" s="49"/>
+      <c r="AD1" s="49"/>
+      <c r="AE1" s="49"/>
+      <c r="AF1" s="49"/>
+      <c r="AG1" s="49"/>
+      <c r="AH1" s="49"/>
+      <c r="AI1" s="49"/>
+      <c r="AJ1" s="49"/>
+      <c r="AK1" s="49"/>
+      <c r="AL1" s="49"/>
     </row>
     <row r="2" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="59" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="51"/>
-      <c r="J2" s="51"/>
-      <c r="K2" s="51"/>
-      <c r="L2" s="51"/>
-      <c r="M2" s="51"/>
-      <c r="N2" s="51"/>
-      <c r="O2" s="51"/>
-      <c r="P2" s="51"/>
-      <c r="Q2" s="51"/>
-      <c r="R2" s="51"/>
-      <c r="S2" s="51"/>
-      <c r="T2" s="51"/>
-      <c r="U2" s="51"/>
-      <c r="V2" s="51"/>
-      <c r="W2" s="51"/>
-      <c r="X2" s="51"/>
-      <c r="Y2" s="51"/>
-      <c r="Z2" s="51"/>
-      <c r="AA2" s="51"/>
-      <c r="AB2" s="51"/>
-      <c r="AC2" s="51"/>
-      <c r="AD2" s="51"/>
-      <c r="AE2" s="51"/>
-      <c r="AF2" s="51"/>
-      <c r="AG2" s="51"/>
-      <c r="AH2" s="51"/>
-      <c r="AI2" s="51"/>
-      <c r="AJ2" s="51"/>
-      <c r="AK2" s="51"/>
-      <c r="AL2" s="51"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="59"/>
+      <c r="L2" s="59"/>
+      <c r="M2" s="59"/>
+      <c r="N2" s="59"/>
+      <c r="O2" s="59"/>
+      <c r="P2" s="59"/>
+      <c r="Q2" s="59"/>
+      <c r="R2" s="59"/>
+      <c r="S2" s="59"/>
+      <c r="T2" s="59"/>
+      <c r="U2" s="59"/>
+      <c r="V2" s="59"/>
+      <c r="W2" s="59"/>
+      <c r="X2" s="59"/>
+      <c r="Y2" s="59"/>
+      <c r="Z2" s="59"/>
+      <c r="AA2" s="59"/>
+      <c r="AB2" s="59"/>
+      <c r="AC2" s="59"/>
+      <c r="AD2" s="59"/>
+      <c r="AE2" s="59"/>
+      <c r="AF2" s="59"/>
+      <c r="AG2" s="59"/>
+      <c r="AH2" s="59"/>
+      <c r="AI2" s="59"/>
+      <c r="AJ2" s="59"/>
+      <c r="AK2" s="59"/>
+      <c r="AL2" s="59"/>
     </row>
     <row r="3" spans="1:38" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="60" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="29" t="s">
@@ -10169,27 +10169,27 @@
       <c r="AF4" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="AG4" s="53" t="s">
+      <c r="AG4" s="61" t="s">
         <v>54</v>
       </c>
-      <c r="AH4" s="54" t="s">
+      <c r="AH4" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="AI4" s="55" t="s">
+      <c r="AI4" s="63" t="s">
         <v>56</v>
       </c>
-      <c r="AJ4" s="56" t="s">
+      <c r="AJ4" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="AK4" s="57" t="s">
+      <c r="AK4" s="65" t="s">
         <v>58</v>
       </c>
-      <c r="AL4" s="56" t="s">
+      <c r="AL4" s="64" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:38" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="52"/>
+      <c r="A5" s="60"/>
       <c r="B5" s="31">
         <v>1</v>
       </c>
@@ -10283,12 +10283,12 @@
       <c r="AF5" s="31">
         <v>31</v>
       </c>
-      <c r="AG5" s="53"/>
-      <c r="AH5" s="53"/>
-      <c r="AI5" s="53"/>
-      <c r="AJ5" s="53"/>
-      <c r="AK5" s="53"/>
-      <c r="AL5" s="53"/>
+      <c r="AG5" s="61"/>
+      <c r="AH5" s="61"/>
+      <c r="AI5" s="61"/>
+      <c r="AJ5" s="61"/>
+      <c r="AK5" s="61"/>
+      <c r="AL5" s="61"/>
     </row>
     <row r="6" spans="1:38" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="1:38" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -11053,46 +11053,46 @@
     </row>
     <row r="18" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="1:38" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="48" t="s">
+      <c r="A19" s="57" t="s">
         <v>61</v>
       </c>
-      <c r="B19" s="48"/>
-      <c r="C19" s="48"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="48"/>
-      <c r="F19" s="48"/>
-      <c r="G19" s="48"/>
-      <c r="H19" s="48"/>
-      <c r="I19" s="48"/>
-      <c r="J19" s="48"/>
-      <c r="K19" s="48"/>
-      <c r="L19" s="48"/>
-      <c r="M19" s="48"/>
-      <c r="N19" s="48"/>
-      <c r="O19" s="48"/>
-      <c r="P19" s="48"/>
-      <c r="Q19" s="48"/>
-      <c r="R19" s="48"/>
-      <c r="S19" s="48"/>
-      <c r="T19" s="48"/>
-      <c r="U19" s="48"/>
-      <c r="V19" s="48"/>
-      <c r="W19" s="48"/>
-      <c r="X19" s="48"/>
-      <c r="Y19" s="48"/>
-      <c r="Z19" s="48"/>
-      <c r="AA19" s="48"/>
-      <c r="AB19" s="48"/>
-      <c r="AC19" s="48"/>
-      <c r="AD19" s="48"/>
-      <c r="AE19" s="48"/>
-      <c r="AF19" s="48"/>
-      <c r="AG19" s="48"/>
-      <c r="AH19" s="48"/>
-      <c r="AI19" s="48"/>
-      <c r="AJ19" s="48"/>
-      <c r="AK19" s="48"/>
-      <c r="AL19" s="48"/>
+      <c r="B19" s="57"/>
+      <c r="C19" s="57"/>
+      <c r="D19" s="57"/>
+      <c r="E19" s="57"/>
+      <c r="F19" s="57"/>
+      <c r="G19" s="57"/>
+      <c r="H19" s="57"/>
+      <c r="I19" s="57"/>
+      <c r="J19" s="57"/>
+      <c r="K19" s="57"/>
+      <c r="L19" s="57"/>
+      <c r="M19" s="57"/>
+      <c r="N19" s="57"/>
+      <c r="O19" s="57"/>
+      <c r="P19" s="57"/>
+      <c r="Q19" s="57"/>
+      <c r="R19" s="57"/>
+      <c r="S19" s="57"/>
+      <c r="T19" s="57"/>
+      <c r="U19" s="57"/>
+      <c r="V19" s="57"/>
+      <c r="W19" s="57"/>
+      <c r="X19" s="57"/>
+      <c r="Y19" s="57"/>
+      <c r="Z19" s="57"/>
+      <c r="AA19" s="57"/>
+      <c r="AB19" s="57"/>
+      <c r="AC19" s="57"/>
+      <c r="AD19" s="57"/>
+      <c r="AE19" s="57"/>
+      <c r="AF19" s="57"/>
+      <c r="AG19" s="57"/>
+      <c r="AH19" s="57"/>
+      <c r="AI19" s="57"/>
+      <c r="AJ19" s="57"/>
+      <c r="AK19" s="57"/>
+      <c r="AL19" s="57"/>
     </row>
     <row r="20" spans="1:38" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
@@ -11451,10 +11451,10 @@
       </c>
     </row>
     <row r="31" spans="1:38" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="49" t="s">
+      <c r="A31" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="B31" s="49"/>
+      <c r="B31" s="58"/>
       <c r="C31" s="11">
         <f t="shared" ref="C31:H31" si="8">SUM(C21:C30)</f>
         <v>15300000</v>
@@ -11513,86 +11513,86 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:35" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="49" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
-      <c r="L1" s="50"/>
-      <c r="M1" s="50"/>
-      <c r="N1" s="50"/>
-      <c r="O1" s="50"/>
-      <c r="P1" s="50"/>
-      <c r="Q1" s="50"/>
-      <c r="R1" s="50"/>
-      <c r="S1" s="50"/>
-      <c r="T1" s="50"/>
-      <c r="U1" s="50"/>
-      <c r="V1" s="50"/>
-      <c r="W1" s="50"/>
-      <c r="X1" s="50"/>
-      <c r="Y1" s="50"/>
-      <c r="Z1" s="50"/>
-      <c r="AA1" s="50"/>
-      <c r="AB1" s="50"/>
-      <c r="AC1" s="50"/>
-      <c r="AD1" s="50"/>
-      <c r="AE1" s="50"/>
-      <c r="AF1" s="50"/>
-      <c r="AG1" s="50"/>
-      <c r="AH1" s="50"/>
-      <c r="AI1" s="50"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
+      <c r="M1" s="49"/>
+      <c r="N1" s="49"/>
+      <c r="O1" s="49"/>
+      <c r="P1" s="49"/>
+      <c r="Q1" s="49"/>
+      <c r="R1" s="49"/>
+      <c r="S1" s="49"/>
+      <c r="T1" s="49"/>
+      <c r="U1" s="49"/>
+      <c r="V1" s="49"/>
+      <c r="W1" s="49"/>
+      <c r="X1" s="49"/>
+      <c r="Y1" s="49"/>
+      <c r="Z1" s="49"/>
+      <c r="AA1" s="49"/>
+      <c r="AB1" s="49"/>
+      <c r="AC1" s="49"/>
+      <c r="AD1" s="49"/>
+      <c r="AE1" s="49"/>
+      <c r="AF1" s="49"/>
+      <c r="AG1" s="49"/>
+      <c r="AH1" s="49"/>
+      <c r="AI1" s="49"/>
     </row>
     <row r="2" spans="1:35" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="59" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="51"/>
-      <c r="J2" s="51"/>
-      <c r="K2" s="51"/>
-      <c r="L2" s="51"/>
-      <c r="M2" s="51"/>
-      <c r="N2" s="51"/>
-      <c r="O2" s="51"/>
-      <c r="P2" s="51"/>
-      <c r="Q2" s="51"/>
-      <c r="R2" s="51"/>
-      <c r="S2" s="51"/>
-      <c r="T2" s="51"/>
-      <c r="U2" s="51"/>
-      <c r="V2" s="51"/>
-      <c r="W2" s="51"/>
-      <c r="X2" s="51"/>
-      <c r="Y2" s="51"/>
-      <c r="Z2" s="51"/>
-      <c r="AA2" s="51"/>
-      <c r="AB2" s="51"/>
-      <c r="AC2" s="51"/>
-      <c r="AD2" s="51"/>
-      <c r="AE2" s="51"/>
-      <c r="AF2" s="51"/>
-      <c r="AG2" s="51"/>
-      <c r="AH2" s="51"/>
-      <c r="AI2" s="51"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="59"/>
+      <c r="L2" s="59"/>
+      <c r="M2" s="59"/>
+      <c r="N2" s="59"/>
+      <c r="O2" s="59"/>
+      <c r="P2" s="59"/>
+      <c r="Q2" s="59"/>
+      <c r="R2" s="59"/>
+      <c r="S2" s="59"/>
+      <c r="T2" s="59"/>
+      <c r="U2" s="59"/>
+      <c r="V2" s="59"/>
+      <c r="W2" s="59"/>
+      <c r="X2" s="59"/>
+      <c r="Y2" s="59"/>
+      <c r="Z2" s="59"/>
+      <c r="AA2" s="59"/>
+      <c r="AB2" s="59"/>
+      <c r="AC2" s="59"/>
+      <c r="AD2" s="59"/>
+      <c r="AE2" s="59"/>
+      <c r="AF2" s="59"/>
+      <c r="AG2" s="59"/>
+      <c r="AH2" s="59"/>
+      <c r="AI2" s="59"/>
     </row>
     <row r="3" spans="1:35" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:35" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="60" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="29" t="s">
@@ -11679,27 +11679,27 @@
       <c r="AC4" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="AD4" s="53" t="s">
+      <c r="AD4" s="61" t="s">
         <v>54</v>
       </c>
-      <c r="AE4" s="54" t="s">
+      <c r="AE4" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="AF4" s="55" t="s">
+      <c r="AF4" s="63" t="s">
         <v>56</v>
       </c>
-      <c r="AG4" s="56" t="s">
+      <c r="AG4" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="AH4" s="57" t="s">
+      <c r="AH4" s="65" t="s">
         <v>58</v>
       </c>
-      <c r="AI4" s="56" t="s">
+      <c r="AI4" s="64" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:35" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="52"/>
+      <c r="A5" s="60"/>
       <c r="B5" s="31">
         <v>1</v>
       </c>
@@ -11784,12 +11784,12 @@
       <c r="AC5" s="31">
         <v>28</v>
       </c>
-      <c r="AD5" s="53"/>
-      <c r="AE5" s="53"/>
-      <c r="AF5" s="53"/>
-      <c r="AG5" s="53"/>
-      <c r="AH5" s="53"/>
-      <c r="AI5" s="53"/>
+      <c r="AD5" s="61"/>
+      <c r="AE5" s="61"/>
+      <c r="AF5" s="61"/>
+      <c r="AG5" s="61"/>
+      <c r="AH5" s="61"/>
+      <c r="AI5" s="61"/>
     </row>
     <row r="6" spans="1:35" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="1:35" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -12512,43 +12512,43 @@
     </row>
     <row r="18" spans="1:35" ht="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="1:35" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="48" t="s">
+      <c r="A19" s="57" t="s">
         <v>70</v>
       </c>
-      <c r="B19" s="48"/>
-      <c r="C19" s="48"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="48"/>
-      <c r="F19" s="48"/>
-      <c r="G19" s="48"/>
-      <c r="H19" s="48"/>
-      <c r="I19" s="48"/>
-      <c r="J19" s="48"/>
-      <c r="K19" s="48"/>
-      <c r="L19" s="48"/>
-      <c r="M19" s="48"/>
-      <c r="N19" s="48"/>
-      <c r="O19" s="48"/>
-      <c r="P19" s="48"/>
-      <c r="Q19" s="48"/>
-      <c r="R19" s="48"/>
-      <c r="S19" s="48"/>
-      <c r="T19" s="48"/>
-      <c r="U19" s="48"/>
-      <c r="V19" s="48"/>
-      <c r="W19" s="48"/>
-      <c r="X19" s="48"/>
-      <c r="Y19" s="48"/>
-      <c r="Z19" s="48"/>
-      <c r="AA19" s="48"/>
-      <c r="AB19" s="48"/>
-      <c r="AC19" s="48"/>
-      <c r="AD19" s="48"/>
-      <c r="AE19" s="48"/>
-      <c r="AF19" s="48"/>
-      <c r="AG19" s="48"/>
-      <c r="AH19" s="48"/>
-      <c r="AI19" s="48"/>
+      <c r="B19" s="57"/>
+      <c r="C19" s="57"/>
+      <c r="D19" s="57"/>
+      <c r="E19" s="57"/>
+      <c r="F19" s="57"/>
+      <c r="G19" s="57"/>
+      <c r="H19" s="57"/>
+      <c r="I19" s="57"/>
+      <c r="J19" s="57"/>
+      <c r="K19" s="57"/>
+      <c r="L19" s="57"/>
+      <c r="M19" s="57"/>
+      <c r="N19" s="57"/>
+      <c r="O19" s="57"/>
+      <c r="P19" s="57"/>
+      <c r="Q19" s="57"/>
+      <c r="R19" s="57"/>
+      <c r="S19" s="57"/>
+      <c r="T19" s="57"/>
+      <c r="U19" s="57"/>
+      <c r="V19" s="57"/>
+      <c r="W19" s="57"/>
+      <c r="X19" s="57"/>
+      <c r="Y19" s="57"/>
+      <c r="Z19" s="57"/>
+      <c r="AA19" s="57"/>
+      <c r="AB19" s="57"/>
+      <c r="AC19" s="57"/>
+      <c r="AD19" s="57"/>
+      <c r="AE19" s="57"/>
+      <c r="AF19" s="57"/>
+      <c r="AG19" s="57"/>
+      <c r="AH19" s="57"/>
+      <c r="AI19" s="57"/>
     </row>
     <row r="20" spans="1:35" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
@@ -12907,10 +12907,10 @@
       </c>
     </row>
     <row r="31" spans="1:35" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="49" t="s">
+      <c r="A31" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="B31" s="49"/>
+      <c r="B31" s="58"/>
       <c r="C31" s="11">
         <f t="shared" ref="C31:H31" si="8">SUM(C21:C30)</f>
         <v>15300000</v>
@@ -12969,92 +12969,92 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="49" t="s">
         <v>71</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
-      <c r="L1" s="50"/>
-      <c r="M1" s="50"/>
-      <c r="N1" s="50"/>
-      <c r="O1" s="50"/>
-      <c r="P1" s="50"/>
-      <c r="Q1" s="50"/>
-      <c r="R1" s="50"/>
-      <c r="S1" s="50"/>
-      <c r="T1" s="50"/>
-      <c r="U1" s="50"/>
-      <c r="V1" s="50"/>
-      <c r="W1" s="50"/>
-      <c r="X1" s="50"/>
-      <c r="Y1" s="50"/>
-      <c r="Z1" s="50"/>
-      <c r="AA1" s="50"/>
-      <c r="AB1" s="50"/>
-      <c r="AC1" s="50"/>
-      <c r="AD1" s="50"/>
-      <c r="AE1" s="50"/>
-      <c r="AF1" s="50"/>
-      <c r="AG1" s="50"/>
-      <c r="AH1" s="50"/>
-      <c r="AI1" s="50"/>
-      <c r="AJ1" s="50"/>
-      <c r="AK1" s="50"/>
-      <c r="AL1" s="50"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
+      <c r="M1" s="49"/>
+      <c r="N1" s="49"/>
+      <c r="O1" s="49"/>
+      <c r="P1" s="49"/>
+      <c r="Q1" s="49"/>
+      <c r="R1" s="49"/>
+      <c r="S1" s="49"/>
+      <c r="T1" s="49"/>
+      <c r="U1" s="49"/>
+      <c r="V1" s="49"/>
+      <c r="W1" s="49"/>
+      <c r="X1" s="49"/>
+      <c r="Y1" s="49"/>
+      <c r="Z1" s="49"/>
+      <c r="AA1" s="49"/>
+      <c r="AB1" s="49"/>
+      <c r="AC1" s="49"/>
+      <c r="AD1" s="49"/>
+      <c r="AE1" s="49"/>
+      <c r="AF1" s="49"/>
+      <c r="AG1" s="49"/>
+      <c r="AH1" s="49"/>
+      <c r="AI1" s="49"/>
+      <c r="AJ1" s="49"/>
+      <c r="AK1" s="49"/>
+      <c r="AL1" s="49"/>
     </row>
     <row r="2" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="59" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="51"/>
-      <c r="J2" s="51"/>
-      <c r="K2" s="51"/>
-      <c r="L2" s="51"/>
-      <c r="M2" s="51"/>
-      <c r="N2" s="51"/>
-      <c r="O2" s="51"/>
-      <c r="P2" s="51"/>
-      <c r="Q2" s="51"/>
-      <c r="R2" s="51"/>
-      <c r="S2" s="51"/>
-      <c r="T2" s="51"/>
-      <c r="U2" s="51"/>
-      <c r="V2" s="51"/>
-      <c r="W2" s="51"/>
-      <c r="X2" s="51"/>
-      <c r="Y2" s="51"/>
-      <c r="Z2" s="51"/>
-      <c r="AA2" s="51"/>
-      <c r="AB2" s="51"/>
-      <c r="AC2" s="51"/>
-      <c r="AD2" s="51"/>
-      <c r="AE2" s="51"/>
-      <c r="AF2" s="51"/>
-      <c r="AG2" s="51"/>
-      <c r="AH2" s="51"/>
-      <c r="AI2" s="51"/>
-      <c r="AJ2" s="51"/>
-      <c r="AK2" s="51"/>
-      <c r="AL2" s="51"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="59"/>
+      <c r="L2" s="59"/>
+      <c r="M2" s="59"/>
+      <c r="N2" s="59"/>
+      <c r="O2" s="59"/>
+      <c r="P2" s="59"/>
+      <c r="Q2" s="59"/>
+      <c r="R2" s="59"/>
+      <c r="S2" s="59"/>
+      <c r="T2" s="59"/>
+      <c r="U2" s="59"/>
+      <c r="V2" s="59"/>
+      <c r="W2" s="59"/>
+      <c r="X2" s="59"/>
+      <c r="Y2" s="59"/>
+      <c r="Z2" s="59"/>
+      <c r="AA2" s="59"/>
+      <c r="AB2" s="59"/>
+      <c r="AC2" s="59"/>
+      <c r="AD2" s="59"/>
+      <c r="AE2" s="59"/>
+      <c r="AF2" s="59"/>
+      <c r="AG2" s="59"/>
+      <c r="AH2" s="59"/>
+      <c r="AI2" s="59"/>
+      <c r="AJ2" s="59"/>
+      <c r="AK2" s="59"/>
+      <c r="AL2" s="59"/>
     </row>
     <row r="3" spans="1:38" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="60" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="29" t="s">
@@ -13150,27 +13150,27 @@
       <c r="AF4" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="AG4" s="53" t="s">
+      <c r="AG4" s="61" t="s">
         <v>54</v>
       </c>
-      <c r="AH4" s="54" t="s">
+      <c r="AH4" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="AI4" s="55" t="s">
+      <c r="AI4" s="63" t="s">
         <v>56</v>
       </c>
-      <c r="AJ4" s="56" t="s">
+      <c r="AJ4" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="AK4" s="57" t="s">
+      <c r="AK4" s="65" t="s">
         <v>58</v>
       </c>
-      <c r="AL4" s="56" t="s">
+      <c r="AL4" s="64" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:38" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="52"/>
+      <c r="A5" s="60"/>
       <c r="B5" s="31">
         <v>1</v>
       </c>
@@ -13264,12 +13264,12 @@
       <c r="AF5" s="31">
         <v>31</v>
       </c>
-      <c r="AG5" s="53"/>
-      <c r="AH5" s="53"/>
-      <c r="AI5" s="53"/>
-      <c r="AJ5" s="53"/>
-      <c r="AK5" s="53"/>
-      <c r="AL5" s="53"/>
+      <c r="AG5" s="61"/>
+      <c r="AH5" s="61"/>
+      <c r="AI5" s="61"/>
+      <c r="AJ5" s="61"/>
+      <c r="AK5" s="61"/>
+      <c r="AL5" s="61"/>
     </row>
     <row r="6" spans="1:38" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="1:38" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -14034,46 +14034,46 @@
     </row>
     <row r="18" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="1:38" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="48" t="s">
+      <c r="A19" s="57" t="s">
         <v>73</v>
       </c>
-      <c r="B19" s="48"/>
-      <c r="C19" s="48"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="48"/>
-      <c r="F19" s="48"/>
-      <c r="G19" s="48"/>
-      <c r="H19" s="48"/>
-      <c r="I19" s="48"/>
-      <c r="J19" s="48"/>
-      <c r="K19" s="48"/>
-      <c r="L19" s="48"/>
-      <c r="M19" s="48"/>
-      <c r="N19" s="48"/>
-      <c r="O19" s="48"/>
-      <c r="P19" s="48"/>
-      <c r="Q19" s="48"/>
-      <c r="R19" s="48"/>
-      <c r="S19" s="48"/>
-      <c r="T19" s="48"/>
-      <c r="U19" s="48"/>
-      <c r="V19" s="48"/>
-      <c r="W19" s="48"/>
-      <c r="X19" s="48"/>
-      <c r="Y19" s="48"/>
-      <c r="Z19" s="48"/>
-      <c r="AA19" s="48"/>
-      <c r="AB19" s="48"/>
-      <c r="AC19" s="48"/>
-      <c r="AD19" s="48"/>
-      <c r="AE19" s="48"/>
-      <c r="AF19" s="48"/>
-      <c r="AG19" s="48"/>
-      <c r="AH19" s="48"/>
-      <c r="AI19" s="48"/>
-      <c r="AJ19" s="48"/>
-      <c r="AK19" s="48"/>
-      <c r="AL19" s="48"/>
+      <c r="B19" s="57"/>
+      <c r="C19" s="57"/>
+      <c r="D19" s="57"/>
+      <c r="E19" s="57"/>
+      <c r="F19" s="57"/>
+      <c r="G19" s="57"/>
+      <c r="H19" s="57"/>
+      <c r="I19" s="57"/>
+      <c r="J19" s="57"/>
+      <c r="K19" s="57"/>
+      <c r="L19" s="57"/>
+      <c r="M19" s="57"/>
+      <c r="N19" s="57"/>
+      <c r="O19" s="57"/>
+      <c r="P19" s="57"/>
+      <c r="Q19" s="57"/>
+      <c r="R19" s="57"/>
+      <c r="S19" s="57"/>
+      <c r="T19" s="57"/>
+      <c r="U19" s="57"/>
+      <c r="V19" s="57"/>
+      <c r="W19" s="57"/>
+      <c r="X19" s="57"/>
+      <c r="Y19" s="57"/>
+      <c r="Z19" s="57"/>
+      <c r="AA19" s="57"/>
+      <c r="AB19" s="57"/>
+      <c r="AC19" s="57"/>
+      <c r="AD19" s="57"/>
+      <c r="AE19" s="57"/>
+      <c r="AF19" s="57"/>
+      <c r="AG19" s="57"/>
+      <c r="AH19" s="57"/>
+      <c r="AI19" s="57"/>
+      <c r="AJ19" s="57"/>
+      <c r="AK19" s="57"/>
+      <c r="AL19" s="57"/>
     </row>
     <row r="20" spans="1:38" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
@@ -14432,10 +14432,10 @@
       </c>
     </row>
     <row r="31" spans="1:38" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="49" t="s">
+      <c r="A31" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="B31" s="49"/>
+      <c r="B31" s="58"/>
       <c r="C31" s="11">
         <f t="shared" ref="C31:H31" si="8">SUM(C21:C30)</f>
         <v>15300000</v>
@@ -14494,90 +14494,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
-      <c r="L1" s="50"/>
-      <c r="M1" s="50"/>
-      <c r="N1" s="50"/>
-      <c r="O1" s="50"/>
-      <c r="P1" s="50"/>
-      <c r="Q1" s="50"/>
-      <c r="R1" s="50"/>
-      <c r="S1" s="50"/>
-      <c r="T1" s="50"/>
-      <c r="U1" s="50"/>
-      <c r="V1" s="50"/>
-      <c r="W1" s="50"/>
-      <c r="X1" s="50"/>
-      <c r="Y1" s="50"/>
-      <c r="Z1" s="50"/>
-      <c r="AA1" s="50"/>
-      <c r="AB1" s="50"/>
-      <c r="AC1" s="50"/>
-      <c r="AD1" s="50"/>
-      <c r="AE1" s="50"/>
-      <c r="AF1" s="50"/>
-      <c r="AG1" s="50"/>
-      <c r="AH1" s="50"/>
-      <c r="AI1" s="50"/>
-      <c r="AJ1" s="50"/>
-      <c r="AK1" s="50"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
+      <c r="M1" s="49"/>
+      <c r="N1" s="49"/>
+      <c r="O1" s="49"/>
+      <c r="P1" s="49"/>
+      <c r="Q1" s="49"/>
+      <c r="R1" s="49"/>
+      <c r="S1" s="49"/>
+      <c r="T1" s="49"/>
+      <c r="U1" s="49"/>
+      <c r="V1" s="49"/>
+      <c r="W1" s="49"/>
+      <c r="X1" s="49"/>
+      <c r="Y1" s="49"/>
+      <c r="Z1" s="49"/>
+      <c r="AA1" s="49"/>
+      <c r="AB1" s="49"/>
+      <c r="AC1" s="49"/>
+      <c r="AD1" s="49"/>
+      <c r="AE1" s="49"/>
+      <c r="AF1" s="49"/>
+      <c r="AG1" s="49"/>
+      <c r="AH1" s="49"/>
+      <c r="AI1" s="49"/>
+      <c r="AJ1" s="49"/>
+      <c r="AK1" s="49"/>
     </row>
     <row r="2" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="59" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="51"/>
-      <c r="J2" s="51"/>
-      <c r="K2" s="51"/>
-      <c r="L2" s="51"/>
-      <c r="M2" s="51"/>
-      <c r="N2" s="51"/>
-      <c r="O2" s="51"/>
-      <c r="P2" s="51"/>
-      <c r="Q2" s="51"/>
-      <c r="R2" s="51"/>
-      <c r="S2" s="51"/>
-      <c r="T2" s="51"/>
-      <c r="U2" s="51"/>
-      <c r="V2" s="51"/>
-      <c r="W2" s="51"/>
-      <c r="X2" s="51"/>
-      <c r="Y2" s="51"/>
-      <c r="Z2" s="51"/>
-      <c r="AA2" s="51"/>
-      <c r="AB2" s="51"/>
-      <c r="AC2" s="51"/>
-      <c r="AD2" s="51"/>
-      <c r="AE2" s="51"/>
-      <c r="AF2" s="51"/>
-      <c r="AG2" s="51"/>
-      <c r="AH2" s="51"/>
-      <c r="AI2" s="51"/>
-      <c r="AJ2" s="51"/>
-      <c r="AK2" s="51"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="59"/>
+      <c r="L2" s="59"/>
+      <c r="M2" s="59"/>
+      <c r="N2" s="59"/>
+      <c r="O2" s="59"/>
+      <c r="P2" s="59"/>
+      <c r="Q2" s="59"/>
+      <c r="R2" s="59"/>
+      <c r="S2" s="59"/>
+      <c r="T2" s="59"/>
+      <c r="U2" s="59"/>
+      <c r="V2" s="59"/>
+      <c r="W2" s="59"/>
+      <c r="X2" s="59"/>
+      <c r="Y2" s="59"/>
+      <c r="Z2" s="59"/>
+      <c r="AA2" s="59"/>
+      <c r="AB2" s="59"/>
+      <c r="AC2" s="59"/>
+      <c r="AD2" s="59"/>
+      <c r="AE2" s="59"/>
+      <c r="AF2" s="59"/>
+      <c r="AG2" s="59"/>
+      <c r="AH2" s="59"/>
+      <c r="AI2" s="59"/>
+      <c r="AJ2" s="59"/>
+      <c r="AK2" s="59"/>
     </row>
     <row r="3" spans="1:37" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:37" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="60" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="29" t="s">
@@ -14670,27 +14670,27 @@
       <c r="AE4" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="AF4" s="53" t="s">
+      <c r="AF4" s="61" t="s">
         <v>54</v>
       </c>
-      <c r="AG4" s="54" t="s">
+      <c r="AG4" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="AH4" s="55" t="s">
+      <c r="AH4" s="63" t="s">
         <v>56</v>
       </c>
-      <c r="AI4" s="56" t="s">
+      <c r="AI4" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="AJ4" s="57" t="s">
+      <c r="AJ4" s="65" t="s">
         <v>58</v>
       </c>
-      <c r="AK4" s="56" t="s">
+      <c r="AK4" s="64" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:37" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="52"/>
+      <c r="A5" s="60"/>
       <c r="B5" s="31">
         <v>1</v>
       </c>
@@ -14781,12 +14781,12 @@
       <c r="AE5" s="31">
         <v>30</v>
       </c>
-      <c r="AF5" s="53"/>
-      <c r="AG5" s="53"/>
-      <c r="AH5" s="53"/>
-      <c r="AI5" s="53"/>
-      <c r="AJ5" s="53"/>
-      <c r="AK5" s="53"/>
+      <c r="AF5" s="61"/>
+      <c r="AG5" s="61"/>
+      <c r="AH5" s="61"/>
+      <c r="AI5" s="61"/>
+      <c r="AJ5" s="61"/>
+      <c r="AK5" s="61"/>
     </row>
     <row r="6" spans="1:37" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="1:37" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -15537,45 +15537,45 @@
     </row>
     <row r="18" spans="1:37" ht="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="1:37" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="48" t="s">
+      <c r="A19" s="57" t="s">
         <v>76</v>
       </c>
-      <c r="B19" s="48"/>
-      <c r="C19" s="48"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="48"/>
-      <c r="F19" s="48"/>
-      <c r="G19" s="48"/>
-      <c r="H19" s="48"/>
-      <c r="I19" s="48"/>
-      <c r="J19" s="48"/>
-      <c r="K19" s="48"/>
-      <c r="L19" s="48"/>
-      <c r="M19" s="48"/>
-      <c r="N19" s="48"/>
-      <c r="O19" s="48"/>
-      <c r="P19" s="48"/>
-      <c r="Q19" s="48"/>
-      <c r="R19" s="48"/>
-      <c r="S19" s="48"/>
-      <c r="T19" s="48"/>
-      <c r="U19" s="48"/>
-      <c r="V19" s="48"/>
-      <c r="W19" s="48"/>
-      <c r="X19" s="48"/>
-      <c r="Y19" s="48"/>
-      <c r="Z19" s="48"/>
-      <c r="AA19" s="48"/>
-      <c r="AB19" s="48"/>
-      <c r="AC19" s="48"/>
-      <c r="AD19" s="48"/>
-      <c r="AE19" s="48"/>
-      <c r="AF19" s="48"/>
-      <c r="AG19" s="48"/>
-      <c r="AH19" s="48"/>
-      <c r="AI19" s="48"/>
-      <c r="AJ19" s="48"/>
-      <c r="AK19" s="48"/>
+      <c r="B19" s="57"/>
+      <c r="C19" s="57"/>
+      <c r="D19" s="57"/>
+      <c r="E19" s="57"/>
+      <c r="F19" s="57"/>
+      <c r="G19" s="57"/>
+      <c r="H19" s="57"/>
+      <c r="I19" s="57"/>
+      <c r="J19" s="57"/>
+      <c r="K19" s="57"/>
+      <c r="L19" s="57"/>
+      <c r="M19" s="57"/>
+      <c r="N19" s="57"/>
+      <c r="O19" s="57"/>
+      <c r="P19" s="57"/>
+      <c r="Q19" s="57"/>
+      <c r="R19" s="57"/>
+      <c r="S19" s="57"/>
+      <c r="T19" s="57"/>
+      <c r="U19" s="57"/>
+      <c r="V19" s="57"/>
+      <c r="W19" s="57"/>
+      <c r="X19" s="57"/>
+      <c r="Y19" s="57"/>
+      <c r="Z19" s="57"/>
+      <c r="AA19" s="57"/>
+      <c r="AB19" s="57"/>
+      <c r="AC19" s="57"/>
+      <c r="AD19" s="57"/>
+      <c r="AE19" s="57"/>
+      <c r="AF19" s="57"/>
+      <c r="AG19" s="57"/>
+      <c r="AH19" s="57"/>
+      <c r="AI19" s="57"/>
+      <c r="AJ19" s="57"/>
+      <c r="AK19" s="57"/>
     </row>
     <row r="20" spans="1:37" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
@@ -15934,10 +15934,10 @@
       </c>
     </row>
     <row r="31" spans="1:37" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="49" t="s">
+      <c r="A31" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="B31" s="49"/>
+      <c r="B31" s="58"/>
       <c r="C31" s="11">
         <f t="shared" ref="C31:H31" si="8">SUM(C21:C30)</f>
         <v>15300000</v>
@@ -15996,92 +15996,92 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="49" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
-      <c r="L1" s="50"/>
-      <c r="M1" s="50"/>
-      <c r="N1" s="50"/>
-      <c r="O1" s="50"/>
-      <c r="P1" s="50"/>
-      <c r="Q1" s="50"/>
-      <c r="R1" s="50"/>
-      <c r="S1" s="50"/>
-      <c r="T1" s="50"/>
-      <c r="U1" s="50"/>
-      <c r="V1" s="50"/>
-      <c r="W1" s="50"/>
-      <c r="X1" s="50"/>
-      <c r="Y1" s="50"/>
-      <c r="Z1" s="50"/>
-      <c r="AA1" s="50"/>
-      <c r="AB1" s="50"/>
-      <c r="AC1" s="50"/>
-      <c r="AD1" s="50"/>
-      <c r="AE1" s="50"/>
-      <c r="AF1" s="50"/>
-      <c r="AG1" s="50"/>
-      <c r="AH1" s="50"/>
-      <c r="AI1" s="50"/>
-      <c r="AJ1" s="50"/>
-      <c r="AK1" s="50"/>
-      <c r="AL1" s="50"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
+      <c r="M1" s="49"/>
+      <c r="N1" s="49"/>
+      <c r="O1" s="49"/>
+      <c r="P1" s="49"/>
+      <c r="Q1" s="49"/>
+      <c r="R1" s="49"/>
+      <c r="S1" s="49"/>
+      <c r="T1" s="49"/>
+      <c r="U1" s="49"/>
+      <c r="V1" s="49"/>
+      <c r="W1" s="49"/>
+      <c r="X1" s="49"/>
+      <c r="Y1" s="49"/>
+      <c r="Z1" s="49"/>
+      <c r="AA1" s="49"/>
+      <c r="AB1" s="49"/>
+      <c r="AC1" s="49"/>
+      <c r="AD1" s="49"/>
+      <c r="AE1" s="49"/>
+      <c r="AF1" s="49"/>
+      <c r="AG1" s="49"/>
+      <c r="AH1" s="49"/>
+      <c r="AI1" s="49"/>
+      <c r="AJ1" s="49"/>
+      <c r="AK1" s="49"/>
+      <c r="AL1" s="49"/>
     </row>
     <row r="2" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="59" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="51"/>
-      <c r="J2" s="51"/>
-      <c r="K2" s="51"/>
-      <c r="L2" s="51"/>
-      <c r="M2" s="51"/>
-      <c r="N2" s="51"/>
-      <c r="O2" s="51"/>
-      <c r="P2" s="51"/>
-      <c r="Q2" s="51"/>
-      <c r="R2" s="51"/>
-      <c r="S2" s="51"/>
-      <c r="T2" s="51"/>
-      <c r="U2" s="51"/>
-      <c r="V2" s="51"/>
-      <c r="W2" s="51"/>
-      <c r="X2" s="51"/>
-      <c r="Y2" s="51"/>
-      <c r="Z2" s="51"/>
-      <c r="AA2" s="51"/>
-      <c r="AB2" s="51"/>
-      <c r="AC2" s="51"/>
-      <c r="AD2" s="51"/>
-      <c r="AE2" s="51"/>
-      <c r="AF2" s="51"/>
-      <c r="AG2" s="51"/>
-      <c r="AH2" s="51"/>
-      <c r="AI2" s="51"/>
-      <c r="AJ2" s="51"/>
-      <c r="AK2" s="51"/>
-      <c r="AL2" s="51"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="59"/>
+      <c r="L2" s="59"/>
+      <c r="M2" s="59"/>
+      <c r="N2" s="59"/>
+      <c r="O2" s="59"/>
+      <c r="P2" s="59"/>
+      <c r="Q2" s="59"/>
+      <c r="R2" s="59"/>
+      <c r="S2" s="59"/>
+      <c r="T2" s="59"/>
+      <c r="U2" s="59"/>
+      <c r="V2" s="59"/>
+      <c r="W2" s="59"/>
+      <c r="X2" s="59"/>
+      <c r="Y2" s="59"/>
+      <c r="Z2" s="59"/>
+      <c r="AA2" s="59"/>
+      <c r="AB2" s="59"/>
+      <c r="AC2" s="59"/>
+      <c r="AD2" s="59"/>
+      <c r="AE2" s="59"/>
+      <c r="AF2" s="59"/>
+      <c r="AG2" s="59"/>
+      <c r="AH2" s="59"/>
+      <c r="AI2" s="59"/>
+      <c r="AJ2" s="59"/>
+      <c r="AK2" s="59"/>
+      <c r="AL2" s="59"/>
     </row>
     <row r="3" spans="1:38" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="60" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="30" t="s">
@@ -16177,27 +16177,27 @@
       <c r="AF4" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="AG4" s="53" t="s">
+      <c r="AG4" s="61" t="s">
         <v>54</v>
       </c>
-      <c r="AH4" s="54" t="s">
+      <c r="AH4" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="AI4" s="55" t="s">
+      <c r="AI4" s="63" t="s">
         <v>56</v>
       </c>
-      <c r="AJ4" s="56" t="s">
+      <c r="AJ4" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="AK4" s="57" t="s">
+      <c r="AK4" s="65" t="s">
         <v>58</v>
       </c>
-      <c r="AL4" s="56" t="s">
+      <c r="AL4" s="64" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:38" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="52"/>
+      <c r="A5" s="60"/>
       <c r="B5" s="32">
         <v>1</v>
       </c>
@@ -16291,12 +16291,12 @@
       <c r="AF5" s="31">
         <v>31</v>
       </c>
-      <c r="AG5" s="53"/>
-      <c r="AH5" s="53"/>
-      <c r="AI5" s="53"/>
-      <c r="AJ5" s="53"/>
-      <c r="AK5" s="53"/>
-      <c r="AL5" s="53"/>
+      <c r="AG5" s="61"/>
+      <c r="AH5" s="61"/>
+      <c r="AI5" s="61"/>
+      <c r="AJ5" s="61"/>
+      <c r="AK5" s="61"/>
+      <c r="AL5" s="61"/>
     </row>
     <row r="6" spans="1:38" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="1:38" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -17061,46 +17061,46 @@
     </row>
     <row r="18" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="1:38" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="48" t="s">
+      <c r="A19" s="57" t="s">
         <v>79</v>
       </c>
-      <c r="B19" s="48"/>
-      <c r="C19" s="48"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="48"/>
-      <c r="F19" s="48"/>
-      <c r="G19" s="48"/>
-      <c r="H19" s="48"/>
-      <c r="I19" s="48"/>
-      <c r="J19" s="48"/>
-      <c r="K19" s="48"/>
-      <c r="L19" s="48"/>
-      <c r="M19" s="48"/>
-      <c r="N19" s="48"/>
-      <c r="O19" s="48"/>
-      <c r="P19" s="48"/>
-      <c r="Q19" s="48"/>
-      <c r="R19" s="48"/>
-      <c r="S19" s="48"/>
-      <c r="T19" s="48"/>
-      <c r="U19" s="48"/>
-      <c r="V19" s="48"/>
-      <c r="W19" s="48"/>
-      <c r="X19" s="48"/>
-      <c r="Y19" s="48"/>
-      <c r="Z19" s="48"/>
-      <c r="AA19" s="48"/>
-      <c r="AB19" s="48"/>
-      <c r="AC19" s="48"/>
-      <c r="AD19" s="48"/>
-      <c r="AE19" s="48"/>
-      <c r="AF19" s="48"/>
-      <c r="AG19" s="48"/>
-      <c r="AH19" s="48"/>
-      <c r="AI19" s="48"/>
-      <c r="AJ19" s="48"/>
-      <c r="AK19" s="48"/>
-      <c r="AL19" s="48"/>
+      <c r="B19" s="57"/>
+      <c r="C19" s="57"/>
+      <c r="D19" s="57"/>
+      <c r="E19" s="57"/>
+      <c r="F19" s="57"/>
+      <c r="G19" s="57"/>
+      <c r="H19" s="57"/>
+      <c r="I19" s="57"/>
+      <c r="J19" s="57"/>
+      <c r="K19" s="57"/>
+      <c r="L19" s="57"/>
+      <c r="M19" s="57"/>
+      <c r="N19" s="57"/>
+      <c r="O19" s="57"/>
+      <c r="P19" s="57"/>
+      <c r="Q19" s="57"/>
+      <c r="R19" s="57"/>
+      <c r="S19" s="57"/>
+      <c r="T19" s="57"/>
+      <c r="U19" s="57"/>
+      <c r="V19" s="57"/>
+      <c r="W19" s="57"/>
+      <c r="X19" s="57"/>
+      <c r="Y19" s="57"/>
+      <c r="Z19" s="57"/>
+      <c r="AA19" s="57"/>
+      <c r="AB19" s="57"/>
+      <c r="AC19" s="57"/>
+      <c r="AD19" s="57"/>
+      <c r="AE19" s="57"/>
+      <c r="AF19" s="57"/>
+      <c r="AG19" s="57"/>
+      <c r="AH19" s="57"/>
+      <c r="AI19" s="57"/>
+      <c r="AJ19" s="57"/>
+      <c r="AK19" s="57"/>
+      <c r="AL19" s="57"/>
     </row>
     <row r="20" spans="1:38" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
@@ -17459,10 +17459,10 @@
       </c>
     </row>
     <row r="31" spans="1:38" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="49" t="s">
+      <c r="A31" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="B31" s="49"/>
+      <c r="B31" s="58"/>
       <c r="C31" s="11">
         <f t="shared" ref="C31:H31" si="8">SUM(C21:C30)</f>
         <v>15300000</v>
@@ -17525,90 +17525,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="49" t="s">
         <v>80</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
-      <c r="L1" s="50"/>
-      <c r="M1" s="50"/>
-      <c r="N1" s="50"/>
-      <c r="O1" s="50"/>
-      <c r="P1" s="50"/>
-      <c r="Q1" s="50"/>
-      <c r="R1" s="50"/>
-      <c r="S1" s="50"/>
-      <c r="T1" s="50"/>
-      <c r="U1" s="50"/>
-      <c r="V1" s="50"/>
-      <c r="W1" s="50"/>
-      <c r="X1" s="50"/>
-      <c r="Y1" s="50"/>
-      <c r="Z1" s="50"/>
-      <c r="AA1" s="50"/>
-      <c r="AB1" s="50"/>
-      <c r="AC1" s="50"/>
-      <c r="AD1" s="50"/>
-      <c r="AE1" s="50"/>
-      <c r="AF1" s="50"/>
-      <c r="AG1" s="50"/>
-      <c r="AH1" s="50"/>
-      <c r="AI1" s="50"/>
-      <c r="AJ1" s="50"/>
-      <c r="AK1" s="50"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
+      <c r="M1" s="49"/>
+      <c r="N1" s="49"/>
+      <c r="O1" s="49"/>
+      <c r="P1" s="49"/>
+      <c r="Q1" s="49"/>
+      <c r="R1" s="49"/>
+      <c r="S1" s="49"/>
+      <c r="T1" s="49"/>
+      <c r="U1" s="49"/>
+      <c r="V1" s="49"/>
+      <c r="W1" s="49"/>
+      <c r="X1" s="49"/>
+      <c r="Y1" s="49"/>
+      <c r="Z1" s="49"/>
+      <c r="AA1" s="49"/>
+      <c r="AB1" s="49"/>
+      <c r="AC1" s="49"/>
+      <c r="AD1" s="49"/>
+      <c r="AE1" s="49"/>
+      <c r="AF1" s="49"/>
+      <c r="AG1" s="49"/>
+      <c r="AH1" s="49"/>
+      <c r="AI1" s="49"/>
+      <c r="AJ1" s="49"/>
+      <c r="AK1" s="49"/>
     </row>
     <row r="2" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="59" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="51"/>
-      <c r="J2" s="51"/>
-      <c r="K2" s="51"/>
-      <c r="L2" s="51"/>
-      <c r="M2" s="51"/>
-      <c r="N2" s="51"/>
-      <c r="O2" s="51"/>
-      <c r="P2" s="51"/>
-      <c r="Q2" s="51"/>
-      <c r="R2" s="51"/>
-      <c r="S2" s="51"/>
-      <c r="T2" s="51"/>
-      <c r="U2" s="51"/>
-      <c r="V2" s="51"/>
-      <c r="W2" s="51"/>
-      <c r="X2" s="51"/>
-      <c r="Y2" s="51"/>
-      <c r="Z2" s="51"/>
-      <c r="AA2" s="51"/>
-      <c r="AB2" s="51"/>
-      <c r="AC2" s="51"/>
-      <c r="AD2" s="51"/>
-      <c r="AE2" s="51"/>
-      <c r="AF2" s="51"/>
-      <c r="AG2" s="51"/>
-      <c r="AH2" s="51"/>
-      <c r="AI2" s="51"/>
-      <c r="AJ2" s="51"/>
-      <c r="AK2" s="51"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="59"/>
+      <c r="L2" s="59"/>
+      <c r="M2" s="59"/>
+      <c r="N2" s="59"/>
+      <c r="O2" s="59"/>
+      <c r="P2" s="59"/>
+      <c r="Q2" s="59"/>
+      <c r="R2" s="59"/>
+      <c r="S2" s="59"/>
+      <c r="T2" s="59"/>
+      <c r="U2" s="59"/>
+      <c r="V2" s="59"/>
+      <c r="W2" s="59"/>
+      <c r="X2" s="59"/>
+      <c r="Y2" s="59"/>
+      <c r="Z2" s="59"/>
+      <c r="AA2" s="59"/>
+      <c r="AB2" s="59"/>
+      <c r="AC2" s="59"/>
+      <c r="AD2" s="59"/>
+      <c r="AE2" s="59"/>
+      <c r="AF2" s="59"/>
+      <c r="AG2" s="59"/>
+      <c r="AH2" s="59"/>
+      <c r="AI2" s="59"/>
+      <c r="AJ2" s="59"/>
+      <c r="AK2" s="59"/>
     </row>
     <row r="3" spans="1:37" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:37" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="60" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="29" t="s">
@@ -17701,27 +17701,27 @@
       <c r="AE4" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="AF4" s="53" t="s">
+      <c r="AF4" s="61" t="s">
         <v>54</v>
       </c>
-      <c r="AG4" s="54" t="s">
+      <c r="AG4" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="AH4" s="55" t="s">
+      <c r="AH4" s="63" t="s">
         <v>56</v>
       </c>
-      <c r="AI4" s="56" t="s">
+      <c r="AI4" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="AJ4" s="57" t="s">
+      <c r="AJ4" s="65" t="s">
         <v>58</v>
       </c>
-      <c r="AK4" s="56" t="s">
+      <c r="AK4" s="64" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:37" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="52"/>
+      <c r="A5" s="60"/>
       <c r="B5" s="31">
         <v>1</v>
       </c>
@@ -17812,12 +17812,12 @@
       <c r="AE5" s="31">
         <v>30</v>
       </c>
-      <c r="AF5" s="53"/>
-      <c r="AG5" s="53"/>
-      <c r="AH5" s="53"/>
-      <c r="AI5" s="53"/>
-      <c r="AJ5" s="53"/>
-      <c r="AK5" s="53"/>
+      <c r="AF5" s="61"/>
+      <c r="AG5" s="61"/>
+      <c r="AH5" s="61"/>
+      <c r="AI5" s="61"/>
+      <c r="AJ5" s="61"/>
+      <c r="AK5" s="61"/>
     </row>
     <row r="6" spans="1:37" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="1:37" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -18676,45 +18676,45 @@
     </row>
     <row r="18" spans="1:37" ht="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="1:37" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="48" t="s">
+      <c r="A19" s="57" t="s">
         <v>82</v>
       </c>
-      <c r="B19" s="48"/>
-      <c r="C19" s="48"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="48"/>
-      <c r="F19" s="48"/>
-      <c r="G19" s="48"/>
-      <c r="H19" s="48"/>
-      <c r="I19" s="48"/>
-      <c r="J19" s="48"/>
-      <c r="K19" s="48"/>
-      <c r="L19" s="48"/>
-      <c r="M19" s="48"/>
-      <c r="N19" s="48"/>
-      <c r="O19" s="48"/>
-      <c r="P19" s="48"/>
-      <c r="Q19" s="48"/>
-      <c r="R19" s="48"/>
-      <c r="S19" s="48"/>
-      <c r="T19" s="48"/>
-      <c r="U19" s="48"/>
-      <c r="V19" s="48"/>
-      <c r="W19" s="48"/>
-      <c r="X19" s="48"/>
-      <c r="Y19" s="48"/>
-      <c r="Z19" s="48"/>
-      <c r="AA19" s="48"/>
-      <c r="AB19" s="48"/>
-      <c r="AC19" s="48"/>
-      <c r="AD19" s="48"/>
-      <c r="AE19" s="48"/>
-      <c r="AF19" s="48"/>
-      <c r="AG19" s="48"/>
-      <c r="AH19" s="48"/>
-      <c r="AI19" s="48"/>
-      <c r="AJ19" s="48"/>
-      <c r="AK19" s="48"/>
+      <c r="B19" s="57"/>
+      <c r="C19" s="57"/>
+      <c r="D19" s="57"/>
+      <c r="E19" s="57"/>
+      <c r="F19" s="57"/>
+      <c r="G19" s="57"/>
+      <c r="H19" s="57"/>
+      <c r="I19" s="57"/>
+      <c r="J19" s="57"/>
+      <c r="K19" s="57"/>
+      <c r="L19" s="57"/>
+      <c r="M19" s="57"/>
+      <c r="N19" s="57"/>
+      <c r="O19" s="57"/>
+      <c r="P19" s="57"/>
+      <c r="Q19" s="57"/>
+      <c r="R19" s="57"/>
+      <c r="S19" s="57"/>
+      <c r="T19" s="57"/>
+      <c r="U19" s="57"/>
+      <c r="V19" s="57"/>
+      <c r="W19" s="57"/>
+      <c r="X19" s="57"/>
+      <c r="Y19" s="57"/>
+      <c r="Z19" s="57"/>
+      <c r="AA19" s="57"/>
+      <c r="AB19" s="57"/>
+      <c r="AC19" s="57"/>
+      <c r="AD19" s="57"/>
+      <c r="AE19" s="57"/>
+      <c r="AF19" s="57"/>
+      <c r="AG19" s="57"/>
+      <c r="AH19" s="57"/>
+      <c r="AI19" s="57"/>
+      <c r="AJ19" s="57"/>
+      <c r="AK19" s="57"/>
     </row>
     <row r="20" spans="1:37" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
@@ -19073,10 +19073,10 @@
       </c>
     </row>
     <row r="31" spans="1:37" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="49" t="s">
+      <c r="A31" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="B31" s="49"/>
+      <c r="B31" s="58"/>
       <c r="C31" s="11">
         <f t="shared" ref="C31:H31" si="8">SUM(C21:C30)</f>
         <v>15300000</v>
@@ -19135,92 +19135,92 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
-      <c r="L1" s="50"/>
-      <c r="M1" s="50"/>
-      <c r="N1" s="50"/>
-      <c r="O1" s="50"/>
-      <c r="P1" s="50"/>
-      <c r="Q1" s="50"/>
-      <c r="R1" s="50"/>
-      <c r="S1" s="50"/>
-      <c r="T1" s="50"/>
-      <c r="U1" s="50"/>
-      <c r="V1" s="50"/>
-      <c r="W1" s="50"/>
-      <c r="X1" s="50"/>
-      <c r="Y1" s="50"/>
-      <c r="Z1" s="50"/>
-      <c r="AA1" s="50"/>
-      <c r="AB1" s="50"/>
-      <c r="AC1" s="50"/>
-      <c r="AD1" s="50"/>
-      <c r="AE1" s="50"/>
-      <c r="AF1" s="50"/>
-      <c r="AG1" s="50"/>
-      <c r="AH1" s="50"/>
-      <c r="AI1" s="50"/>
-      <c r="AJ1" s="50"/>
-      <c r="AK1" s="50"/>
-      <c r="AL1" s="50"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
+      <c r="M1" s="49"/>
+      <c r="N1" s="49"/>
+      <c r="O1" s="49"/>
+      <c r="P1" s="49"/>
+      <c r="Q1" s="49"/>
+      <c r="R1" s="49"/>
+      <c r="S1" s="49"/>
+      <c r="T1" s="49"/>
+      <c r="U1" s="49"/>
+      <c r="V1" s="49"/>
+      <c r="W1" s="49"/>
+      <c r="X1" s="49"/>
+      <c r="Y1" s="49"/>
+      <c r="Z1" s="49"/>
+      <c r="AA1" s="49"/>
+      <c r="AB1" s="49"/>
+      <c r="AC1" s="49"/>
+      <c r="AD1" s="49"/>
+      <c r="AE1" s="49"/>
+      <c r="AF1" s="49"/>
+      <c r="AG1" s="49"/>
+      <c r="AH1" s="49"/>
+      <c r="AI1" s="49"/>
+      <c r="AJ1" s="49"/>
+      <c r="AK1" s="49"/>
+      <c r="AL1" s="49"/>
     </row>
     <row r="2" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="59" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="51"/>
-      <c r="J2" s="51"/>
-      <c r="K2" s="51"/>
-      <c r="L2" s="51"/>
-      <c r="M2" s="51"/>
-      <c r="N2" s="51"/>
-      <c r="O2" s="51"/>
-      <c r="P2" s="51"/>
-      <c r="Q2" s="51"/>
-      <c r="R2" s="51"/>
-      <c r="S2" s="51"/>
-      <c r="T2" s="51"/>
-      <c r="U2" s="51"/>
-      <c r="V2" s="51"/>
-      <c r="W2" s="51"/>
-      <c r="X2" s="51"/>
-      <c r="Y2" s="51"/>
-      <c r="Z2" s="51"/>
-      <c r="AA2" s="51"/>
-      <c r="AB2" s="51"/>
-      <c r="AC2" s="51"/>
-      <c r="AD2" s="51"/>
-      <c r="AE2" s="51"/>
-      <c r="AF2" s="51"/>
-      <c r="AG2" s="51"/>
-      <c r="AH2" s="51"/>
-      <c r="AI2" s="51"/>
-      <c r="AJ2" s="51"/>
-      <c r="AK2" s="51"/>
-      <c r="AL2" s="51"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="59"/>
+      <c r="L2" s="59"/>
+      <c r="M2" s="59"/>
+      <c r="N2" s="59"/>
+      <c r="O2" s="59"/>
+      <c r="P2" s="59"/>
+      <c r="Q2" s="59"/>
+      <c r="R2" s="59"/>
+      <c r="S2" s="59"/>
+      <c r="T2" s="59"/>
+      <c r="U2" s="59"/>
+      <c r="V2" s="59"/>
+      <c r="W2" s="59"/>
+      <c r="X2" s="59"/>
+      <c r="Y2" s="59"/>
+      <c r="Z2" s="59"/>
+      <c r="AA2" s="59"/>
+      <c r="AB2" s="59"/>
+      <c r="AC2" s="59"/>
+      <c r="AD2" s="59"/>
+      <c r="AE2" s="59"/>
+      <c r="AF2" s="59"/>
+      <c r="AG2" s="59"/>
+      <c r="AH2" s="59"/>
+      <c r="AI2" s="59"/>
+      <c r="AJ2" s="59"/>
+      <c r="AK2" s="59"/>
+      <c r="AL2" s="59"/>
     </row>
     <row r="3" spans="1:38" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="60" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="29" t="s">
@@ -19316,27 +19316,27 @@
       <c r="AF4" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="AG4" s="53" t="s">
+      <c r="AG4" s="61" t="s">
         <v>54</v>
       </c>
-      <c r="AH4" s="54" t="s">
+      <c r="AH4" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="AI4" s="55" t="s">
+      <c r="AI4" s="63" t="s">
         <v>56</v>
       </c>
-      <c r="AJ4" s="56" t="s">
+      <c r="AJ4" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="AK4" s="57" t="s">
+      <c r="AK4" s="65" t="s">
         <v>58</v>
       </c>
-      <c r="AL4" s="56" t="s">
+      <c r="AL4" s="64" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:38" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="52"/>
+      <c r="A5" s="60"/>
       <c r="B5" s="31">
         <v>1</v>
       </c>
@@ -19430,12 +19430,12 @@
       <c r="AF5" s="32">
         <v>31</v>
       </c>
-      <c r="AG5" s="53"/>
-      <c r="AH5" s="53"/>
-      <c r="AI5" s="53"/>
-      <c r="AJ5" s="53"/>
-      <c r="AK5" s="53"/>
-      <c r="AL5" s="53"/>
+      <c r="AG5" s="61"/>
+      <c r="AH5" s="61"/>
+      <c r="AI5" s="61"/>
+      <c r="AJ5" s="61"/>
+      <c r="AK5" s="61"/>
+      <c r="AL5" s="61"/>
     </row>
     <row r="6" spans="1:38" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="1:38" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -20200,46 +20200,46 @@
     </row>
     <row r="18" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="1:38" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="48" t="s">
+      <c r="A19" s="57" t="s">
         <v>85</v>
       </c>
-      <c r="B19" s="48"/>
-      <c r="C19" s="48"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="48"/>
-      <c r="F19" s="48"/>
-      <c r="G19" s="48"/>
-      <c r="H19" s="48"/>
-      <c r="I19" s="48"/>
-      <c r="J19" s="48"/>
-      <c r="K19" s="48"/>
-      <c r="L19" s="48"/>
-      <c r="M19" s="48"/>
-      <c r="N19" s="48"/>
-      <c r="O19" s="48"/>
-      <c r="P19" s="48"/>
-      <c r="Q19" s="48"/>
-      <c r="R19" s="48"/>
-      <c r="S19" s="48"/>
-      <c r="T19" s="48"/>
-      <c r="U19" s="48"/>
-      <c r="V19" s="48"/>
-      <c r="W19" s="48"/>
-      <c r="X19" s="48"/>
-      <c r="Y19" s="48"/>
-      <c r="Z19" s="48"/>
-      <c r="AA19" s="48"/>
-      <c r="AB19" s="48"/>
-      <c r="AC19" s="48"/>
-      <c r="AD19" s="48"/>
-      <c r="AE19" s="48"/>
-      <c r="AF19" s="48"/>
-      <c r="AG19" s="48"/>
-      <c r="AH19" s="48"/>
-      <c r="AI19" s="48"/>
-      <c r="AJ19" s="48"/>
-      <c r="AK19" s="48"/>
-      <c r="AL19" s="48"/>
+      <c r="B19" s="57"/>
+      <c r="C19" s="57"/>
+      <c r="D19" s="57"/>
+      <c r="E19" s="57"/>
+      <c r="F19" s="57"/>
+      <c r="G19" s="57"/>
+      <c r="H19" s="57"/>
+      <c r="I19" s="57"/>
+      <c r="J19" s="57"/>
+      <c r="K19" s="57"/>
+      <c r="L19" s="57"/>
+      <c r="M19" s="57"/>
+      <c r="N19" s="57"/>
+      <c r="O19" s="57"/>
+      <c r="P19" s="57"/>
+      <c r="Q19" s="57"/>
+      <c r="R19" s="57"/>
+      <c r="S19" s="57"/>
+      <c r="T19" s="57"/>
+      <c r="U19" s="57"/>
+      <c r="V19" s="57"/>
+      <c r="W19" s="57"/>
+      <c r="X19" s="57"/>
+      <c r="Y19" s="57"/>
+      <c r="Z19" s="57"/>
+      <c r="AA19" s="57"/>
+      <c r="AB19" s="57"/>
+      <c r="AC19" s="57"/>
+      <c r="AD19" s="57"/>
+      <c r="AE19" s="57"/>
+      <c r="AF19" s="57"/>
+      <c r="AG19" s="57"/>
+      <c r="AH19" s="57"/>
+      <c r="AI19" s="57"/>
+      <c r="AJ19" s="57"/>
+      <c r="AK19" s="57"/>
+      <c r="AL19" s="57"/>
     </row>
     <row r="20" spans="1:38" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
@@ -20598,10 +20598,10 @@
       </c>
     </row>
     <row r="31" spans="1:38" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="49" t="s">
+      <c r="A31" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="B31" s="49"/>
+      <c r="B31" s="58"/>
       <c r="C31" s="11">
         <f t="shared" ref="C31:H31" si="8">SUM(C21:C30)</f>
         <v>15300000</v>

--- a/ضبط_رواتب_الموظفين.xlsx
+++ b/ضبط_رواتب_الموظفين.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DeLL\Desktop\ملفات خاصة بالمعمل ووظائفه\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CB11E48-F832-4424-87CF-1D5291CCEFA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E71CCEFA-02BA-442B-B2A6-E831F6111005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="الملخص السنوي" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="706" uniqueCount="102">
   <si>
     <t>الملخص السنوي الشامل — 2026</t>
   </si>
@@ -370,6 +370,9 @@
   </si>
   <si>
     <t>📊  الملخص الشهري للرواتب — ديسمبر  2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -897,37 +900,13 @@
     <xf numFmtId="1" fontId="11" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="32" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -949,6 +928,30 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1227,46 +1230,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="54" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="54"/>
-      <c r="K1" s="54"/>
-      <c r="L1" s="54"/>
-      <c r="M1" s="54"/>
-      <c r="N1" s="54"/>
-      <c r="O1" s="54"/>
-      <c r="P1" s="54"/>
-      <c r="Q1" s="54"/>
+      <c r="A1" s="58" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
+      <c r="H1" s="58"/>
+      <c r="I1" s="58"/>
+      <c r="J1" s="58"/>
+      <c r="K1" s="58"/>
+      <c r="L1" s="58"/>
+      <c r="M1" s="58"/>
+      <c r="N1" s="58"/>
+      <c r="O1" s="58"/>
+      <c r="P1" s="58"/>
+      <c r="Q1" s="58"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="55" t="s">
+      <c r="A2" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
-      <c r="L2" s="55"/>
-      <c r="M2" s="55"/>
-      <c r="N2" s="55"/>
-      <c r="O2" s="55"/>
-      <c r="P2" s="55"/>
-      <c r="Q2" s="55"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="59"/>
+      <c r="L2" s="59"/>
+      <c r="M2" s="59"/>
+      <c r="N2" s="59"/>
+      <c r="O2" s="59"/>
+      <c r="P2" s="59"/>
+      <c r="Q2" s="59"/>
     </row>
     <row r="3" spans="1:17" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:17" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1360,7 +1363,7 @@
       </c>
       <c r="J5" s="5">
         <f>IF(ISNUMBER(يوليو!AL7),يوليو!AL7,"")</f>
-        <v>7233333.3300000001</v>
+        <v>6781720.4299999997</v>
       </c>
       <c r="K5" s="5">
         <f>IF(ISNUMBER(أغسطس!AL7),أغسطس!AL7,"")</f>
@@ -1384,11 +1387,11 @@
       </c>
       <c r="P5" s="6">
         <f>IF(ISNUMBER(يناير!AK7),يناير!AK7,0)+IF(ISNUMBER(فبراير!AH7),فبراير!AH7,0)+IF(ISNUMBER(مارس!AK7),مارس!AK7,0)+IF(ISNUMBER(أبريل!AJ7),أبريل!AJ7,0)+IF(ISNUMBER(مايو!AK7),مايو!AK7,0)+IF(ISNUMBER(يونيو!AJ7),يونيو!AJ7,0)+IF(ISNUMBER(يوليو!AK7),يوليو!AK7,0)+IF(ISNUMBER(أغسطس!AK7),أغسطس!AK7,0)+IF(ISNUMBER(سبتمبر!AJ7),سبتمبر!AJ7,0)+IF(ISNUMBER(أكتوبر!AK7),أكتوبر!AK7,0)+IF(ISNUMBER(نوفمبر!AJ7),نوفمبر!AJ7,0)+IF(ISNUMBER(ديسمبر!AK7),ديسمبر!AK7,0)</f>
-        <v>700000</v>
+        <v>1151612.8999999999</v>
       </c>
       <c r="Q5" s="7">
         <f t="shared" ref="Q5:Q14" si="0">IFERROR(SUM(D5:O5),"")</f>
-        <v>84933333.310000002</v>
+        <v>84481720.409999996</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -1498,7 +1501,7 @@
       </c>
       <c r="J7" s="5">
         <f>IF(ISNUMBER(يوليو!AL9),يوليو!AL9,"")</f>
-        <v>2583333.33</v>
+        <v>2578853.04</v>
       </c>
       <c r="K7" s="5">
         <f>IF(ISNUMBER(أغسطس!AL9),أغسطس!AL9,"")</f>
@@ -1526,7 +1529,7 @@
       </c>
       <c r="Q7" s="7">
         <f t="shared" si="0"/>
-        <v>30384259.229999997</v>
+        <v>30379778.939999998</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -1567,7 +1570,7 @@
       </c>
       <c r="J8" s="10">
         <f>IF(ISNUMBER(يوليو!AL10),يوليو!AL10,"")</f>
-        <v>826666.67</v>
+        <v>829534.05</v>
       </c>
       <c r="K8" s="10">
         <f>IF(ISNUMBER(أغسطس!AL10),أغسطس!AL10,"")</f>
@@ -1595,7 +1598,7 @@
       </c>
       <c r="Q8" s="7">
         <f t="shared" si="0"/>
-        <v>9459259.2799999993</v>
+        <v>9462126.6599999983</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -1636,7 +1639,7 @@
       </c>
       <c r="J9" s="5">
         <f>IF(ISNUMBER(يوليو!AL11),يوليو!AL11,"")</f>
-        <v>2066666.67</v>
+        <v>2052329.75</v>
       </c>
       <c r="K9" s="5">
         <f>IF(ISNUMBER(أغسطس!AL11),أغسطس!AL11,"")</f>
@@ -1664,7 +1667,7 @@
       </c>
       <c r="Q9" s="7">
         <f t="shared" si="0"/>
-        <v>22974074.090000004</v>
+        <v>22959737.170000002</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -2013,10 +2016,10 @@
       </c>
     </row>
     <row r="15" spans="1:17" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="56" t="s">
+      <c r="A15" s="60" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="56"/>
+      <c r="B15" s="60"/>
       <c r="C15" s="11">
         <f t="shared" ref="C15:Q15" si="1">IFERROR(SUM(C5:C14),0)</f>
         <v>15300000</v>
@@ -2047,7 +2050,7 @@
       </c>
       <c r="J15" s="11">
         <f t="shared" si="1"/>
-        <v>15810000</v>
+        <v>15342437.27</v>
       </c>
       <c r="K15" s="11">
         <f t="shared" si="1"/>
@@ -2071,11 +2074,11 @@
       </c>
       <c r="P15" s="12">
         <f t="shared" si="1"/>
-        <v>2853333.34</v>
+        <v>3304946.2399999998</v>
       </c>
       <c r="Q15" s="12">
         <f t="shared" si="1"/>
-        <v>184289814.80000001</v>
+        <v>183822252.06999999</v>
       </c>
     </row>
   </sheetData>
@@ -2103,92 +2106,92 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
-      <c r="L1" s="49"/>
-      <c r="M1" s="49"/>
-      <c r="N1" s="49"/>
-      <c r="O1" s="49"/>
-      <c r="P1" s="49"/>
-      <c r="Q1" s="49"/>
-      <c r="R1" s="49"/>
-      <c r="S1" s="49"/>
-      <c r="T1" s="49"/>
-      <c r="U1" s="49"/>
-      <c r="V1" s="49"/>
-      <c r="W1" s="49"/>
-      <c r="X1" s="49"/>
-      <c r="Y1" s="49"/>
-      <c r="Z1" s="49"/>
-      <c r="AA1" s="49"/>
-      <c r="AB1" s="49"/>
-      <c r="AC1" s="49"/>
-      <c r="AD1" s="49"/>
-      <c r="AE1" s="49"/>
-      <c r="AF1" s="49"/>
-      <c r="AG1" s="49"/>
-      <c r="AH1" s="49"/>
-      <c r="AI1" s="49"/>
-      <c r="AJ1" s="49"/>
-      <c r="AK1" s="49"/>
-      <c r="AL1" s="49"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="50"/>
+      <c r="M1" s="50"/>
+      <c r="N1" s="50"/>
+      <c r="O1" s="50"/>
+      <c r="P1" s="50"/>
+      <c r="Q1" s="50"/>
+      <c r="R1" s="50"/>
+      <c r="S1" s="50"/>
+      <c r="T1" s="50"/>
+      <c r="U1" s="50"/>
+      <c r="V1" s="50"/>
+      <c r="W1" s="50"/>
+      <c r="X1" s="50"/>
+      <c r="Y1" s="50"/>
+      <c r="Z1" s="50"/>
+      <c r="AA1" s="50"/>
+      <c r="AB1" s="50"/>
+      <c r="AC1" s="50"/>
+      <c r="AD1" s="50"/>
+      <c r="AE1" s="50"/>
+      <c r="AF1" s="50"/>
+      <c r="AG1" s="50"/>
+      <c r="AH1" s="50"/>
+      <c r="AI1" s="50"/>
+      <c r="AJ1" s="50"/>
+      <c r="AK1" s="50"/>
+      <c r="AL1" s="50"/>
     </row>
     <row r="2" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="59" t="s">
+      <c r="A2" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="59"/>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="59"/>
-      <c r="H2" s="59"/>
-      <c r="I2" s="59"/>
-      <c r="J2" s="59"/>
-      <c r="K2" s="59"/>
-      <c r="L2" s="59"/>
-      <c r="M2" s="59"/>
-      <c r="N2" s="59"/>
-      <c r="O2" s="59"/>
-      <c r="P2" s="59"/>
-      <c r="Q2" s="59"/>
-      <c r="R2" s="59"/>
-      <c r="S2" s="59"/>
-      <c r="T2" s="59"/>
-      <c r="U2" s="59"/>
-      <c r="V2" s="59"/>
-      <c r="W2" s="59"/>
-      <c r="X2" s="59"/>
-      <c r="Y2" s="59"/>
-      <c r="Z2" s="59"/>
-      <c r="AA2" s="59"/>
-      <c r="AB2" s="59"/>
-      <c r="AC2" s="59"/>
-      <c r="AD2" s="59"/>
-      <c r="AE2" s="59"/>
-      <c r="AF2" s="59"/>
-      <c r="AG2" s="59"/>
-      <c r="AH2" s="59"/>
-      <c r="AI2" s="59"/>
-      <c r="AJ2" s="59"/>
-      <c r="AK2" s="59"/>
-      <c r="AL2" s="59"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="51"/>
+      <c r="K2" s="51"/>
+      <c r="L2" s="51"/>
+      <c r="M2" s="51"/>
+      <c r="N2" s="51"/>
+      <c r="O2" s="51"/>
+      <c r="P2" s="51"/>
+      <c r="Q2" s="51"/>
+      <c r="R2" s="51"/>
+      <c r="S2" s="51"/>
+      <c r="T2" s="51"/>
+      <c r="U2" s="51"/>
+      <c r="V2" s="51"/>
+      <c r="W2" s="51"/>
+      <c r="X2" s="51"/>
+      <c r="Y2" s="51"/>
+      <c r="Z2" s="51"/>
+      <c r="AA2" s="51"/>
+      <c r="AB2" s="51"/>
+      <c r="AC2" s="51"/>
+      <c r="AD2" s="51"/>
+      <c r="AE2" s="51"/>
+      <c r="AF2" s="51"/>
+      <c r="AG2" s="51"/>
+      <c r="AH2" s="51"/>
+      <c r="AI2" s="51"/>
+      <c r="AJ2" s="51"/>
+      <c r="AK2" s="51"/>
+      <c r="AL2" s="51"/>
     </row>
     <row r="3" spans="1:38" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="60" t="s">
+      <c r="A4" s="52" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="29" t="s">
@@ -2284,27 +2287,27 @@
       <c r="AF4" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="AG4" s="61" t="s">
+      <c r="AG4" s="53" t="s">
         <v>54</v>
       </c>
-      <c r="AH4" s="62" t="s">
+      <c r="AH4" s="54" t="s">
         <v>55</v>
       </c>
-      <c r="AI4" s="63" t="s">
+      <c r="AI4" s="55" t="s">
         <v>56</v>
       </c>
-      <c r="AJ4" s="64" t="s">
+      <c r="AJ4" s="56" t="s">
         <v>57</v>
       </c>
-      <c r="AK4" s="65" t="s">
+      <c r="AK4" s="57" t="s">
         <v>58</v>
       </c>
-      <c r="AL4" s="64" t="s">
+      <c r="AL4" s="56" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:38" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="60"/>
+      <c r="A5" s="52"/>
       <c r="B5" s="31">
         <v>1</v>
       </c>
@@ -2398,12 +2401,12 @@
       <c r="AF5" s="31">
         <v>31</v>
       </c>
-      <c r="AG5" s="61"/>
-      <c r="AH5" s="61"/>
-      <c r="AI5" s="61"/>
-      <c r="AJ5" s="61"/>
-      <c r="AK5" s="61"/>
-      <c r="AL5" s="61"/>
+      <c r="AG5" s="53"/>
+      <c r="AH5" s="53"/>
+      <c r="AI5" s="53"/>
+      <c r="AJ5" s="53"/>
+      <c r="AK5" s="53"/>
+      <c r="AL5" s="53"/>
     </row>
     <row r="6" spans="1:38" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="1:38" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3168,46 +3171,46 @@
     </row>
     <row r="18" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="1:38" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="57" t="s">
+      <c r="A19" s="48" t="s">
         <v>88</v>
       </c>
-      <c r="B19" s="57"/>
-      <c r="C19" s="57"/>
-      <c r="D19" s="57"/>
-      <c r="E19" s="57"/>
-      <c r="F19" s="57"/>
-      <c r="G19" s="57"/>
-      <c r="H19" s="57"/>
-      <c r="I19" s="57"/>
-      <c r="J19" s="57"/>
-      <c r="K19" s="57"/>
-      <c r="L19" s="57"/>
-      <c r="M19" s="57"/>
-      <c r="N19" s="57"/>
-      <c r="O19" s="57"/>
-      <c r="P19" s="57"/>
-      <c r="Q19" s="57"/>
-      <c r="R19" s="57"/>
-      <c r="S19" s="57"/>
-      <c r="T19" s="57"/>
-      <c r="U19" s="57"/>
-      <c r="V19" s="57"/>
-      <c r="W19" s="57"/>
-      <c r="X19" s="57"/>
-      <c r="Y19" s="57"/>
-      <c r="Z19" s="57"/>
-      <c r="AA19" s="57"/>
-      <c r="AB19" s="57"/>
-      <c r="AC19" s="57"/>
-      <c r="AD19" s="57"/>
-      <c r="AE19" s="57"/>
-      <c r="AF19" s="57"/>
-      <c r="AG19" s="57"/>
-      <c r="AH19" s="57"/>
-      <c r="AI19" s="57"/>
-      <c r="AJ19" s="57"/>
-      <c r="AK19" s="57"/>
-      <c r="AL19" s="57"/>
+      <c r="B19" s="48"/>
+      <c r="C19" s="48"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="48"/>
+      <c r="G19" s="48"/>
+      <c r="H19" s="48"/>
+      <c r="I19" s="48"/>
+      <c r="J19" s="48"/>
+      <c r="K19" s="48"/>
+      <c r="L19" s="48"/>
+      <c r="M19" s="48"/>
+      <c r="N19" s="48"/>
+      <c r="O19" s="48"/>
+      <c r="P19" s="48"/>
+      <c r="Q19" s="48"/>
+      <c r="R19" s="48"/>
+      <c r="S19" s="48"/>
+      <c r="T19" s="48"/>
+      <c r="U19" s="48"/>
+      <c r="V19" s="48"/>
+      <c r="W19" s="48"/>
+      <c r="X19" s="48"/>
+      <c r="Y19" s="48"/>
+      <c r="Z19" s="48"/>
+      <c r="AA19" s="48"/>
+      <c r="AB19" s="48"/>
+      <c r="AC19" s="48"/>
+      <c r="AD19" s="48"/>
+      <c r="AE19" s="48"/>
+      <c r="AF19" s="48"/>
+      <c r="AG19" s="48"/>
+      <c r="AH19" s="48"/>
+      <c r="AI19" s="48"/>
+      <c r="AJ19" s="48"/>
+      <c r="AK19" s="48"/>
+      <c r="AL19" s="48"/>
     </row>
     <row r="20" spans="1:38" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
@@ -3566,10 +3569,10 @@
       </c>
     </row>
     <row r="31" spans="1:38" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="58" t="s">
+      <c r="A31" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="B31" s="58"/>
+      <c r="B31" s="49"/>
       <c r="C31" s="11">
         <f t="shared" ref="C31:H31" si="8">SUM(C21:C30)</f>
         <v>15300000</v>
@@ -3628,90 +3631,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="50" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
-      <c r="L1" s="49"/>
-      <c r="M1" s="49"/>
-      <c r="N1" s="49"/>
-      <c r="O1" s="49"/>
-      <c r="P1" s="49"/>
-      <c r="Q1" s="49"/>
-      <c r="R1" s="49"/>
-      <c r="S1" s="49"/>
-      <c r="T1" s="49"/>
-      <c r="U1" s="49"/>
-      <c r="V1" s="49"/>
-      <c r="W1" s="49"/>
-      <c r="X1" s="49"/>
-      <c r="Y1" s="49"/>
-      <c r="Z1" s="49"/>
-      <c r="AA1" s="49"/>
-      <c r="AB1" s="49"/>
-      <c r="AC1" s="49"/>
-      <c r="AD1" s="49"/>
-      <c r="AE1" s="49"/>
-      <c r="AF1" s="49"/>
-      <c r="AG1" s="49"/>
-      <c r="AH1" s="49"/>
-      <c r="AI1" s="49"/>
-      <c r="AJ1" s="49"/>
-      <c r="AK1" s="49"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="50"/>
+      <c r="M1" s="50"/>
+      <c r="N1" s="50"/>
+      <c r="O1" s="50"/>
+      <c r="P1" s="50"/>
+      <c r="Q1" s="50"/>
+      <c r="R1" s="50"/>
+      <c r="S1" s="50"/>
+      <c r="T1" s="50"/>
+      <c r="U1" s="50"/>
+      <c r="V1" s="50"/>
+      <c r="W1" s="50"/>
+      <c r="X1" s="50"/>
+      <c r="Y1" s="50"/>
+      <c r="Z1" s="50"/>
+      <c r="AA1" s="50"/>
+      <c r="AB1" s="50"/>
+      <c r="AC1" s="50"/>
+      <c r="AD1" s="50"/>
+      <c r="AE1" s="50"/>
+      <c r="AF1" s="50"/>
+      <c r="AG1" s="50"/>
+      <c r="AH1" s="50"/>
+      <c r="AI1" s="50"/>
+      <c r="AJ1" s="50"/>
+      <c r="AK1" s="50"/>
     </row>
     <row r="2" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="59" t="s">
+      <c r="A2" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="59"/>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="59"/>
-      <c r="H2" s="59"/>
-      <c r="I2" s="59"/>
-      <c r="J2" s="59"/>
-      <c r="K2" s="59"/>
-      <c r="L2" s="59"/>
-      <c r="M2" s="59"/>
-      <c r="N2" s="59"/>
-      <c r="O2" s="59"/>
-      <c r="P2" s="59"/>
-      <c r="Q2" s="59"/>
-      <c r="R2" s="59"/>
-      <c r="S2" s="59"/>
-      <c r="T2" s="59"/>
-      <c r="U2" s="59"/>
-      <c r="V2" s="59"/>
-      <c r="W2" s="59"/>
-      <c r="X2" s="59"/>
-      <c r="Y2" s="59"/>
-      <c r="Z2" s="59"/>
-      <c r="AA2" s="59"/>
-      <c r="AB2" s="59"/>
-      <c r="AC2" s="59"/>
-      <c r="AD2" s="59"/>
-      <c r="AE2" s="59"/>
-      <c r="AF2" s="59"/>
-      <c r="AG2" s="59"/>
-      <c r="AH2" s="59"/>
-      <c r="AI2" s="59"/>
-      <c r="AJ2" s="59"/>
-      <c r="AK2" s="59"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="51"/>
+      <c r="K2" s="51"/>
+      <c r="L2" s="51"/>
+      <c r="M2" s="51"/>
+      <c r="N2" s="51"/>
+      <c r="O2" s="51"/>
+      <c r="P2" s="51"/>
+      <c r="Q2" s="51"/>
+      <c r="R2" s="51"/>
+      <c r="S2" s="51"/>
+      <c r="T2" s="51"/>
+      <c r="U2" s="51"/>
+      <c r="V2" s="51"/>
+      <c r="W2" s="51"/>
+      <c r="X2" s="51"/>
+      <c r="Y2" s="51"/>
+      <c r="Z2" s="51"/>
+      <c r="AA2" s="51"/>
+      <c r="AB2" s="51"/>
+      <c r="AC2" s="51"/>
+      <c r="AD2" s="51"/>
+      <c r="AE2" s="51"/>
+      <c r="AF2" s="51"/>
+      <c r="AG2" s="51"/>
+      <c r="AH2" s="51"/>
+      <c r="AI2" s="51"/>
+      <c r="AJ2" s="51"/>
+      <c r="AK2" s="51"/>
     </row>
     <row r="3" spans="1:37" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:37" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="60" t="s">
+      <c r="A4" s="52" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="29" t="s">
@@ -3804,27 +3807,27 @@
       <c r="AE4" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="AF4" s="61" t="s">
+      <c r="AF4" s="53" t="s">
         <v>54</v>
       </c>
-      <c r="AG4" s="62" t="s">
+      <c r="AG4" s="54" t="s">
         <v>55</v>
       </c>
-      <c r="AH4" s="63" t="s">
+      <c r="AH4" s="55" t="s">
         <v>56</v>
       </c>
-      <c r="AI4" s="64" t="s">
+      <c r="AI4" s="56" t="s">
         <v>57</v>
       </c>
-      <c r="AJ4" s="65" t="s">
+      <c r="AJ4" s="57" t="s">
         <v>58</v>
       </c>
-      <c r="AK4" s="64" t="s">
+      <c r="AK4" s="56" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:37" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="60"/>
+      <c r="A5" s="52"/>
       <c r="B5" s="31">
         <v>1</v>
       </c>
@@ -3915,12 +3918,12 @@
       <c r="AE5" s="31">
         <v>30</v>
       </c>
-      <c r="AF5" s="61"/>
-      <c r="AG5" s="61"/>
-      <c r="AH5" s="61"/>
-      <c r="AI5" s="61"/>
-      <c r="AJ5" s="61"/>
-      <c r="AK5" s="61"/>
+      <c r="AF5" s="53"/>
+      <c r="AG5" s="53"/>
+      <c r="AH5" s="53"/>
+      <c r="AI5" s="53"/>
+      <c r="AJ5" s="53"/>
+      <c r="AK5" s="53"/>
     </row>
     <row r="6" spans="1:37" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="1:37" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4671,45 +4674,45 @@
     </row>
     <row r="18" spans="1:37" ht="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="1:37" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="57" t="s">
+      <c r="A19" s="48" t="s">
         <v>91</v>
       </c>
-      <c r="B19" s="57"/>
-      <c r="C19" s="57"/>
-      <c r="D19" s="57"/>
-      <c r="E19" s="57"/>
-      <c r="F19" s="57"/>
-      <c r="G19" s="57"/>
-      <c r="H19" s="57"/>
-      <c r="I19" s="57"/>
-      <c r="J19" s="57"/>
-      <c r="K19" s="57"/>
-      <c r="L19" s="57"/>
-      <c r="M19" s="57"/>
-      <c r="N19" s="57"/>
-      <c r="O19" s="57"/>
-      <c r="P19" s="57"/>
-      <c r="Q19" s="57"/>
-      <c r="R19" s="57"/>
-      <c r="S19" s="57"/>
-      <c r="T19" s="57"/>
-      <c r="U19" s="57"/>
-      <c r="V19" s="57"/>
-      <c r="W19" s="57"/>
-      <c r="X19" s="57"/>
-      <c r="Y19" s="57"/>
-      <c r="Z19" s="57"/>
-      <c r="AA19" s="57"/>
-      <c r="AB19" s="57"/>
-      <c r="AC19" s="57"/>
-      <c r="AD19" s="57"/>
-      <c r="AE19" s="57"/>
-      <c r="AF19" s="57"/>
-      <c r="AG19" s="57"/>
-      <c r="AH19" s="57"/>
-      <c r="AI19" s="57"/>
-      <c r="AJ19" s="57"/>
-      <c r="AK19" s="57"/>
+      <c r="B19" s="48"/>
+      <c r="C19" s="48"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="48"/>
+      <c r="G19" s="48"/>
+      <c r="H19" s="48"/>
+      <c r="I19" s="48"/>
+      <c r="J19" s="48"/>
+      <c r="K19" s="48"/>
+      <c r="L19" s="48"/>
+      <c r="M19" s="48"/>
+      <c r="N19" s="48"/>
+      <c r="O19" s="48"/>
+      <c r="P19" s="48"/>
+      <c r="Q19" s="48"/>
+      <c r="R19" s="48"/>
+      <c r="S19" s="48"/>
+      <c r="T19" s="48"/>
+      <c r="U19" s="48"/>
+      <c r="V19" s="48"/>
+      <c r="W19" s="48"/>
+      <c r="X19" s="48"/>
+      <c r="Y19" s="48"/>
+      <c r="Z19" s="48"/>
+      <c r="AA19" s="48"/>
+      <c r="AB19" s="48"/>
+      <c r="AC19" s="48"/>
+      <c r="AD19" s="48"/>
+      <c r="AE19" s="48"/>
+      <c r="AF19" s="48"/>
+      <c r="AG19" s="48"/>
+      <c r="AH19" s="48"/>
+      <c r="AI19" s="48"/>
+      <c r="AJ19" s="48"/>
+      <c r="AK19" s="48"/>
     </row>
     <row r="20" spans="1:37" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
@@ -5068,10 +5071,10 @@
       </c>
     </row>
     <row r="31" spans="1:37" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="58" t="s">
+      <c r="A31" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="B31" s="58"/>
+      <c r="B31" s="49"/>
       <c r="C31" s="11">
         <f t="shared" ref="C31:H31" si="8">SUM(C21:C30)</f>
         <v>15300000</v>
@@ -5130,92 +5133,92 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="50" t="s">
         <v>92</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
-      <c r="L1" s="49"/>
-      <c r="M1" s="49"/>
-      <c r="N1" s="49"/>
-      <c r="O1" s="49"/>
-      <c r="P1" s="49"/>
-      <c r="Q1" s="49"/>
-      <c r="R1" s="49"/>
-      <c r="S1" s="49"/>
-      <c r="T1" s="49"/>
-      <c r="U1" s="49"/>
-      <c r="V1" s="49"/>
-      <c r="W1" s="49"/>
-      <c r="X1" s="49"/>
-      <c r="Y1" s="49"/>
-      <c r="Z1" s="49"/>
-      <c r="AA1" s="49"/>
-      <c r="AB1" s="49"/>
-      <c r="AC1" s="49"/>
-      <c r="AD1" s="49"/>
-      <c r="AE1" s="49"/>
-      <c r="AF1" s="49"/>
-      <c r="AG1" s="49"/>
-      <c r="AH1" s="49"/>
-      <c r="AI1" s="49"/>
-      <c r="AJ1" s="49"/>
-      <c r="AK1" s="49"/>
-      <c r="AL1" s="49"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="50"/>
+      <c r="M1" s="50"/>
+      <c r="N1" s="50"/>
+      <c r="O1" s="50"/>
+      <c r="P1" s="50"/>
+      <c r="Q1" s="50"/>
+      <c r="R1" s="50"/>
+      <c r="S1" s="50"/>
+      <c r="T1" s="50"/>
+      <c r="U1" s="50"/>
+      <c r="V1" s="50"/>
+      <c r="W1" s="50"/>
+      <c r="X1" s="50"/>
+      <c r="Y1" s="50"/>
+      <c r="Z1" s="50"/>
+      <c r="AA1" s="50"/>
+      <c r="AB1" s="50"/>
+      <c r="AC1" s="50"/>
+      <c r="AD1" s="50"/>
+      <c r="AE1" s="50"/>
+      <c r="AF1" s="50"/>
+      <c r="AG1" s="50"/>
+      <c r="AH1" s="50"/>
+      <c r="AI1" s="50"/>
+      <c r="AJ1" s="50"/>
+      <c r="AK1" s="50"/>
+      <c r="AL1" s="50"/>
     </row>
     <row r="2" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="59" t="s">
+      <c r="A2" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="59"/>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="59"/>
-      <c r="H2" s="59"/>
-      <c r="I2" s="59"/>
-      <c r="J2" s="59"/>
-      <c r="K2" s="59"/>
-      <c r="L2" s="59"/>
-      <c r="M2" s="59"/>
-      <c r="N2" s="59"/>
-      <c r="O2" s="59"/>
-      <c r="P2" s="59"/>
-      <c r="Q2" s="59"/>
-      <c r="R2" s="59"/>
-      <c r="S2" s="59"/>
-      <c r="T2" s="59"/>
-      <c r="U2" s="59"/>
-      <c r="V2" s="59"/>
-      <c r="W2" s="59"/>
-      <c r="X2" s="59"/>
-      <c r="Y2" s="59"/>
-      <c r="Z2" s="59"/>
-      <c r="AA2" s="59"/>
-      <c r="AB2" s="59"/>
-      <c r="AC2" s="59"/>
-      <c r="AD2" s="59"/>
-      <c r="AE2" s="59"/>
-      <c r="AF2" s="59"/>
-      <c r="AG2" s="59"/>
-      <c r="AH2" s="59"/>
-      <c r="AI2" s="59"/>
-      <c r="AJ2" s="59"/>
-      <c r="AK2" s="59"/>
-      <c r="AL2" s="59"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="51"/>
+      <c r="K2" s="51"/>
+      <c r="L2" s="51"/>
+      <c r="M2" s="51"/>
+      <c r="N2" s="51"/>
+      <c r="O2" s="51"/>
+      <c r="P2" s="51"/>
+      <c r="Q2" s="51"/>
+      <c r="R2" s="51"/>
+      <c r="S2" s="51"/>
+      <c r="T2" s="51"/>
+      <c r="U2" s="51"/>
+      <c r="V2" s="51"/>
+      <c r="W2" s="51"/>
+      <c r="X2" s="51"/>
+      <c r="Y2" s="51"/>
+      <c r="Z2" s="51"/>
+      <c r="AA2" s="51"/>
+      <c r="AB2" s="51"/>
+      <c r="AC2" s="51"/>
+      <c r="AD2" s="51"/>
+      <c r="AE2" s="51"/>
+      <c r="AF2" s="51"/>
+      <c r="AG2" s="51"/>
+      <c r="AH2" s="51"/>
+      <c r="AI2" s="51"/>
+      <c r="AJ2" s="51"/>
+      <c r="AK2" s="51"/>
+      <c r="AL2" s="51"/>
     </row>
     <row r="3" spans="1:38" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="60" t="s">
+      <c r="A4" s="52" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="29" t="s">
@@ -5311,27 +5314,27 @@
       <c r="AF4" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="AG4" s="61" t="s">
+      <c r="AG4" s="53" t="s">
         <v>54</v>
       </c>
-      <c r="AH4" s="62" t="s">
+      <c r="AH4" s="54" t="s">
         <v>55</v>
       </c>
-      <c r="AI4" s="63" t="s">
+      <c r="AI4" s="55" t="s">
         <v>56</v>
       </c>
-      <c r="AJ4" s="64" t="s">
+      <c r="AJ4" s="56" t="s">
         <v>57</v>
       </c>
-      <c r="AK4" s="65" t="s">
+      <c r="AK4" s="57" t="s">
         <v>58</v>
       </c>
-      <c r="AL4" s="64" t="s">
+      <c r="AL4" s="56" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:38" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="60"/>
+      <c r="A5" s="52"/>
       <c r="B5" s="31">
         <v>1</v>
       </c>
@@ -5425,12 +5428,12 @@
       <c r="AF5" s="31">
         <v>31</v>
       </c>
-      <c r="AG5" s="61"/>
-      <c r="AH5" s="61"/>
-      <c r="AI5" s="61"/>
-      <c r="AJ5" s="61"/>
-      <c r="AK5" s="61"/>
-      <c r="AL5" s="61"/>
+      <c r="AG5" s="53"/>
+      <c r="AH5" s="53"/>
+      <c r="AI5" s="53"/>
+      <c r="AJ5" s="53"/>
+      <c r="AK5" s="53"/>
+      <c r="AL5" s="53"/>
     </row>
     <row r="6" spans="1:38" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="1:38" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6195,46 +6198,46 @@
     </row>
     <row r="18" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="1:38" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="57" t="s">
+      <c r="A19" s="48" t="s">
         <v>94</v>
       </c>
-      <c r="B19" s="57"/>
-      <c r="C19" s="57"/>
-      <c r="D19" s="57"/>
-      <c r="E19" s="57"/>
-      <c r="F19" s="57"/>
-      <c r="G19" s="57"/>
-      <c r="H19" s="57"/>
-      <c r="I19" s="57"/>
-      <c r="J19" s="57"/>
-      <c r="K19" s="57"/>
-      <c r="L19" s="57"/>
-      <c r="M19" s="57"/>
-      <c r="N19" s="57"/>
-      <c r="O19" s="57"/>
-      <c r="P19" s="57"/>
-      <c r="Q19" s="57"/>
-      <c r="R19" s="57"/>
-      <c r="S19" s="57"/>
-      <c r="T19" s="57"/>
-      <c r="U19" s="57"/>
-      <c r="V19" s="57"/>
-      <c r="W19" s="57"/>
-      <c r="X19" s="57"/>
-      <c r="Y19" s="57"/>
-      <c r="Z19" s="57"/>
-      <c r="AA19" s="57"/>
-      <c r="AB19" s="57"/>
-      <c r="AC19" s="57"/>
-      <c r="AD19" s="57"/>
-      <c r="AE19" s="57"/>
-      <c r="AF19" s="57"/>
-      <c r="AG19" s="57"/>
-      <c r="AH19" s="57"/>
-      <c r="AI19" s="57"/>
-      <c r="AJ19" s="57"/>
-      <c r="AK19" s="57"/>
-      <c r="AL19" s="57"/>
+      <c r="B19" s="48"/>
+      <c r="C19" s="48"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="48"/>
+      <c r="G19" s="48"/>
+      <c r="H19" s="48"/>
+      <c r="I19" s="48"/>
+      <c r="J19" s="48"/>
+      <c r="K19" s="48"/>
+      <c r="L19" s="48"/>
+      <c r="M19" s="48"/>
+      <c r="N19" s="48"/>
+      <c r="O19" s="48"/>
+      <c r="P19" s="48"/>
+      <c r="Q19" s="48"/>
+      <c r="R19" s="48"/>
+      <c r="S19" s="48"/>
+      <c r="T19" s="48"/>
+      <c r="U19" s="48"/>
+      <c r="V19" s="48"/>
+      <c r="W19" s="48"/>
+      <c r="X19" s="48"/>
+      <c r="Y19" s="48"/>
+      <c r="Z19" s="48"/>
+      <c r="AA19" s="48"/>
+      <c r="AB19" s="48"/>
+      <c r="AC19" s="48"/>
+      <c r="AD19" s="48"/>
+      <c r="AE19" s="48"/>
+      <c r="AF19" s="48"/>
+      <c r="AG19" s="48"/>
+      <c r="AH19" s="48"/>
+      <c r="AI19" s="48"/>
+      <c r="AJ19" s="48"/>
+      <c r="AK19" s="48"/>
+      <c r="AL19" s="48"/>
     </row>
     <row r="20" spans="1:38" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
@@ -6593,10 +6596,10 @@
       </c>
     </row>
     <row r="31" spans="1:38" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="58" t="s">
+      <c r="A31" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="B31" s="58"/>
+      <c r="B31" s="49"/>
       <c r="C31" s="11">
         <f t="shared" ref="C31:H31" si="8">SUM(C21:C30)</f>
         <v>15300000</v>
@@ -6655,90 +6658,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="50" t="s">
         <v>95</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
-      <c r="L1" s="49"/>
-      <c r="M1" s="49"/>
-      <c r="N1" s="49"/>
-      <c r="O1" s="49"/>
-      <c r="P1" s="49"/>
-      <c r="Q1" s="49"/>
-      <c r="R1" s="49"/>
-      <c r="S1" s="49"/>
-      <c r="T1" s="49"/>
-      <c r="U1" s="49"/>
-      <c r="V1" s="49"/>
-      <c r="W1" s="49"/>
-      <c r="X1" s="49"/>
-      <c r="Y1" s="49"/>
-      <c r="Z1" s="49"/>
-      <c r="AA1" s="49"/>
-      <c r="AB1" s="49"/>
-      <c r="AC1" s="49"/>
-      <c r="AD1" s="49"/>
-      <c r="AE1" s="49"/>
-      <c r="AF1" s="49"/>
-      <c r="AG1" s="49"/>
-      <c r="AH1" s="49"/>
-      <c r="AI1" s="49"/>
-      <c r="AJ1" s="49"/>
-      <c r="AK1" s="49"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="50"/>
+      <c r="M1" s="50"/>
+      <c r="N1" s="50"/>
+      <c r="O1" s="50"/>
+      <c r="P1" s="50"/>
+      <c r="Q1" s="50"/>
+      <c r="R1" s="50"/>
+      <c r="S1" s="50"/>
+      <c r="T1" s="50"/>
+      <c r="U1" s="50"/>
+      <c r="V1" s="50"/>
+      <c r="W1" s="50"/>
+      <c r="X1" s="50"/>
+      <c r="Y1" s="50"/>
+      <c r="Z1" s="50"/>
+      <c r="AA1" s="50"/>
+      <c r="AB1" s="50"/>
+      <c r="AC1" s="50"/>
+      <c r="AD1" s="50"/>
+      <c r="AE1" s="50"/>
+      <c r="AF1" s="50"/>
+      <c r="AG1" s="50"/>
+      <c r="AH1" s="50"/>
+      <c r="AI1" s="50"/>
+      <c r="AJ1" s="50"/>
+      <c r="AK1" s="50"/>
     </row>
     <row r="2" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="59" t="s">
+      <c r="A2" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="59"/>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="59"/>
-      <c r="H2" s="59"/>
-      <c r="I2" s="59"/>
-      <c r="J2" s="59"/>
-      <c r="K2" s="59"/>
-      <c r="L2" s="59"/>
-      <c r="M2" s="59"/>
-      <c r="N2" s="59"/>
-      <c r="O2" s="59"/>
-      <c r="P2" s="59"/>
-      <c r="Q2" s="59"/>
-      <c r="R2" s="59"/>
-      <c r="S2" s="59"/>
-      <c r="T2" s="59"/>
-      <c r="U2" s="59"/>
-      <c r="V2" s="59"/>
-      <c r="W2" s="59"/>
-      <c r="X2" s="59"/>
-      <c r="Y2" s="59"/>
-      <c r="Z2" s="59"/>
-      <c r="AA2" s="59"/>
-      <c r="AB2" s="59"/>
-      <c r="AC2" s="59"/>
-      <c r="AD2" s="59"/>
-      <c r="AE2" s="59"/>
-      <c r="AF2" s="59"/>
-      <c r="AG2" s="59"/>
-      <c r="AH2" s="59"/>
-      <c r="AI2" s="59"/>
-      <c r="AJ2" s="59"/>
-      <c r="AK2" s="59"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="51"/>
+      <c r="K2" s="51"/>
+      <c r="L2" s="51"/>
+      <c r="M2" s="51"/>
+      <c r="N2" s="51"/>
+      <c r="O2" s="51"/>
+      <c r="P2" s="51"/>
+      <c r="Q2" s="51"/>
+      <c r="R2" s="51"/>
+      <c r="S2" s="51"/>
+      <c r="T2" s="51"/>
+      <c r="U2" s="51"/>
+      <c r="V2" s="51"/>
+      <c r="W2" s="51"/>
+      <c r="X2" s="51"/>
+      <c r="Y2" s="51"/>
+      <c r="Z2" s="51"/>
+      <c r="AA2" s="51"/>
+      <c r="AB2" s="51"/>
+      <c r="AC2" s="51"/>
+      <c r="AD2" s="51"/>
+      <c r="AE2" s="51"/>
+      <c r="AF2" s="51"/>
+      <c r="AG2" s="51"/>
+      <c r="AH2" s="51"/>
+      <c r="AI2" s="51"/>
+      <c r="AJ2" s="51"/>
+      <c r="AK2" s="51"/>
     </row>
     <row r="3" spans="1:37" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:37" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="60" t="s">
+      <c r="A4" s="52" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="29" t="s">
@@ -6831,27 +6834,27 @@
       <c r="AE4" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="AF4" s="61" t="s">
+      <c r="AF4" s="53" t="s">
         <v>54</v>
       </c>
-      <c r="AG4" s="62" t="s">
+      <c r="AG4" s="54" t="s">
         <v>55</v>
       </c>
-      <c r="AH4" s="63" t="s">
+      <c r="AH4" s="55" t="s">
         <v>56</v>
       </c>
-      <c r="AI4" s="64" t="s">
+      <c r="AI4" s="56" t="s">
         <v>57</v>
       </c>
-      <c r="AJ4" s="65" t="s">
+      <c r="AJ4" s="57" t="s">
         <v>58</v>
       </c>
-      <c r="AK4" s="64" t="s">
+      <c r="AK4" s="56" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:37" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="60"/>
+      <c r="A5" s="52"/>
       <c r="B5" s="31">
         <v>1</v>
       </c>
@@ -6942,12 +6945,12 @@
       <c r="AE5" s="31">
         <v>30</v>
       </c>
-      <c r="AF5" s="61"/>
-      <c r="AG5" s="61"/>
-      <c r="AH5" s="61"/>
-      <c r="AI5" s="61"/>
-      <c r="AJ5" s="61"/>
-      <c r="AK5" s="61"/>
+      <c r="AF5" s="53"/>
+      <c r="AG5" s="53"/>
+      <c r="AH5" s="53"/>
+      <c r="AI5" s="53"/>
+      <c r="AJ5" s="53"/>
+      <c r="AK5" s="53"/>
     </row>
     <row r="6" spans="1:37" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="1:37" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7698,45 +7701,45 @@
     </row>
     <row r="18" spans="1:37" ht="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="1:37" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="57" t="s">
+      <c r="A19" s="48" t="s">
         <v>97</v>
       </c>
-      <c r="B19" s="57"/>
-      <c r="C19" s="57"/>
-      <c r="D19" s="57"/>
-      <c r="E19" s="57"/>
-      <c r="F19" s="57"/>
-      <c r="G19" s="57"/>
-      <c r="H19" s="57"/>
-      <c r="I19" s="57"/>
-      <c r="J19" s="57"/>
-      <c r="K19" s="57"/>
-      <c r="L19" s="57"/>
-      <c r="M19" s="57"/>
-      <c r="N19" s="57"/>
-      <c r="O19" s="57"/>
-      <c r="P19" s="57"/>
-      <c r="Q19" s="57"/>
-      <c r="R19" s="57"/>
-      <c r="S19" s="57"/>
-      <c r="T19" s="57"/>
-      <c r="U19" s="57"/>
-      <c r="V19" s="57"/>
-      <c r="W19" s="57"/>
-      <c r="X19" s="57"/>
-      <c r="Y19" s="57"/>
-      <c r="Z19" s="57"/>
-      <c r="AA19" s="57"/>
-      <c r="AB19" s="57"/>
-      <c r="AC19" s="57"/>
-      <c r="AD19" s="57"/>
-      <c r="AE19" s="57"/>
-      <c r="AF19" s="57"/>
-      <c r="AG19" s="57"/>
-      <c r="AH19" s="57"/>
-      <c r="AI19" s="57"/>
-      <c r="AJ19" s="57"/>
-      <c r="AK19" s="57"/>
+      <c r="B19" s="48"/>
+      <c r="C19" s="48"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="48"/>
+      <c r="G19" s="48"/>
+      <c r="H19" s="48"/>
+      <c r="I19" s="48"/>
+      <c r="J19" s="48"/>
+      <c r="K19" s="48"/>
+      <c r="L19" s="48"/>
+      <c r="M19" s="48"/>
+      <c r="N19" s="48"/>
+      <c r="O19" s="48"/>
+      <c r="P19" s="48"/>
+      <c r="Q19" s="48"/>
+      <c r="R19" s="48"/>
+      <c r="S19" s="48"/>
+      <c r="T19" s="48"/>
+      <c r="U19" s="48"/>
+      <c r="V19" s="48"/>
+      <c r="W19" s="48"/>
+      <c r="X19" s="48"/>
+      <c r="Y19" s="48"/>
+      <c r="Z19" s="48"/>
+      <c r="AA19" s="48"/>
+      <c r="AB19" s="48"/>
+      <c r="AC19" s="48"/>
+      <c r="AD19" s="48"/>
+      <c r="AE19" s="48"/>
+      <c r="AF19" s="48"/>
+      <c r="AG19" s="48"/>
+      <c r="AH19" s="48"/>
+      <c r="AI19" s="48"/>
+      <c r="AJ19" s="48"/>
+      <c r="AK19" s="48"/>
     </row>
     <row r="20" spans="1:37" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
@@ -8095,10 +8098,10 @@
       </c>
     </row>
     <row r="31" spans="1:37" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="58" t="s">
+      <c r="A31" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="B31" s="58"/>
+      <c r="B31" s="49"/>
       <c r="C31" s="11">
         <f t="shared" ref="C31:H31" si="8">SUM(C21:C30)</f>
         <v>15300000</v>
@@ -8157,92 +8160,92 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="50" t="s">
         <v>98</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
-      <c r="L1" s="49"/>
-      <c r="M1" s="49"/>
-      <c r="N1" s="49"/>
-      <c r="O1" s="49"/>
-      <c r="P1" s="49"/>
-      <c r="Q1" s="49"/>
-      <c r="R1" s="49"/>
-      <c r="S1" s="49"/>
-      <c r="T1" s="49"/>
-      <c r="U1" s="49"/>
-      <c r="V1" s="49"/>
-      <c r="W1" s="49"/>
-      <c r="X1" s="49"/>
-      <c r="Y1" s="49"/>
-      <c r="Z1" s="49"/>
-      <c r="AA1" s="49"/>
-      <c r="AB1" s="49"/>
-      <c r="AC1" s="49"/>
-      <c r="AD1" s="49"/>
-      <c r="AE1" s="49"/>
-      <c r="AF1" s="49"/>
-      <c r="AG1" s="49"/>
-      <c r="AH1" s="49"/>
-      <c r="AI1" s="49"/>
-      <c r="AJ1" s="49"/>
-      <c r="AK1" s="49"/>
-      <c r="AL1" s="49"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="50"/>
+      <c r="M1" s="50"/>
+      <c r="N1" s="50"/>
+      <c r="O1" s="50"/>
+      <c r="P1" s="50"/>
+      <c r="Q1" s="50"/>
+      <c r="R1" s="50"/>
+      <c r="S1" s="50"/>
+      <c r="T1" s="50"/>
+      <c r="U1" s="50"/>
+      <c r="V1" s="50"/>
+      <c r="W1" s="50"/>
+      <c r="X1" s="50"/>
+      <c r="Y1" s="50"/>
+      <c r="Z1" s="50"/>
+      <c r="AA1" s="50"/>
+      <c r="AB1" s="50"/>
+      <c r="AC1" s="50"/>
+      <c r="AD1" s="50"/>
+      <c r="AE1" s="50"/>
+      <c r="AF1" s="50"/>
+      <c r="AG1" s="50"/>
+      <c r="AH1" s="50"/>
+      <c r="AI1" s="50"/>
+      <c r="AJ1" s="50"/>
+      <c r="AK1" s="50"/>
+      <c r="AL1" s="50"/>
     </row>
     <row r="2" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="59" t="s">
+      <c r="A2" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="59"/>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="59"/>
-      <c r="H2" s="59"/>
-      <c r="I2" s="59"/>
-      <c r="J2" s="59"/>
-      <c r="K2" s="59"/>
-      <c r="L2" s="59"/>
-      <c r="M2" s="59"/>
-      <c r="N2" s="59"/>
-      <c r="O2" s="59"/>
-      <c r="P2" s="59"/>
-      <c r="Q2" s="59"/>
-      <c r="R2" s="59"/>
-      <c r="S2" s="59"/>
-      <c r="T2" s="59"/>
-      <c r="U2" s="59"/>
-      <c r="V2" s="59"/>
-      <c r="W2" s="59"/>
-      <c r="X2" s="59"/>
-      <c r="Y2" s="59"/>
-      <c r="Z2" s="59"/>
-      <c r="AA2" s="59"/>
-      <c r="AB2" s="59"/>
-      <c r="AC2" s="59"/>
-      <c r="AD2" s="59"/>
-      <c r="AE2" s="59"/>
-      <c r="AF2" s="59"/>
-      <c r="AG2" s="59"/>
-      <c r="AH2" s="59"/>
-      <c r="AI2" s="59"/>
-      <c r="AJ2" s="59"/>
-      <c r="AK2" s="59"/>
-      <c r="AL2" s="59"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="51"/>
+      <c r="K2" s="51"/>
+      <c r="L2" s="51"/>
+      <c r="M2" s="51"/>
+      <c r="N2" s="51"/>
+      <c r="O2" s="51"/>
+      <c r="P2" s="51"/>
+      <c r="Q2" s="51"/>
+      <c r="R2" s="51"/>
+      <c r="S2" s="51"/>
+      <c r="T2" s="51"/>
+      <c r="U2" s="51"/>
+      <c r="V2" s="51"/>
+      <c r="W2" s="51"/>
+      <c r="X2" s="51"/>
+      <c r="Y2" s="51"/>
+      <c r="Z2" s="51"/>
+      <c r="AA2" s="51"/>
+      <c r="AB2" s="51"/>
+      <c r="AC2" s="51"/>
+      <c r="AD2" s="51"/>
+      <c r="AE2" s="51"/>
+      <c r="AF2" s="51"/>
+      <c r="AG2" s="51"/>
+      <c r="AH2" s="51"/>
+      <c r="AI2" s="51"/>
+      <c r="AJ2" s="51"/>
+      <c r="AK2" s="51"/>
+      <c r="AL2" s="51"/>
     </row>
     <row r="3" spans="1:38" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="60" t="s">
+      <c r="A4" s="52" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="29" t="s">
@@ -8338,27 +8341,27 @@
       <c r="AF4" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="AG4" s="61" t="s">
+      <c r="AG4" s="53" t="s">
         <v>54</v>
       </c>
-      <c r="AH4" s="62" t="s">
+      <c r="AH4" s="54" t="s">
         <v>55</v>
       </c>
-      <c r="AI4" s="63" t="s">
+      <c r="AI4" s="55" t="s">
         <v>56</v>
       </c>
-      <c r="AJ4" s="64" t="s">
+      <c r="AJ4" s="56" t="s">
         <v>57</v>
       </c>
-      <c r="AK4" s="65" t="s">
+      <c r="AK4" s="57" t="s">
         <v>58</v>
       </c>
-      <c r="AL4" s="64" t="s">
+      <c r="AL4" s="56" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:38" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="60"/>
+      <c r="A5" s="52"/>
       <c r="B5" s="31">
         <v>1</v>
       </c>
@@ -8452,12 +8455,12 @@
       <c r="AF5" s="31">
         <v>31</v>
       </c>
-      <c r="AG5" s="61"/>
-      <c r="AH5" s="61"/>
-      <c r="AI5" s="61"/>
-      <c r="AJ5" s="61"/>
-      <c r="AK5" s="61"/>
-      <c r="AL5" s="61"/>
+      <c r="AG5" s="53"/>
+      <c r="AH5" s="53"/>
+      <c r="AI5" s="53"/>
+      <c r="AJ5" s="53"/>
+      <c r="AK5" s="53"/>
+      <c r="AL5" s="53"/>
     </row>
     <row r="6" spans="1:38" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="1:38" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -9222,46 +9225,46 @@
     </row>
     <row r="18" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="1:38" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="57" t="s">
+      <c r="A19" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="B19" s="57"/>
-      <c r="C19" s="57"/>
-      <c r="D19" s="57"/>
-      <c r="E19" s="57"/>
-      <c r="F19" s="57"/>
-      <c r="G19" s="57"/>
-      <c r="H19" s="57"/>
-      <c r="I19" s="57"/>
-      <c r="J19" s="57"/>
-      <c r="K19" s="57"/>
-      <c r="L19" s="57"/>
-      <c r="M19" s="57"/>
-      <c r="N19" s="57"/>
-      <c r="O19" s="57"/>
-      <c r="P19" s="57"/>
-      <c r="Q19" s="57"/>
-      <c r="R19" s="57"/>
-      <c r="S19" s="57"/>
-      <c r="T19" s="57"/>
-      <c r="U19" s="57"/>
-      <c r="V19" s="57"/>
-      <c r="W19" s="57"/>
-      <c r="X19" s="57"/>
-      <c r="Y19" s="57"/>
-      <c r="Z19" s="57"/>
-      <c r="AA19" s="57"/>
-      <c r="AB19" s="57"/>
-      <c r="AC19" s="57"/>
-      <c r="AD19" s="57"/>
-      <c r="AE19" s="57"/>
-      <c r="AF19" s="57"/>
-      <c r="AG19" s="57"/>
-      <c r="AH19" s="57"/>
-      <c r="AI19" s="57"/>
-      <c r="AJ19" s="57"/>
-      <c r="AK19" s="57"/>
-      <c r="AL19" s="57"/>
+      <c r="B19" s="48"/>
+      <c r="C19" s="48"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="48"/>
+      <c r="G19" s="48"/>
+      <c r="H19" s="48"/>
+      <c r="I19" s="48"/>
+      <c r="J19" s="48"/>
+      <c r="K19" s="48"/>
+      <c r="L19" s="48"/>
+      <c r="M19" s="48"/>
+      <c r="N19" s="48"/>
+      <c r="O19" s="48"/>
+      <c r="P19" s="48"/>
+      <c r="Q19" s="48"/>
+      <c r="R19" s="48"/>
+      <c r="S19" s="48"/>
+      <c r="T19" s="48"/>
+      <c r="U19" s="48"/>
+      <c r="V19" s="48"/>
+      <c r="W19" s="48"/>
+      <c r="X19" s="48"/>
+      <c r="Y19" s="48"/>
+      <c r="Z19" s="48"/>
+      <c r="AA19" s="48"/>
+      <c r="AB19" s="48"/>
+      <c r="AC19" s="48"/>
+      <c r="AD19" s="48"/>
+      <c r="AE19" s="48"/>
+      <c r="AF19" s="48"/>
+      <c r="AG19" s="48"/>
+      <c r="AH19" s="48"/>
+      <c r="AI19" s="48"/>
+      <c r="AJ19" s="48"/>
+      <c r="AK19" s="48"/>
+      <c r="AL19" s="48"/>
     </row>
     <row r="20" spans="1:38" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
@@ -9620,10 +9623,10 @@
       </c>
     </row>
     <row r="31" spans="1:38" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="58" t="s">
+      <c r="A31" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="B31" s="58"/>
+      <c r="B31" s="49"/>
       <c r="C31" s="11">
         <f t="shared" ref="C31:H31" si="8">SUM(C21:C30)</f>
         <v>15300000</v>
@@ -9684,30 +9687,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
     </row>
     <row r="2" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="50" t="s">
+      <c r="B2" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="50"/>
-      <c r="D2" s="51" t="s">
+      <c r="C2" s="62"/>
+      <c r="D2" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
       <c r="G2" s="14">
         <v>9</v>
       </c>
@@ -9878,74 +9881,74 @@
     </row>
     <row r="16" spans="1:8" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="17" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="52" t="s">
+      <c r="A17" s="64" t="s">
         <v>34</v>
       </c>
-      <c r="B17" s="52"/>
-      <c r="C17" s="52"/>
-      <c r="D17" s="52"/>
-      <c r="E17" s="52"/>
-      <c r="F17" s="52"/>
+      <c r="B17" s="64"/>
+      <c r="C17" s="64"/>
+      <c r="D17" s="64"/>
+      <c r="E17" s="64"/>
+      <c r="F17" s="64"/>
     </row>
     <row r="18" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="53" t="s">
+      <c r="B18" s="65" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="53"/>
-      <c r="D18" s="53"/>
-      <c r="E18" s="53"/>
-      <c r="F18" s="53"/>
+      <c r="C18" s="65"/>
+      <c r="D18" s="65"/>
+      <c r="E18" s="65"/>
+      <c r="F18" s="65"/>
     </row>
     <row r="19" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="48" t="s">
+      <c r="B19" s="61" t="s">
         <v>38</v>
       </c>
-      <c r="C19" s="48"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="48"/>
-      <c r="F19" s="48"/>
+      <c r="C19" s="61"/>
+      <c r="D19" s="61"/>
+      <c r="E19" s="61"/>
+      <c r="F19" s="61"/>
     </row>
     <row r="20" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="48" t="s">
+      <c r="B20" s="61" t="s">
         <v>40</v>
       </c>
-      <c r="C20" s="48"/>
-      <c r="D20" s="48"/>
-      <c r="E20" s="48"/>
-      <c r="F20" s="48"/>
+      <c r="C20" s="61"/>
+      <c r="D20" s="61"/>
+      <c r="E20" s="61"/>
+      <c r="F20" s="61"/>
     </row>
     <row r="21" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="48" t="s">
+      <c r="B21" s="61" t="s">
         <v>42</v>
       </c>
-      <c r="C21" s="48"/>
-      <c r="D21" s="48"/>
-      <c r="E21" s="48"/>
-      <c r="F21" s="48"/>
+      <c r="C21" s="61"/>
+      <c r="D21" s="61"/>
+      <c r="E21" s="61"/>
+      <c r="F21" s="61"/>
     </row>
     <row r="22" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="48" t="s">
+      <c r="B22" s="61" t="s">
         <v>44</v>
       </c>
-      <c r="C22" s="48"/>
-      <c r="D22" s="48"/>
-      <c r="E22" s="48"/>
-      <c r="F22" s="48"/>
+      <c r="C22" s="61"/>
+      <c r="D22" s="61"/>
+      <c r="E22" s="61"/>
+      <c r="F22" s="61"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -9988,92 +9991,92 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="50" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
-      <c r="L1" s="49"/>
-      <c r="M1" s="49"/>
-      <c r="N1" s="49"/>
-      <c r="O1" s="49"/>
-      <c r="P1" s="49"/>
-      <c r="Q1" s="49"/>
-      <c r="R1" s="49"/>
-      <c r="S1" s="49"/>
-      <c r="T1" s="49"/>
-      <c r="U1" s="49"/>
-      <c r="V1" s="49"/>
-      <c r="W1" s="49"/>
-      <c r="X1" s="49"/>
-      <c r="Y1" s="49"/>
-      <c r="Z1" s="49"/>
-      <c r="AA1" s="49"/>
-      <c r="AB1" s="49"/>
-      <c r="AC1" s="49"/>
-      <c r="AD1" s="49"/>
-      <c r="AE1" s="49"/>
-      <c r="AF1" s="49"/>
-      <c r="AG1" s="49"/>
-      <c r="AH1" s="49"/>
-      <c r="AI1" s="49"/>
-      <c r="AJ1" s="49"/>
-      <c r="AK1" s="49"/>
-      <c r="AL1" s="49"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="50"/>
+      <c r="M1" s="50"/>
+      <c r="N1" s="50"/>
+      <c r="O1" s="50"/>
+      <c r="P1" s="50"/>
+      <c r="Q1" s="50"/>
+      <c r="R1" s="50"/>
+      <c r="S1" s="50"/>
+      <c r="T1" s="50"/>
+      <c r="U1" s="50"/>
+      <c r="V1" s="50"/>
+      <c r="W1" s="50"/>
+      <c r="X1" s="50"/>
+      <c r="Y1" s="50"/>
+      <c r="Z1" s="50"/>
+      <c r="AA1" s="50"/>
+      <c r="AB1" s="50"/>
+      <c r="AC1" s="50"/>
+      <c r="AD1" s="50"/>
+      <c r="AE1" s="50"/>
+      <c r="AF1" s="50"/>
+      <c r="AG1" s="50"/>
+      <c r="AH1" s="50"/>
+      <c r="AI1" s="50"/>
+      <c r="AJ1" s="50"/>
+      <c r="AK1" s="50"/>
+      <c r="AL1" s="50"/>
     </row>
     <row r="2" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="59" t="s">
+      <c r="A2" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="59"/>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="59"/>
-      <c r="H2" s="59"/>
-      <c r="I2" s="59"/>
-      <c r="J2" s="59"/>
-      <c r="K2" s="59"/>
-      <c r="L2" s="59"/>
-      <c r="M2" s="59"/>
-      <c r="N2" s="59"/>
-      <c r="O2" s="59"/>
-      <c r="P2" s="59"/>
-      <c r="Q2" s="59"/>
-      <c r="R2" s="59"/>
-      <c r="S2" s="59"/>
-      <c r="T2" s="59"/>
-      <c r="U2" s="59"/>
-      <c r="V2" s="59"/>
-      <c r="W2" s="59"/>
-      <c r="X2" s="59"/>
-      <c r="Y2" s="59"/>
-      <c r="Z2" s="59"/>
-      <c r="AA2" s="59"/>
-      <c r="AB2" s="59"/>
-      <c r="AC2" s="59"/>
-      <c r="AD2" s="59"/>
-      <c r="AE2" s="59"/>
-      <c r="AF2" s="59"/>
-      <c r="AG2" s="59"/>
-      <c r="AH2" s="59"/>
-      <c r="AI2" s="59"/>
-      <c r="AJ2" s="59"/>
-      <c r="AK2" s="59"/>
-      <c r="AL2" s="59"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="51"/>
+      <c r="K2" s="51"/>
+      <c r="L2" s="51"/>
+      <c r="M2" s="51"/>
+      <c r="N2" s="51"/>
+      <c r="O2" s="51"/>
+      <c r="P2" s="51"/>
+      <c r="Q2" s="51"/>
+      <c r="R2" s="51"/>
+      <c r="S2" s="51"/>
+      <c r="T2" s="51"/>
+      <c r="U2" s="51"/>
+      <c r="V2" s="51"/>
+      <c r="W2" s="51"/>
+      <c r="X2" s="51"/>
+      <c r="Y2" s="51"/>
+      <c r="Z2" s="51"/>
+      <c r="AA2" s="51"/>
+      <c r="AB2" s="51"/>
+      <c r="AC2" s="51"/>
+      <c r="AD2" s="51"/>
+      <c r="AE2" s="51"/>
+      <c r="AF2" s="51"/>
+      <c r="AG2" s="51"/>
+      <c r="AH2" s="51"/>
+      <c r="AI2" s="51"/>
+      <c r="AJ2" s="51"/>
+      <c r="AK2" s="51"/>
+      <c r="AL2" s="51"/>
     </row>
     <row r="3" spans="1:38" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="60" t="s">
+      <c r="A4" s="52" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="29" t="s">
@@ -10169,27 +10172,27 @@
       <c r="AF4" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="AG4" s="61" t="s">
+      <c r="AG4" s="53" t="s">
         <v>54</v>
       </c>
-      <c r="AH4" s="62" t="s">
+      <c r="AH4" s="54" t="s">
         <v>55</v>
       </c>
-      <c r="AI4" s="63" t="s">
+      <c r="AI4" s="55" t="s">
         <v>56</v>
       </c>
-      <c r="AJ4" s="64" t="s">
+      <c r="AJ4" s="56" t="s">
         <v>57</v>
       </c>
-      <c r="AK4" s="65" t="s">
+      <c r="AK4" s="57" t="s">
         <v>58</v>
       </c>
-      <c r="AL4" s="64" t="s">
+      <c r="AL4" s="56" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:38" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="60"/>
+      <c r="A5" s="52"/>
       <c r="B5" s="31">
         <v>1</v>
       </c>
@@ -10283,12 +10286,12 @@
       <c r="AF5" s="31">
         <v>31</v>
       </c>
-      <c r="AG5" s="61"/>
-      <c r="AH5" s="61"/>
-      <c r="AI5" s="61"/>
-      <c r="AJ5" s="61"/>
-      <c r="AK5" s="61"/>
-      <c r="AL5" s="61"/>
+      <c r="AG5" s="53"/>
+      <c r="AH5" s="53"/>
+      <c r="AI5" s="53"/>
+      <c r="AJ5" s="53"/>
+      <c r="AK5" s="53"/>
+      <c r="AL5" s="53"/>
     </row>
     <row r="6" spans="1:38" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="1:38" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -11053,46 +11056,46 @@
     </row>
     <row r="18" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="1:38" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="57" t="s">
+      <c r="A19" s="48" t="s">
         <v>61</v>
       </c>
-      <c r="B19" s="57"/>
-      <c r="C19" s="57"/>
-      <c r="D19" s="57"/>
-      <c r="E19" s="57"/>
-      <c r="F19" s="57"/>
-      <c r="G19" s="57"/>
-      <c r="H19" s="57"/>
-      <c r="I19" s="57"/>
-      <c r="J19" s="57"/>
-      <c r="K19" s="57"/>
-      <c r="L19" s="57"/>
-      <c r="M19" s="57"/>
-      <c r="N19" s="57"/>
-      <c r="O19" s="57"/>
-      <c r="P19" s="57"/>
-      <c r="Q19" s="57"/>
-      <c r="R19" s="57"/>
-      <c r="S19" s="57"/>
-      <c r="T19" s="57"/>
-      <c r="U19" s="57"/>
-      <c r="V19" s="57"/>
-      <c r="W19" s="57"/>
-      <c r="X19" s="57"/>
-      <c r="Y19" s="57"/>
-      <c r="Z19" s="57"/>
-      <c r="AA19" s="57"/>
-      <c r="AB19" s="57"/>
-      <c r="AC19" s="57"/>
-      <c r="AD19" s="57"/>
-      <c r="AE19" s="57"/>
-      <c r="AF19" s="57"/>
-      <c r="AG19" s="57"/>
-      <c r="AH19" s="57"/>
-      <c r="AI19" s="57"/>
-      <c r="AJ19" s="57"/>
-      <c r="AK19" s="57"/>
-      <c r="AL19" s="57"/>
+      <c r="B19" s="48"/>
+      <c r="C19" s="48"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="48"/>
+      <c r="G19" s="48"/>
+      <c r="H19" s="48"/>
+      <c r="I19" s="48"/>
+      <c r="J19" s="48"/>
+      <c r="K19" s="48"/>
+      <c r="L19" s="48"/>
+      <c r="M19" s="48"/>
+      <c r="N19" s="48"/>
+      <c r="O19" s="48"/>
+      <c r="P19" s="48"/>
+      <c r="Q19" s="48"/>
+      <c r="R19" s="48"/>
+      <c r="S19" s="48"/>
+      <c r="T19" s="48"/>
+      <c r="U19" s="48"/>
+      <c r="V19" s="48"/>
+      <c r="W19" s="48"/>
+      <c r="X19" s="48"/>
+      <c r="Y19" s="48"/>
+      <c r="Z19" s="48"/>
+      <c r="AA19" s="48"/>
+      <c r="AB19" s="48"/>
+      <c r="AC19" s="48"/>
+      <c r="AD19" s="48"/>
+      <c r="AE19" s="48"/>
+      <c r="AF19" s="48"/>
+      <c r="AG19" s="48"/>
+      <c r="AH19" s="48"/>
+      <c r="AI19" s="48"/>
+      <c r="AJ19" s="48"/>
+      <c r="AK19" s="48"/>
+      <c r="AL19" s="48"/>
     </row>
     <row r="20" spans="1:38" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
@@ -11451,10 +11454,10 @@
       </c>
     </row>
     <row r="31" spans="1:38" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="58" t="s">
+      <c r="A31" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="B31" s="58"/>
+      <c r="B31" s="49"/>
       <c r="C31" s="11">
         <f t="shared" ref="C31:H31" si="8">SUM(C21:C30)</f>
         <v>15300000</v>
@@ -11513,86 +11516,86 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:35" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="50" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
-      <c r="L1" s="49"/>
-      <c r="M1" s="49"/>
-      <c r="N1" s="49"/>
-      <c r="O1" s="49"/>
-      <c r="P1" s="49"/>
-      <c r="Q1" s="49"/>
-      <c r="R1" s="49"/>
-      <c r="S1" s="49"/>
-      <c r="T1" s="49"/>
-      <c r="U1" s="49"/>
-      <c r="V1" s="49"/>
-      <c r="W1" s="49"/>
-      <c r="X1" s="49"/>
-      <c r="Y1" s="49"/>
-      <c r="Z1" s="49"/>
-      <c r="AA1" s="49"/>
-      <c r="AB1" s="49"/>
-      <c r="AC1" s="49"/>
-      <c r="AD1" s="49"/>
-      <c r="AE1" s="49"/>
-      <c r="AF1" s="49"/>
-      <c r="AG1" s="49"/>
-      <c r="AH1" s="49"/>
-      <c r="AI1" s="49"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="50"/>
+      <c r="M1" s="50"/>
+      <c r="N1" s="50"/>
+      <c r="O1" s="50"/>
+      <c r="P1" s="50"/>
+      <c r="Q1" s="50"/>
+      <c r="R1" s="50"/>
+      <c r="S1" s="50"/>
+      <c r="T1" s="50"/>
+      <c r="U1" s="50"/>
+      <c r="V1" s="50"/>
+      <c r="W1" s="50"/>
+      <c r="X1" s="50"/>
+      <c r="Y1" s="50"/>
+      <c r="Z1" s="50"/>
+      <c r="AA1" s="50"/>
+      <c r="AB1" s="50"/>
+      <c r="AC1" s="50"/>
+      <c r="AD1" s="50"/>
+      <c r="AE1" s="50"/>
+      <c r="AF1" s="50"/>
+      <c r="AG1" s="50"/>
+      <c r="AH1" s="50"/>
+      <c r="AI1" s="50"/>
     </row>
     <row r="2" spans="1:35" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="59" t="s">
+      <c r="A2" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="59"/>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="59"/>
-      <c r="H2" s="59"/>
-      <c r="I2" s="59"/>
-      <c r="J2" s="59"/>
-      <c r="K2" s="59"/>
-      <c r="L2" s="59"/>
-      <c r="M2" s="59"/>
-      <c r="N2" s="59"/>
-      <c r="O2" s="59"/>
-      <c r="P2" s="59"/>
-      <c r="Q2" s="59"/>
-      <c r="R2" s="59"/>
-      <c r="S2" s="59"/>
-      <c r="T2" s="59"/>
-      <c r="U2" s="59"/>
-      <c r="V2" s="59"/>
-      <c r="W2" s="59"/>
-      <c r="X2" s="59"/>
-      <c r="Y2" s="59"/>
-      <c r="Z2" s="59"/>
-      <c r="AA2" s="59"/>
-      <c r="AB2" s="59"/>
-      <c r="AC2" s="59"/>
-      <c r="AD2" s="59"/>
-      <c r="AE2" s="59"/>
-      <c r="AF2" s="59"/>
-      <c r="AG2" s="59"/>
-      <c r="AH2" s="59"/>
-      <c r="AI2" s="59"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="51"/>
+      <c r="K2" s="51"/>
+      <c r="L2" s="51"/>
+      <c r="M2" s="51"/>
+      <c r="N2" s="51"/>
+      <c r="O2" s="51"/>
+      <c r="P2" s="51"/>
+      <c r="Q2" s="51"/>
+      <c r="R2" s="51"/>
+      <c r="S2" s="51"/>
+      <c r="T2" s="51"/>
+      <c r="U2" s="51"/>
+      <c r="V2" s="51"/>
+      <c r="W2" s="51"/>
+      <c r="X2" s="51"/>
+      <c r="Y2" s="51"/>
+      <c r="Z2" s="51"/>
+      <c r="AA2" s="51"/>
+      <c r="AB2" s="51"/>
+      <c r="AC2" s="51"/>
+      <c r="AD2" s="51"/>
+      <c r="AE2" s="51"/>
+      <c r="AF2" s="51"/>
+      <c r="AG2" s="51"/>
+      <c r="AH2" s="51"/>
+      <c r="AI2" s="51"/>
     </row>
     <row r="3" spans="1:35" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:35" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="60" t="s">
+      <c r="A4" s="52" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="29" t="s">
@@ -11679,27 +11682,27 @@
       <c r="AC4" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="AD4" s="61" t="s">
+      <c r="AD4" s="53" t="s">
         <v>54</v>
       </c>
-      <c r="AE4" s="62" t="s">
+      <c r="AE4" s="54" t="s">
         <v>55</v>
       </c>
-      <c r="AF4" s="63" t="s">
+      <c r="AF4" s="55" t="s">
         <v>56</v>
       </c>
-      <c r="AG4" s="64" t="s">
+      <c r="AG4" s="56" t="s">
         <v>57</v>
       </c>
-      <c r="AH4" s="65" t="s">
+      <c r="AH4" s="57" t="s">
         <v>58</v>
       </c>
-      <c r="AI4" s="64" t="s">
+      <c r="AI4" s="56" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:35" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="60"/>
+      <c r="A5" s="52"/>
       <c r="B5" s="31">
         <v>1</v>
       </c>
@@ -11784,12 +11787,12 @@
       <c r="AC5" s="31">
         <v>28</v>
       </c>
-      <c r="AD5" s="61"/>
-      <c r="AE5" s="61"/>
-      <c r="AF5" s="61"/>
-      <c r="AG5" s="61"/>
-      <c r="AH5" s="61"/>
-      <c r="AI5" s="61"/>
+      <c r="AD5" s="53"/>
+      <c r="AE5" s="53"/>
+      <c r="AF5" s="53"/>
+      <c r="AG5" s="53"/>
+      <c r="AH5" s="53"/>
+      <c r="AI5" s="53"/>
     </row>
     <row r="6" spans="1:35" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="1:35" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -12512,43 +12515,43 @@
     </row>
     <row r="18" spans="1:35" ht="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="1:35" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="57" t="s">
+      <c r="A19" s="48" t="s">
         <v>70</v>
       </c>
-      <c r="B19" s="57"/>
-      <c r="C19" s="57"/>
-      <c r="D19" s="57"/>
-      <c r="E19" s="57"/>
-      <c r="F19" s="57"/>
-      <c r="G19" s="57"/>
-      <c r="H19" s="57"/>
-      <c r="I19" s="57"/>
-      <c r="J19" s="57"/>
-      <c r="K19" s="57"/>
-      <c r="L19" s="57"/>
-      <c r="M19" s="57"/>
-      <c r="N19" s="57"/>
-      <c r="O19" s="57"/>
-      <c r="P19" s="57"/>
-      <c r="Q19" s="57"/>
-      <c r="R19" s="57"/>
-      <c r="S19" s="57"/>
-      <c r="T19" s="57"/>
-      <c r="U19" s="57"/>
-      <c r="V19" s="57"/>
-      <c r="W19" s="57"/>
-      <c r="X19" s="57"/>
-      <c r="Y19" s="57"/>
-      <c r="Z19" s="57"/>
-      <c r="AA19" s="57"/>
-      <c r="AB19" s="57"/>
-      <c r="AC19" s="57"/>
-      <c r="AD19" s="57"/>
-      <c r="AE19" s="57"/>
-      <c r="AF19" s="57"/>
-      <c r="AG19" s="57"/>
-      <c r="AH19" s="57"/>
-      <c r="AI19" s="57"/>
+      <c r="B19" s="48"/>
+      <c r="C19" s="48"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="48"/>
+      <c r="G19" s="48"/>
+      <c r="H19" s="48"/>
+      <c r="I19" s="48"/>
+      <c r="J19" s="48"/>
+      <c r="K19" s="48"/>
+      <c r="L19" s="48"/>
+      <c r="M19" s="48"/>
+      <c r="N19" s="48"/>
+      <c r="O19" s="48"/>
+      <c r="P19" s="48"/>
+      <c r="Q19" s="48"/>
+      <c r="R19" s="48"/>
+      <c r="S19" s="48"/>
+      <c r="T19" s="48"/>
+      <c r="U19" s="48"/>
+      <c r="V19" s="48"/>
+      <c r="W19" s="48"/>
+      <c r="X19" s="48"/>
+      <c r="Y19" s="48"/>
+      <c r="Z19" s="48"/>
+      <c r="AA19" s="48"/>
+      <c r="AB19" s="48"/>
+      <c r="AC19" s="48"/>
+      <c r="AD19" s="48"/>
+      <c r="AE19" s="48"/>
+      <c r="AF19" s="48"/>
+      <c r="AG19" s="48"/>
+      <c r="AH19" s="48"/>
+      <c r="AI19" s="48"/>
     </row>
     <row r="20" spans="1:35" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
@@ -12907,10 +12910,10 @@
       </c>
     </row>
     <row r="31" spans="1:35" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="58" t="s">
+      <c r="A31" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="B31" s="58"/>
+      <c r="B31" s="49"/>
       <c r="C31" s="11">
         <f t="shared" ref="C31:H31" si="8">SUM(C21:C30)</f>
         <v>15300000</v>
@@ -12969,92 +12972,92 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="50" t="s">
         <v>71</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
-      <c r="L1" s="49"/>
-      <c r="M1" s="49"/>
-      <c r="N1" s="49"/>
-      <c r="O1" s="49"/>
-      <c r="P1" s="49"/>
-      <c r="Q1" s="49"/>
-      <c r="R1" s="49"/>
-      <c r="S1" s="49"/>
-      <c r="T1" s="49"/>
-      <c r="U1" s="49"/>
-      <c r="V1" s="49"/>
-      <c r="W1" s="49"/>
-      <c r="X1" s="49"/>
-      <c r="Y1" s="49"/>
-      <c r="Z1" s="49"/>
-      <c r="AA1" s="49"/>
-      <c r="AB1" s="49"/>
-      <c r="AC1" s="49"/>
-      <c r="AD1" s="49"/>
-      <c r="AE1" s="49"/>
-      <c r="AF1" s="49"/>
-      <c r="AG1" s="49"/>
-      <c r="AH1" s="49"/>
-      <c r="AI1" s="49"/>
-      <c r="AJ1" s="49"/>
-      <c r="AK1" s="49"/>
-      <c r="AL1" s="49"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="50"/>
+      <c r="M1" s="50"/>
+      <c r="N1" s="50"/>
+      <c r="O1" s="50"/>
+      <c r="P1" s="50"/>
+      <c r="Q1" s="50"/>
+      <c r="R1" s="50"/>
+      <c r="S1" s="50"/>
+      <c r="T1" s="50"/>
+      <c r="U1" s="50"/>
+      <c r="V1" s="50"/>
+      <c r="W1" s="50"/>
+      <c r="X1" s="50"/>
+      <c r="Y1" s="50"/>
+      <c r="Z1" s="50"/>
+      <c r="AA1" s="50"/>
+      <c r="AB1" s="50"/>
+      <c r="AC1" s="50"/>
+      <c r="AD1" s="50"/>
+      <c r="AE1" s="50"/>
+      <c r="AF1" s="50"/>
+      <c r="AG1" s="50"/>
+      <c r="AH1" s="50"/>
+      <c r="AI1" s="50"/>
+      <c r="AJ1" s="50"/>
+      <c r="AK1" s="50"/>
+      <c r="AL1" s="50"/>
     </row>
     <row r="2" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="59" t="s">
+      <c r="A2" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="59"/>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="59"/>
-      <c r="H2" s="59"/>
-      <c r="I2" s="59"/>
-      <c r="J2" s="59"/>
-      <c r="K2" s="59"/>
-      <c r="L2" s="59"/>
-      <c r="M2" s="59"/>
-      <c r="N2" s="59"/>
-      <c r="O2" s="59"/>
-      <c r="P2" s="59"/>
-      <c r="Q2" s="59"/>
-      <c r="R2" s="59"/>
-      <c r="S2" s="59"/>
-      <c r="T2" s="59"/>
-      <c r="U2" s="59"/>
-      <c r="V2" s="59"/>
-      <c r="W2" s="59"/>
-      <c r="X2" s="59"/>
-      <c r="Y2" s="59"/>
-      <c r="Z2" s="59"/>
-      <c r="AA2" s="59"/>
-      <c r="AB2" s="59"/>
-      <c r="AC2" s="59"/>
-      <c r="AD2" s="59"/>
-      <c r="AE2" s="59"/>
-      <c r="AF2" s="59"/>
-      <c r="AG2" s="59"/>
-      <c r="AH2" s="59"/>
-      <c r="AI2" s="59"/>
-      <c r="AJ2" s="59"/>
-      <c r="AK2" s="59"/>
-      <c r="AL2" s="59"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="51"/>
+      <c r="K2" s="51"/>
+      <c r="L2" s="51"/>
+      <c r="M2" s="51"/>
+      <c r="N2" s="51"/>
+      <c r="O2" s="51"/>
+      <c r="P2" s="51"/>
+      <c r="Q2" s="51"/>
+      <c r="R2" s="51"/>
+      <c r="S2" s="51"/>
+      <c r="T2" s="51"/>
+      <c r="U2" s="51"/>
+      <c r="V2" s="51"/>
+      <c r="W2" s="51"/>
+      <c r="X2" s="51"/>
+      <c r="Y2" s="51"/>
+      <c r="Z2" s="51"/>
+      <c r="AA2" s="51"/>
+      <c r="AB2" s="51"/>
+      <c r="AC2" s="51"/>
+      <c r="AD2" s="51"/>
+      <c r="AE2" s="51"/>
+      <c r="AF2" s="51"/>
+      <c r="AG2" s="51"/>
+      <c r="AH2" s="51"/>
+      <c r="AI2" s="51"/>
+      <c r="AJ2" s="51"/>
+      <c r="AK2" s="51"/>
+      <c r="AL2" s="51"/>
     </row>
     <row r="3" spans="1:38" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="60" t="s">
+      <c r="A4" s="52" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="29" t="s">
@@ -13150,27 +13153,27 @@
       <c r="AF4" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="AG4" s="61" t="s">
+      <c r="AG4" s="53" t="s">
         <v>54</v>
       </c>
-      <c r="AH4" s="62" t="s">
+      <c r="AH4" s="54" t="s">
         <v>55</v>
       </c>
-      <c r="AI4" s="63" t="s">
+      <c r="AI4" s="55" t="s">
         <v>56</v>
       </c>
-      <c r="AJ4" s="64" t="s">
+      <c r="AJ4" s="56" t="s">
         <v>57</v>
       </c>
-      <c r="AK4" s="65" t="s">
+      <c r="AK4" s="57" t="s">
         <v>58</v>
       </c>
-      <c r="AL4" s="64" t="s">
+      <c r="AL4" s="56" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:38" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="60"/>
+      <c r="A5" s="52"/>
       <c r="B5" s="31">
         <v>1</v>
       </c>
@@ -13264,12 +13267,12 @@
       <c r="AF5" s="31">
         <v>31</v>
       </c>
-      <c r="AG5" s="61"/>
-      <c r="AH5" s="61"/>
-      <c r="AI5" s="61"/>
-      <c r="AJ5" s="61"/>
-      <c r="AK5" s="61"/>
-      <c r="AL5" s="61"/>
+      <c r="AG5" s="53"/>
+      <c r="AH5" s="53"/>
+      <c r="AI5" s="53"/>
+      <c r="AJ5" s="53"/>
+      <c r="AK5" s="53"/>
+      <c r="AL5" s="53"/>
     </row>
     <row r="6" spans="1:38" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="1:38" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -14034,46 +14037,46 @@
     </row>
     <row r="18" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="1:38" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="57" t="s">
+      <c r="A19" s="48" t="s">
         <v>73</v>
       </c>
-      <c r="B19" s="57"/>
-      <c r="C19" s="57"/>
-      <c r="D19" s="57"/>
-      <c r="E19" s="57"/>
-      <c r="F19" s="57"/>
-      <c r="G19" s="57"/>
-      <c r="H19" s="57"/>
-      <c r="I19" s="57"/>
-      <c r="J19" s="57"/>
-      <c r="K19" s="57"/>
-      <c r="L19" s="57"/>
-      <c r="M19" s="57"/>
-      <c r="N19" s="57"/>
-      <c r="O19" s="57"/>
-      <c r="P19" s="57"/>
-      <c r="Q19" s="57"/>
-      <c r="R19" s="57"/>
-      <c r="S19" s="57"/>
-      <c r="T19" s="57"/>
-      <c r="U19" s="57"/>
-      <c r="V19" s="57"/>
-      <c r="W19" s="57"/>
-      <c r="X19" s="57"/>
-      <c r="Y19" s="57"/>
-      <c r="Z19" s="57"/>
-      <c r="AA19" s="57"/>
-      <c r="AB19" s="57"/>
-      <c r="AC19" s="57"/>
-      <c r="AD19" s="57"/>
-      <c r="AE19" s="57"/>
-      <c r="AF19" s="57"/>
-      <c r="AG19" s="57"/>
-      <c r="AH19" s="57"/>
-      <c r="AI19" s="57"/>
-      <c r="AJ19" s="57"/>
-      <c r="AK19" s="57"/>
-      <c r="AL19" s="57"/>
+      <c r="B19" s="48"/>
+      <c r="C19" s="48"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="48"/>
+      <c r="G19" s="48"/>
+      <c r="H19" s="48"/>
+      <c r="I19" s="48"/>
+      <c r="J19" s="48"/>
+      <c r="K19" s="48"/>
+      <c r="L19" s="48"/>
+      <c r="M19" s="48"/>
+      <c r="N19" s="48"/>
+      <c r="O19" s="48"/>
+      <c r="P19" s="48"/>
+      <c r="Q19" s="48"/>
+      <c r="R19" s="48"/>
+      <c r="S19" s="48"/>
+      <c r="T19" s="48"/>
+      <c r="U19" s="48"/>
+      <c r="V19" s="48"/>
+      <c r="W19" s="48"/>
+      <c r="X19" s="48"/>
+      <c r="Y19" s="48"/>
+      <c r="Z19" s="48"/>
+      <c r="AA19" s="48"/>
+      <c r="AB19" s="48"/>
+      <c r="AC19" s="48"/>
+      <c r="AD19" s="48"/>
+      <c r="AE19" s="48"/>
+      <c r="AF19" s="48"/>
+      <c r="AG19" s="48"/>
+      <c r="AH19" s="48"/>
+      <c r="AI19" s="48"/>
+      <c r="AJ19" s="48"/>
+      <c r="AK19" s="48"/>
+      <c r="AL19" s="48"/>
     </row>
     <row r="20" spans="1:38" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
@@ -14432,10 +14435,10 @@
       </c>
     </row>
     <row r="31" spans="1:38" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="58" t="s">
+      <c r="A31" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="B31" s="58"/>
+      <c r="B31" s="49"/>
       <c r="C31" s="11">
         <f t="shared" ref="C31:H31" si="8">SUM(C21:C30)</f>
         <v>15300000</v>
@@ -14494,90 +14497,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
-      <c r="L1" s="49"/>
-      <c r="M1" s="49"/>
-      <c r="N1" s="49"/>
-      <c r="O1" s="49"/>
-      <c r="P1" s="49"/>
-      <c r="Q1" s="49"/>
-      <c r="R1" s="49"/>
-      <c r="S1" s="49"/>
-      <c r="T1" s="49"/>
-      <c r="U1" s="49"/>
-      <c r="V1" s="49"/>
-      <c r="W1" s="49"/>
-      <c r="X1" s="49"/>
-      <c r="Y1" s="49"/>
-      <c r="Z1" s="49"/>
-      <c r="AA1" s="49"/>
-      <c r="AB1" s="49"/>
-      <c r="AC1" s="49"/>
-      <c r="AD1" s="49"/>
-      <c r="AE1" s="49"/>
-      <c r="AF1" s="49"/>
-      <c r="AG1" s="49"/>
-      <c r="AH1" s="49"/>
-      <c r="AI1" s="49"/>
-      <c r="AJ1" s="49"/>
-      <c r="AK1" s="49"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="50"/>
+      <c r="M1" s="50"/>
+      <c r="N1" s="50"/>
+      <c r="O1" s="50"/>
+      <c r="P1" s="50"/>
+      <c r="Q1" s="50"/>
+      <c r="R1" s="50"/>
+      <c r="S1" s="50"/>
+      <c r="T1" s="50"/>
+      <c r="U1" s="50"/>
+      <c r="V1" s="50"/>
+      <c r="W1" s="50"/>
+      <c r="X1" s="50"/>
+      <c r="Y1" s="50"/>
+      <c r="Z1" s="50"/>
+      <c r="AA1" s="50"/>
+      <c r="AB1" s="50"/>
+      <c r="AC1" s="50"/>
+      <c r="AD1" s="50"/>
+      <c r="AE1" s="50"/>
+      <c r="AF1" s="50"/>
+      <c r="AG1" s="50"/>
+      <c r="AH1" s="50"/>
+      <c r="AI1" s="50"/>
+      <c r="AJ1" s="50"/>
+      <c r="AK1" s="50"/>
     </row>
     <row r="2" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="59" t="s">
+      <c r="A2" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="59"/>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="59"/>
-      <c r="H2" s="59"/>
-      <c r="I2" s="59"/>
-      <c r="J2" s="59"/>
-      <c r="K2" s="59"/>
-      <c r="L2" s="59"/>
-      <c r="M2" s="59"/>
-      <c r="N2" s="59"/>
-      <c r="O2" s="59"/>
-      <c r="P2" s="59"/>
-      <c r="Q2" s="59"/>
-      <c r="R2" s="59"/>
-      <c r="S2" s="59"/>
-      <c r="T2" s="59"/>
-      <c r="U2" s="59"/>
-      <c r="V2" s="59"/>
-      <c r="W2" s="59"/>
-      <c r="X2" s="59"/>
-      <c r="Y2" s="59"/>
-      <c r="Z2" s="59"/>
-      <c r="AA2" s="59"/>
-      <c r="AB2" s="59"/>
-      <c r="AC2" s="59"/>
-      <c r="AD2" s="59"/>
-      <c r="AE2" s="59"/>
-      <c r="AF2" s="59"/>
-      <c r="AG2" s="59"/>
-      <c r="AH2" s="59"/>
-      <c r="AI2" s="59"/>
-      <c r="AJ2" s="59"/>
-      <c r="AK2" s="59"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="51"/>
+      <c r="K2" s="51"/>
+      <c r="L2" s="51"/>
+      <c r="M2" s="51"/>
+      <c r="N2" s="51"/>
+      <c r="O2" s="51"/>
+      <c r="P2" s="51"/>
+      <c r="Q2" s="51"/>
+      <c r="R2" s="51"/>
+      <c r="S2" s="51"/>
+      <c r="T2" s="51"/>
+      <c r="U2" s="51"/>
+      <c r="V2" s="51"/>
+      <c r="W2" s="51"/>
+      <c r="X2" s="51"/>
+      <c r="Y2" s="51"/>
+      <c r="Z2" s="51"/>
+      <c r="AA2" s="51"/>
+      <c r="AB2" s="51"/>
+      <c r="AC2" s="51"/>
+      <c r="AD2" s="51"/>
+      <c r="AE2" s="51"/>
+      <c r="AF2" s="51"/>
+      <c r="AG2" s="51"/>
+      <c r="AH2" s="51"/>
+      <c r="AI2" s="51"/>
+      <c r="AJ2" s="51"/>
+      <c r="AK2" s="51"/>
     </row>
     <row r="3" spans="1:37" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:37" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="60" t="s">
+      <c r="A4" s="52" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="29" t="s">
@@ -14670,27 +14673,27 @@
       <c r="AE4" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="AF4" s="61" t="s">
+      <c r="AF4" s="53" t="s">
         <v>54</v>
       </c>
-      <c r="AG4" s="62" t="s">
+      <c r="AG4" s="54" t="s">
         <v>55</v>
       </c>
-      <c r="AH4" s="63" t="s">
+      <c r="AH4" s="55" t="s">
         <v>56</v>
       </c>
-      <c r="AI4" s="64" t="s">
+      <c r="AI4" s="56" t="s">
         <v>57</v>
       </c>
-      <c r="AJ4" s="65" t="s">
+      <c r="AJ4" s="57" t="s">
         <v>58</v>
       </c>
-      <c r="AK4" s="64" t="s">
+      <c r="AK4" s="56" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:37" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="60"/>
+      <c r="A5" s="52"/>
       <c r="B5" s="31">
         <v>1</v>
       </c>
@@ -14781,12 +14784,12 @@
       <c r="AE5" s="31">
         <v>30</v>
       </c>
-      <c r="AF5" s="61"/>
-      <c r="AG5" s="61"/>
-      <c r="AH5" s="61"/>
-      <c r="AI5" s="61"/>
-      <c r="AJ5" s="61"/>
-      <c r="AK5" s="61"/>
+      <c r="AF5" s="53"/>
+      <c r="AG5" s="53"/>
+      <c r="AH5" s="53"/>
+      <c r="AI5" s="53"/>
+      <c r="AJ5" s="53"/>
+      <c r="AK5" s="53"/>
     </row>
     <row r="6" spans="1:37" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="1:37" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -15537,45 +15540,45 @@
     </row>
     <row r="18" spans="1:37" ht="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="1:37" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="57" t="s">
+      <c r="A19" s="48" t="s">
         <v>76</v>
       </c>
-      <c r="B19" s="57"/>
-      <c r="C19" s="57"/>
-      <c r="D19" s="57"/>
-      <c r="E19" s="57"/>
-      <c r="F19" s="57"/>
-      <c r="G19" s="57"/>
-      <c r="H19" s="57"/>
-      <c r="I19" s="57"/>
-      <c r="J19" s="57"/>
-      <c r="K19" s="57"/>
-      <c r="L19" s="57"/>
-      <c r="M19" s="57"/>
-      <c r="N19" s="57"/>
-      <c r="O19" s="57"/>
-      <c r="P19" s="57"/>
-      <c r="Q19" s="57"/>
-      <c r="R19" s="57"/>
-      <c r="S19" s="57"/>
-      <c r="T19" s="57"/>
-      <c r="U19" s="57"/>
-      <c r="V19" s="57"/>
-      <c r="W19" s="57"/>
-      <c r="X19" s="57"/>
-      <c r="Y19" s="57"/>
-      <c r="Z19" s="57"/>
-      <c r="AA19" s="57"/>
-      <c r="AB19" s="57"/>
-      <c r="AC19" s="57"/>
-      <c r="AD19" s="57"/>
-      <c r="AE19" s="57"/>
-      <c r="AF19" s="57"/>
-      <c r="AG19" s="57"/>
-      <c r="AH19" s="57"/>
-      <c r="AI19" s="57"/>
-      <c r="AJ19" s="57"/>
-      <c r="AK19" s="57"/>
+      <c r="B19" s="48"/>
+      <c r="C19" s="48"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="48"/>
+      <c r="G19" s="48"/>
+      <c r="H19" s="48"/>
+      <c r="I19" s="48"/>
+      <c r="J19" s="48"/>
+      <c r="K19" s="48"/>
+      <c r="L19" s="48"/>
+      <c r="M19" s="48"/>
+      <c r="N19" s="48"/>
+      <c r="O19" s="48"/>
+      <c r="P19" s="48"/>
+      <c r="Q19" s="48"/>
+      <c r="R19" s="48"/>
+      <c r="S19" s="48"/>
+      <c r="T19" s="48"/>
+      <c r="U19" s="48"/>
+      <c r="V19" s="48"/>
+      <c r="W19" s="48"/>
+      <c r="X19" s="48"/>
+      <c r="Y19" s="48"/>
+      <c r="Z19" s="48"/>
+      <c r="AA19" s="48"/>
+      <c r="AB19" s="48"/>
+      <c r="AC19" s="48"/>
+      <c r="AD19" s="48"/>
+      <c r="AE19" s="48"/>
+      <c r="AF19" s="48"/>
+      <c r="AG19" s="48"/>
+      <c r="AH19" s="48"/>
+      <c r="AI19" s="48"/>
+      <c r="AJ19" s="48"/>
+      <c r="AK19" s="48"/>
     </row>
     <row r="20" spans="1:37" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
@@ -15934,10 +15937,10 @@
       </c>
     </row>
     <row r="31" spans="1:37" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="58" t="s">
+      <c r="A31" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="B31" s="58"/>
+      <c r="B31" s="49"/>
       <c r="C31" s="11">
         <f t="shared" ref="C31:H31" si="8">SUM(C21:C30)</f>
         <v>15300000</v>
@@ -15996,92 +15999,92 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="50" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
-      <c r="L1" s="49"/>
-      <c r="M1" s="49"/>
-      <c r="N1" s="49"/>
-      <c r="O1" s="49"/>
-      <c r="P1" s="49"/>
-      <c r="Q1" s="49"/>
-      <c r="R1" s="49"/>
-      <c r="S1" s="49"/>
-      <c r="T1" s="49"/>
-      <c r="U1" s="49"/>
-      <c r="V1" s="49"/>
-      <c r="W1" s="49"/>
-      <c r="X1" s="49"/>
-      <c r="Y1" s="49"/>
-      <c r="Z1" s="49"/>
-      <c r="AA1" s="49"/>
-      <c r="AB1" s="49"/>
-      <c r="AC1" s="49"/>
-      <c r="AD1" s="49"/>
-      <c r="AE1" s="49"/>
-      <c r="AF1" s="49"/>
-      <c r="AG1" s="49"/>
-      <c r="AH1" s="49"/>
-      <c r="AI1" s="49"/>
-      <c r="AJ1" s="49"/>
-      <c r="AK1" s="49"/>
-      <c r="AL1" s="49"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="50"/>
+      <c r="M1" s="50"/>
+      <c r="N1" s="50"/>
+      <c r="O1" s="50"/>
+      <c r="P1" s="50"/>
+      <c r="Q1" s="50"/>
+      <c r="R1" s="50"/>
+      <c r="S1" s="50"/>
+      <c r="T1" s="50"/>
+      <c r="U1" s="50"/>
+      <c r="V1" s="50"/>
+      <c r="W1" s="50"/>
+      <c r="X1" s="50"/>
+      <c r="Y1" s="50"/>
+      <c r="Z1" s="50"/>
+      <c r="AA1" s="50"/>
+      <c r="AB1" s="50"/>
+      <c r="AC1" s="50"/>
+      <c r="AD1" s="50"/>
+      <c r="AE1" s="50"/>
+      <c r="AF1" s="50"/>
+      <c r="AG1" s="50"/>
+      <c r="AH1" s="50"/>
+      <c r="AI1" s="50"/>
+      <c r="AJ1" s="50"/>
+      <c r="AK1" s="50"/>
+      <c r="AL1" s="50"/>
     </row>
     <row r="2" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="59" t="s">
+      <c r="A2" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="59"/>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="59"/>
-      <c r="H2" s="59"/>
-      <c r="I2" s="59"/>
-      <c r="J2" s="59"/>
-      <c r="K2" s="59"/>
-      <c r="L2" s="59"/>
-      <c r="M2" s="59"/>
-      <c r="N2" s="59"/>
-      <c r="O2" s="59"/>
-      <c r="P2" s="59"/>
-      <c r="Q2" s="59"/>
-      <c r="R2" s="59"/>
-      <c r="S2" s="59"/>
-      <c r="T2" s="59"/>
-      <c r="U2" s="59"/>
-      <c r="V2" s="59"/>
-      <c r="W2" s="59"/>
-      <c r="X2" s="59"/>
-      <c r="Y2" s="59"/>
-      <c r="Z2" s="59"/>
-      <c r="AA2" s="59"/>
-      <c r="AB2" s="59"/>
-      <c r="AC2" s="59"/>
-      <c r="AD2" s="59"/>
-      <c r="AE2" s="59"/>
-      <c r="AF2" s="59"/>
-      <c r="AG2" s="59"/>
-      <c r="AH2" s="59"/>
-      <c r="AI2" s="59"/>
-      <c r="AJ2" s="59"/>
-      <c r="AK2" s="59"/>
-      <c r="AL2" s="59"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="51"/>
+      <c r="K2" s="51"/>
+      <c r="L2" s="51"/>
+      <c r="M2" s="51"/>
+      <c r="N2" s="51"/>
+      <c r="O2" s="51"/>
+      <c r="P2" s="51"/>
+      <c r="Q2" s="51"/>
+      <c r="R2" s="51"/>
+      <c r="S2" s="51"/>
+      <c r="T2" s="51"/>
+      <c r="U2" s="51"/>
+      <c r="V2" s="51"/>
+      <c r="W2" s="51"/>
+      <c r="X2" s="51"/>
+      <c r="Y2" s="51"/>
+      <c r="Z2" s="51"/>
+      <c r="AA2" s="51"/>
+      <c r="AB2" s="51"/>
+      <c r="AC2" s="51"/>
+      <c r="AD2" s="51"/>
+      <c r="AE2" s="51"/>
+      <c r="AF2" s="51"/>
+      <c r="AG2" s="51"/>
+      <c r="AH2" s="51"/>
+      <c r="AI2" s="51"/>
+      <c r="AJ2" s="51"/>
+      <c r="AK2" s="51"/>
+      <c r="AL2" s="51"/>
     </row>
     <row r="3" spans="1:38" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="60" t="s">
+      <c r="A4" s="52" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="30" t="s">
@@ -16177,27 +16180,27 @@
       <c r="AF4" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="AG4" s="61" t="s">
+      <c r="AG4" s="53" t="s">
         <v>54</v>
       </c>
-      <c r="AH4" s="62" t="s">
+      <c r="AH4" s="54" t="s">
         <v>55</v>
       </c>
-      <c r="AI4" s="63" t="s">
+      <c r="AI4" s="55" t="s">
         <v>56</v>
       </c>
-      <c r="AJ4" s="64" t="s">
+      <c r="AJ4" s="56" t="s">
         <v>57</v>
       </c>
-      <c r="AK4" s="65" t="s">
+      <c r="AK4" s="57" t="s">
         <v>58</v>
       </c>
-      <c r="AL4" s="64" t="s">
+      <c r="AL4" s="56" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:38" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="60"/>
+      <c r="A5" s="52"/>
       <c r="B5" s="32">
         <v>1</v>
       </c>
@@ -16291,12 +16294,12 @@
       <c r="AF5" s="31">
         <v>31</v>
       </c>
-      <c r="AG5" s="61"/>
-      <c r="AH5" s="61"/>
-      <c r="AI5" s="61"/>
-      <c r="AJ5" s="61"/>
-      <c r="AK5" s="61"/>
-      <c r="AL5" s="61"/>
+      <c r="AG5" s="53"/>
+      <c r="AH5" s="53"/>
+      <c r="AI5" s="53"/>
+      <c r="AJ5" s="53"/>
+      <c r="AK5" s="53"/>
+      <c r="AL5" s="53"/>
     </row>
     <row r="6" spans="1:38" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="1:38" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -17061,46 +17064,46 @@
     </row>
     <row r="18" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="1:38" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="57" t="s">
+      <c r="A19" s="48" t="s">
         <v>79</v>
       </c>
-      <c r="B19" s="57"/>
-      <c r="C19" s="57"/>
-      <c r="D19" s="57"/>
-      <c r="E19" s="57"/>
-      <c r="F19" s="57"/>
-      <c r="G19" s="57"/>
-      <c r="H19" s="57"/>
-      <c r="I19" s="57"/>
-      <c r="J19" s="57"/>
-      <c r="K19" s="57"/>
-      <c r="L19" s="57"/>
-      <c r="M19" s="57"/>
-      <c r="N19" s="57"/>
-      <c r="O19" s="57"/>
-      <c r="P19" s="57"/>
-      <c r="Q19" s="57"/>
-      <c r="R19" s="57"/>
-      <c r="S19" s="57"/>
-      <c r="T19" s="57"/>
-      <c r="U19" s="57"/>
-      <c r="V19" s="57"/>
-      <c r="W19" s="57"/>
-      <c r="X19" s="57"/>
-      <c r="Y19" s="57"/>
-      <c r="Z19" s="57"/>
-      <c r="AA19" s="57"/>
-      <c r="AB19" s="57"/>
-      <c r="AC19" s="57"/>
-      <c r="AD19" s="57"/>
-      <c r="AE19" s="57"/>
-      <c r="AF19" s="57"/>
-      <c r="AG19" s="57"/>
-      <c r="AH19" s="57"/>
-      <c r="AI19" s="57"/>
-      <c r="AJ19" s="57"/>
-      <c r="AK19" s="57"/>
-      <c r="AL19" s="57"/>
+      <c r="B19" s="48"/>
+      <c r="C19" s="48"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="48"/>
+      <c r="G19" s="48"/>
+      <c r="H19" s="48"/>
+      <c r="I19" s="48"/>
+      <c r="J19" s="48"/>
+      <c r="K19" s="48"/>
+      <c r="L19" s="48"/>
+      <c r="M19" s="48"/>
+      <c r="N19" s="48"/>
+      <c r="O19" s="48"/>
+      <c r="P19" s="48"/>
+      <c r="Q19" s="48"/>
+      <c r="R19" s="48"/>
+      <c r="S19" s="48"/>
+      <c r="T19" s="48"/>
+      <c r="U19" s="48"/>
+      <c r="V19" s="48"/>
+      <c r="W19" s="48"/>
+      <c r="X19" s="48"/>
+      <c r="Y19" s="48"/>
+      <c r="Z19" s="48"/>
+      <c r="AA19" s="48"/>
+      <c r="AB19" s="48"/>
+      <c r="AC19" s="48"/>
+      <c r="AD19" s="48"/>
+      <c r="AE19" s="48"/>
+      <c r="AF19" s="48"/>
+      <c r="AG19" s="48"/>
+      <c r="AH19" s="48"/>
+      <c r="AI19" s="48"/>
+      <c r="AJ19" s="48"/>
+      <c r="AK19" s="48"/>
+      <c r="AL19" s="48"/>
     </row>
     <row r="20" spans="1:38" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
@@ -17459,10 +17462,10 @@
       </c>
     </row>
     <row r="31" spans="1:38" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="58" t="s">
+      <c r="A31" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="B31" s="58"/>
+      <c r="B31" s="49"/>
       <c r="C31" s="11">
         <f t="shared" ref="C31:H31" si="8">SUM(C21:C30)</f>
         <v>15300000</v>
@@ -17525,90 +17528,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
-      <c r="L1" s="49"/>
-      <c r="M1" s="49"/>
-      <c r="N1" s="49"/>
-      <c r="O1" s="49"/>
-      <c r="P1" s="49"/>
-      <c r="Q1" s="49"/>
-      <c r="R1" s="49"/>
-      <c r="S1" s="49"/>
-      <c r="T1" s="49"/>
-      <c r="U1" s="49"/>
-      <c r="V1" s="49"/>
-      <c r="W1" s="49"/>
-      <c r="X1" s="49"/>
-      <c r="Y1" s="49"/>
-      <c r="Z1" s="49"/>
-      <c r="AA1" s="49"/>
-      <c r="AB1" s="49"/>
-      <c r="AC1" s="49"/>
-      <c r="AD1" s="49"/>
-      <c r="AE1" s="49"/>
-      <c r="AF1" s="49"/>
-      <c r="AG1" s="49"/>
-      <c r="AH1" s="49"/>
-      <c r="AI1" s="49"/>
-      <c r="AJ1" s="49"/>
-      <c r="AK1" s="49"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="50"/>
+      <c r="M1" s="50"/>
+      <c r="N1" s="50"/>
+      <c r="O1" s="50"/>
+      <c r="P1" s="50"/>
+      <c r="Q1" s="50"/>
+      <c r="R1" s="50"/>
+      <c r="S1" s="50"/>
+      <c r="T1" s="50"/>
+      <c r="U1" s="50"/>
+      <c r="V1" s="50"/>
+      <c r="W1" s="50"/>
+      <c r="X1" s="50"/>
+      <c r="Y1" s="50"/>
+      <c r="Z1" s="50"/>
+      <c r="AA1" s="50"/>
+      <c r="AB1" s="50"/>
+      <c r="AC1" s="50"/>
+      <c r="AD1" s="50"/>
+      <c r="AE1" s="50"/>
+      <c r="AF1" s="50"/>
+      <c r="AG1" s="50"/>
+      <c r="AH1" s="50"/>
+      <c r="AI1" s="50"/>
+      <c r="AJ1" s="50"/>
+      <c r="AK1" s="50"/>
     </row>
     <row r="2" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="59" t="s">
+      <c r="A2" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="59"/>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="59"/>
-      <c r="H2" s="59"/>
-      <c r="I2" s="59"/>
-      <c r="J2" s="59"/>
-      <c r="K2" s="59"/>
-      <c r="L2" s="59"/>
-      <c r="M2" s="59"/>
-      <c r="N2" s="59"/>
-      <c r="O2" s="59"/>
-      <c r="P2" s="59"/>
-      <c r="Q2" s="59"/>
-      <c r="R2" s="59"/>
-      <c r="S2" s="59"/>
-      <c r="T2" s="59"/>
-      <c r="U2" s="59"/>
-      <c r="V2" s="59"/>
-      <c r="W2" s="59"/>
-      <c r="X2" s="59"/>
-      <c r="Y2" s="59"/>
-      <c r="Z2" s="59"/>
-      <c r="AA2" s="59"/>
-      <c r="AB2" s="59"/>
-      <c r="AC2" s="59"/>
-      <c r="AD2" s="59"/>
-      <c r="AE2" s="59"/>
-      <c r="AF2" s="59"/>
-      <c r="AG2" s="59"/>
-      <c r="AH2" s="59"/>
-      <c r="AI2" s="59"/>
-      <c r="AJ2" s="59"/>
-      <c r="AK2" s="59"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="51"/>
+      <c r="K2" s="51"/>
+      <c r="L2" s="51"/>
+      <c r="M2" s="51"/>
+      <c r="N2" s="51"/>
+      <c r="O2" s="51"/>
+      <c r="P2" s="51"/>
+      <c r="Q2" s="51"/>
+      <c r="R2" s="51"/>
+      <c r="S2" s="51"/>
+      <c r="T2" s="51"/>
+      <c r="U2" s="51"/>
+      <c r="V2" s="51"/>
+      <c r="W2" s="51"/>
+      <c r="X2" s="51"/>
+      <c r="Y2" s="51"/>
+      <c r="Z2" s="51"/>
+      <c r="AA2" s="51"/>
+      <c r="AB2" s="51"/>
+      <c r="AC2" s="51"/>
+      <c r="AD2" s="51"/>
+      <c r="AE2" s="51"/>
+      <c r="AF2" s="51"/>
+      <c r="AG2" s="51"/>
+      <c r="AH2" s="51"/>
+      <c r="AI2" s="51"/>
+      <c r="AJ2" s="51"/>
+      <c r="AK2" s="51"/>
     </row>
     <row r="3" spans="1:37" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:37" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="60" t="s">
+      <c r="A4" s="52" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="29" t="s">
@@ -17701,27 +17704,27 @@
       <c r="AE4" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="AF4" s="61" t="s">
+      <c r="AF4" s="53" t="s">
         <v>54</v>
       </c>
-      <c r="AG4" s="62" t="s">
+      <c r="AG4" s="54" t="s">
         <v>55</v>
       </c>
-      <c r="AH4" s="63" t="s">
+      <c r="AH4" s="55" t="s">
         <v>56</v>
       </c>
-      <c r="AI4" s="64" t="s">
+      <c r="AI4" s="56" t="s">
         <v>57</v>
       </c>
-      <c r="AJ4" s="65" t="s">
+      <c r="AJ4" s="57" t="s">
         <v>58</v>
       </c>
-      <c r="AK4" s="64" t="s">
+      <c r="AK4" s="56" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:37" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="60"/>
+      <c r="A5" s="52"/>
       <c r="B5" s="31">
         <v>1</v>
       </c>
@@ -17812,12 +17815,12 @@
       <c r="AE5" s="31">
         <v>30</v>
       </c>
-      <c r="AF5" s="61"/>
-      <c r="AG5" s="61"/>
-      <c r="AH5" s="61"/>
-      <c r="AI5" s="61"/>
-      <c r="AJ5" s="61"/>
-      <c r="AK5" s="61"/>
+      <c r="AF5" s="53"/>
+      <c r="AG5" s="53"/>
+      <c r="AH5" s="53"/>
+      <c r="AI5" s="53"/>
+      <c r="AJ5" s="53"/>
+      <c r="AK5" s="53"/>
     </row>
     <row r="6" spans="1:37" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="1:37" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -18676,45 +18679,45 @@
     </row>
     <row r="18" spans="1:37" ht="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="1:37" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="57" t="s">
+      <c r="A19" s="48" t="s">
         <v>82</v>
       </c>
-      <c r="B19" s="57"/>
-      <c r="C19" s="57"/>
-      <c r="D19" s="57"/>
-      <c r="E19" s="57"/>
-      <c r="F19" s="57"/>
-      <c r="G19" s="57"/>
-      <c r="H19" s="57"/>
-      <c r="I19" s="57"/>
-      <c r="J19" s="57"/>
-      <c r="K19" s="57"/>
-      <c r="L19" s="57"/>
-      <c r="M19" s="57"/>
-      <c r="N19" s="57"/>
-      <c r="O19" s="57"/>
-      <c r="P19" s="57"/>
-      <c r="Q19" s="57"/>
-      <c r="R19" s="57"/>
-      <c r="S19" s="57"/>
-      <c r="T19" s="57"/>
-      <c r="U19" s="57"/>
-      <c r="V19" s="57"/>
-      <c r="W19" s="57"/>
-      <c r="X19" s="57"/>
-      <c r="Y19" s="57"/>
-      <c r="Z19" s="57"/>
-      <c r="AA19" s="57"/>
-      <c r="AB19" s="57"/>
-      <c r="AC19" s="57"/>
-      <c r="AD19" s="57"/>
-      <c r="AE19" s="57"/>
-      <c r="AF19" s="57"/>
-      <c r="AG19" s="57"/>
-      <c r="AH19" s="57"/>
-      <c r="AI19" s="57"/>
-      <c r="AJ19" s="57"/>
-      <c r="AK19" s="57"/>
+      <c r="B19" s="48"/>
+      <c r="C19" s="48"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="48"/>
+      <c r="G19" s="48"/>
+      <c r="H19" s="48"/>
+      <c r="I19" s="48"/>
+      <c r="J19" s="48"/>
+      <c r="K19" s="48"/>
+      <c r="L19" s="48"/>
+      <c r="M19" s="48"/>
+      <c r="N19" s="48"/>
+      <c r="O19" s="48"/>
+      <c r="P19" s="48"/>
+      <c r="Q19" s="48"/>
+      <c r="R19" s="48"/>
+      <c r="S19" s="48"/>
+      <c r="T19" s="48"/>
+      <c r="U19" s="48"/>
+      <c r="V19" s="48"/>
+      <c r="W19" s="48"/>
+      <c r="X19" s="48"/>
+      <c r="Y19" s="48"/>
+      <c r="Z19" s="48"/>
+      <c r="AA19" s="48"/>
+      <c r="AB19" s="48"/>
+      <c r="AC19" s="48"/>
+      <c r="AD19" s="48"/>
+      <c r="AE19" s="48"/>
+      <c r="AF19" s="48"/>
+      <c r="AG19" s="48"/>
+      <c r="AH19" s="48"/>
+      <c r="AI19" s="48"/>
+      <c r="AJ19" s="48"/>
+      <c r="AK19" s="48"/>
     </row>
     <row r="20" spans="1:37" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
@@ -19073,10 +19076,10 @@
       </c>
     </row>
     <row r="31" spans="1:37" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="58" t="s">
+      <c r="A31" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="B31" s="58"/>
+      <c r="B31" s="49"/>
       <c r="C31" s="11">
         <f t="shared" ref="C31:H31" si="8">SUM(C21:C30)</f>
         <v>15300000</v>
@@ -19135,92 +19138,92 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="50" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
-      <c r="L1" s="49"/>
-      <c r="M1" s="49"/>
-      <c r="N1" s="49"/>
-      <c r="O1" s="49"/>
-      <c r="P1" s="49"/>
-      <c r="Q1" s="49"/>
-      <c r="R1" s="49"/>
-      <c r="S1" s="49"/>
-      <c r="T1" s="49"/>
-      <c r="U1" s="49"/>
-      <c r="V1" s="49"/>
-      <c r="W1" s="49"/>
-      <c r="X1" s="49"/>
-      <c r="Y1" s="49"/>
-      <c r="Z1" s="49"/>
-      <c r="AA1" s="49"/>
-      <c r="AB1" s="49"/>
-      <c r="AC1" s="49"/>
-      <c r="AD1" s="49"/>
-      <c r="AE1" s="49"/>
-      <c r="AF1" s="49"/>
-      <c r="AG1" s="49"/>
-      <c r="AH1" s="49"/>
-      <c r="AI1" s="49"/>
-      <c r="AJ1" s="49"/>
-      <c r="AK1" s="49"/>
-      <c r="AL1" s="49"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="50"/>
+      <c r="M1" s="50"/>
+      <c r="N1" s="50"/>
+      <c r="O1" s="50"/>
+      <c r="P1" s="50"/>
+      <c r="Q1" s="50"/>
+      <c r="R1" s="50"/>
+      <c r="S1" s="50"/>
+      <c r="T1" s="50"/>
+      <c r="U1" s="50"/>
+      <c r="V1" s="50"/>
+      <c r="W1" s="50"/>
+      <c r="X1" s="50"/>
+      <c r="Y1" s="50"/>
+      <c r="Z1" s="50"/>
+      <c r="AA1" s="50"/>
+      <c r="AB1" s="50"/>
+      <c r="AC1" s="50"/>
+      <c r="AD1" s="50"/>
+      <c r="AE1" s="50"/>
+      <c r="AF1" s="50"/>
+      <c r="AG1" s="50"/>
+      <c r="AH1" s="50"/>
+      <c r="AI1" s="50"/>
+      <c r="AJ1" s="50"/>
+      <c r="AK1" s="50"/>
+      <c r="AL1" s="50"/>
     </row>
     <row r="2" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="59" t="s">
+      <c r="A2" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="59"/>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="59"/>
-      <c r="H2" s="59"/>
-      <c r="I2" s="59"/>
-      <c r="J2" s="59"/>
-      <c r="K2" s="59"/>
-      <c r="L2" s="59"/>
-      <c r="M2" s="59"/>
-      <c r="N2" s="59"/>
-      <c r="O2" s="59"/>
-      <c r="P2" s="59"/>
-      <c r="Q2" s="59"/>
-      <c r="R2" s="59"/>
-      <c r="S2" s="59"/>
-      <c r="T2" s="59"/>
-      <c r="U2" s="59"/>
-      <c r="V2" s="59"/>
-      <c r="W2" s="59"/>
-      <c r="X2" s="59"/>
-      <c r="Y2" s="59"/>
-      <c r="Z2" s="59"/>
-      <c r="AA2" s="59"/>
-      <c r="AB2" s="59"/>
-      <c r="AC2" s="59"/>
-      <c r="AD2" s="59"/>
-      <c r="AE2" s="59"/>
-      <c r="AF2" s="59"/>
-      <c r="AG2" s="59"/>
-      <c r="AH2" s="59"/>
-      <c r="AI2" s="59"/>
-      <c r="AJ2" s="59"/>
-      <c r="AK2" s="59"/>
-      <c r="AL2" s="59"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="51"/>
+      <c r="K2" s="51"/>
+      <c r="L2" s="51"/>
+      <c r="M2" s="51"/>
+      <c r="N2" s="51"/>
+      <c r="O2" s="51"/>
+      <c r="P2" s="51"/>
+      <c r="Q2" s="51"/>
+      <c r="R2" s="51"/>
+      <c r="S2" s="51"/>
+      <c r="T2" s="51"/>
+      <c r="U2" s="51"/>
+      <c r="V2" s="51"/>
+      <c r="W2" s="51"/>
+      <c r="X2" s="51"/>
+      <c r="Y2" s="51"/>
+      <c r="Z2" s="51"/>
+      <c r="AA2" s="51"/>
+      <c r="AB2" s="51"/>
+      <c r="AC2" s="51"/>
+      <c r="AD2" s="51"/>
+      <c r="AE2" s="51"/>
+      <c r="AF2" s="51"/>
+      <c r="AG2" s="51"/>
+      <c r="AH2" s="51"/>
+      <c r="AI2" s="51"/>
+      <c r="AJ2" s="51"/>
+      <c r="AK2" s="51"/>
+      <c r="AL2" s="51"/>
     </row>
     <row r="3" spans="1:38" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="60" t="s">
+      <c r="A4" s="52" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="29" t="s">
@@ -19316,27 +19319,27 @@
       <c r="AF4" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="AG4" s="61" t="s">
+      <c r="AG4" s="53" t="s">
         <v>54</v>
       </c>
-      <c r="AH4" s="62" t="s">
+      <c r="AH4" s="54" t="s">
         <v>55</v>
       </c>
-      <c r="AI4" s="63" t="s">
+      <c r="AI4" s="55" t="s">
         <v>56</v>
       </c>
-      <c r="AJ4" s="64" t="s">
+      <c r="AJ4" s="56" t="s">
         <v>57</v>
       </c>
-      <c r="AK4" s="65" t="s">
+      <c r="AK4" s="57" t="s">
         <v>58</v>
       </c>
-      <c r="AL4" s="64" t="s">
+      <c r="AL4" s="56" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:38" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="60"/>
+      <c r="A5" s="52"/>
       <c r="B5" s="31">
         <v>1</v>
       </c>
@@ -19430,12 +19433,12 @@
       <c r="AF5" s="32">
         <v>31</v>
       </c>
-      <c r="AG5" s="61"/>
-      <c r="AH5" s="61"/>
-      <c r="AI5" s="61"/>
-      <c r="AJ5" s="61"/>
-      <c r="AK5" s="61"/>
-      <c r="AL5" s="61"/>
+      <c r="AG5" s="53"/>
+      <c r="AH5" s="53"/>
+      <c r="AI5" s="53"/>
+      <c r="AJ5" s="53"/>
+      <c r="AK5" s="53"/>
+      <c r="AL5" s="53"/>
     </row>
     <row r="6" spans="1:38" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="1:38" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -19444,9 +19447,13 @@
         <v xml:space="preserve">أبو بكر </v>
       </c>
       <c r="B7" s="33"/>
-      <c r="C7" s="33"/>
+      <c r="C7" s="33" t="s">
+        <v>39</v>
+      </c>
       <c r="D7" s="34"/>
-      <c r="E7" s="33"/>
+      <c r="E7" s="33" t="s">
+        <v>39</v>
+      </c>
       <c r="F7" s="33"/>
       <c r="G7" s="33"/>
       <c r="H7" s="33"/>
@@ -19476,7 +19483,7 @@
       <c r="AF7" s="34"/>
       <c r="AG7" s="35">
         <f t="shared" ref="AG7:AG16" si="0">COUNTIF(B7:AF7,"غ")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH7" s="36">
         <f t="shared" ref="AH7:AH16" si="1">SUMIF(B7:AF7,"&gt;"&amp;0)+SUMIF(B7:AF7,"&lt;"&amp;0)</f>
@@ -19488,15 +19495,15 @@
       </c>
       <c r="AJ7" s="38">
         <f>IF('بيانات الموظفين'!C5="","-",31-AG7)</f>
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="AK7" s="6">
         <f>IF('بيانات الموظفين'!C5="","-",ROUND(('بيانات الموظفين'!C5/31)*AG7,2))</f>
-        <v>0</v>
+        <v>451612.9</v>
       </c>
       <c r="AL7" s="39">
         <f>IF('بيانات الموظفين'!C5="","-",ROUND('بيانات الموظفين'!C5+ROUND('بيانات الموظفين'!C5/30,2)+IF(ISNUMBER(AI7),AI7,0)-IF(ISNUMBER(AK7),AK7,0),2))</f>
-        <v>7233333.3300000001</v>
+        <v>6781720.4299999997</v>
       </c>
     </row>
     <row r="8" spans="1:38" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -19504,11 +19511,19 @@
         <f>'بيانات الموظفين'!B6</f>
         <v>هيثم صمادي</v>
       </c>
-      <c r="B8" s="40"/>
-      <c r="C8" s="40"/>
+      <c r="B8" s="40">
+        <v>0.5</v>
+      </c>
+      <c r="C8" s="40">
+        <v>1.5</v>
+      </c>
       <c r="D8" s="34"/>
-      <c r="E8" s="40"/>
-      <c r="F8" s="40"/>
+      <c r="E8" s="40" t="s">
+        <v>101</v>
+      </c>
+      <c r="F8" s="40">
+        <v>-2</v>
+      </c>
       <c r="G8" s="40"/>
       <c r="H8" s="40"/>
       <c r="I8" s="40"/>
@@ -19565,11 +19580,15 @@
         <f>'بيانات الموظفين'!B7</f>
         <v>حسام كبريتة</v>
       </c>
-      <c r="B9" s="33"/>
+      <c r="B9" s="33">
+        <v>0.5</v>
+      </c>
       <c r="C9" s="33"/>
       <c r="D9" s="34"/>
       <c r="E9" s="33"/>
-      <c r="F9" s="33"/>
+      <c r="F9" s="33">
+        <v>-1</v>
+      </c>
       <c r="G9" s="33"/>
       <c r="H9" s="33"/>
       <c r="I9" s="33"/>
@@ -19602,11 +19621,11 @@
       </c>
       <c r="AH9" s="36">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AI9" s="37" t="str">
+        <v>-0.5</v>
+      </c>
+      <c r="AI9" s="37">
         <f>IF(OR('بيانات الموظفين'!C7="",NOT(ISNUMBER('بيانات الموظفين'!G2)),AH9=0),"-",ROUND(AH9*(('بيانات الموظفين'!C7/31)/'بيانات الموظفين'!G2),2))</f>
-        <v>-</v>
+        <v>-4480.29</v>
       </c>
       <c r="AJ9" s="38">
         <f>IF('بيانات الموظفين'!C7="","-",31-AG9)</f>
@@ -19618,7 +19637,7 @@
       </c>
       <c r="AL9" s="39">
         <f>IF('بيانات الموظفين'!C7="","-",ROUND('بيانات الموظفين'!C7+ROUND('بيانات الموظفين'!C7/30,2)+IF(ISNUMBER(AI9),AI9,0)-IF(ISNUMBER(AK9),AK9,0),2))</f>
-        <v>2583333.33</v>
+        <v>2578853.04</v>
       </c>
     </row>
     <row r="10" spans="1:38" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -19630,7 +19649,9 @@
       <c r="C10" s="40"/>
       <c r="D10" s="34"/>
       <c r="E10" s="40"/>
-      <c r="F10" s="40"/>
+      <c r="F10" s="40">
+        <v>1</v>
+      </c>
       <c r="G10" s="40"/>
       <c r="H10" s="40"/>
       <c r="I10" s="40"/>
@@ -19663,11 +19684,11 @@
       </c>
       <c r="AH10" s="36">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AI10" s="37" t="str">
+        <v>1</v>
+      </c>
+      <c r="AI10" s="37">
         <f>IF(OR('بيانات الموظفين'!C8="",NOT(ISNUMBER('بيانات الموظفين'!G2)),AH10=0),"-",ROUND(AH10*(('بيانات الموظفين'!C8/31)/'بيانات الموظفين'!G2),2))</f>
-        <v>-</v>
+        <v>2867.38</v>
       </c>
       <c r="AJ10" s="38">
         <f>IF('بيانات الموظفين'!C8="","-",31-AG10)</f>
@@ -19679,7 +19700,7 @@
       </c>
       <c r="AL10" s="39">
         <f>IF('بيانات الموظفين'!C8="","-",ROUND('بيانات الموظفين'!C8+ROUND('بيانات الموظفين'!C8/30,2)+IF(ISNUMBER(AI10),AI10,0)-IF(ISNUMBER(AK10),AK10,0),2))</f>
-        <v>826666.67</v>
+        <v>829534.05</v>
       </c>
     </row>
     <row r="11" spans="1:38" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -19691,7 +19712,9 @@
       <c r="C11" s="33"/>
       <c r="D11" s="34"/>
       <c r="E11" s="33"/>
-      <c r="F11" s="33"/>
+      <c r="F11" s="33">
+        <v>-2</v>
+      </c>
       <c r="G11" s="33"/>
       <c r="H11" s="33"/>
       <c r="I11" s="33"/>
@@ -19724,11 +19747,11 @@
       </c>
       <c r="AH11" s="36">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AI11" s="37" t="str">
+        <v>-2</v>
+      </c>
+      <c r="AI11" s="37">
         <f>IF(OR('بيانات الموظفين'!C9="",NOT(ISNUMBER('بيانات الموظفين'!G2)),AH11=0),"-",ROUND(AH11*(('بيانات الموظفين'!C9/31)/'بيانات الموظفين'!G2),2))</f>
-        <v>-</v>
+        <v>-14336.92</v>
       </c>
       <c r="AJ11" s="38">
         <f>IF('بيانات الموظفين'!C9="","-",31-AG11)</f>
@@ -19740,7 +19763,7 @@
       </c>
       <c r="AL11" s="39">
         <f>IF('بيانات الموظفين'!C9="","-",ROUND('بيانات الموظفين'!C9+ROUND('بيانات الموظفين'!C9/30,2)+IF(ISNUMBER(AI11),AI11,0)-IF(ISNUMBER(AK11),AK11,0),2))</f>
-        <v>2066666.67</v>
+        <v>2052329.75</v>
       </c>
     </row>
     <row r="12" spans="1:38" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -20058,7 +20081,7 @@
       </c>
       <c r="C17" s="41">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" s="41">
         <f t="shared" si="2"/>
@@ -20066,7 +20089,7 @@
       </c>
       <c r="E17" s="41">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" s="41">
         <f t="shared" si="2"/>
@@ -20178,68 +20201,68 @@
       </c>
       <c r="AG17" s="41">
         <f>SUM(AG7:AG16)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH17" s="42">
         <f>SUM(AH7:AH16)</f>
-        <v>0</v>
+        <v>-1.5</v>
       </c>
       <c r="AI17" s="43">
         <f>SUM(AI7:AI16)</f>
-        <v>0</v>
+        <v>-15949.83</v>
       </c>
       <c r="AJ17" s="44"/>
       <c r="AK17" s="43">
         <f>SUM(AK7:AK16)</f>
-        <v>0</v>
+        <v>451612.9</v>
       </c>
       <c r="AL17" s="43">
         <f>SUM(AL7:AL16)</f>
-        <v>15810000</v>
+        <v>15342437.27</v>
       </c>
     </row>
     <row r="18" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="1:38" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="57" t="s">
+      <c r="A19" s="48" t="s">
         <v>85</v>
       </c>
-      <c r="B19" s="57"/>
-      <c r="C19" s="57"/>
-      <c r="D19" s="57"/>
-      <c r="E19" s="57"/>
-      <c r="F19" s="57"/>
-      <c r="G19" s="57"/>
-      <c r="H19" s="57"/>
-      <c r="I19" s="57"/>
-      <c r="J19" s="57"/>
-      <c r="K19" s="57"/>
-      <c r="L19" s="57"/>
-      <c r="M19" s="57"/>
-      <c r="N19" s="57"/>
-      <c r="O19" s="57"/>
-      <c r="P19" s="57"/>
-      <c r="Q19" s="57"/>
-      <c r="R19" s="57"/>
-      <c r="S19" s="57"/>
-      <c r="T19" s="57"/>
-      <c r="U19" s="57"/>
-      <c r="V19" s="57"/>
-      <c r="W19" s="57"/>
-      <c r="X19" s="57"/>
-      <c r="Y19" s="57"/>
-      <c r="Z19" s="57"/>
-      <c r="AA19" s="57"/>
-      <c r="AB19" s="57"/>
-      <c r="AC19" s="57"/>
-      <c r="AD19" s="57"/>
-      <c r="AE19" s="57"/>
-      <c r="AF19" s="57"/>
-      <c r="AG19" s="57"/>
-      <c r="AH19" s="57"/>
-      <c r="AI19" s="57"/>
-      <c r="AJ19" s="57"/>
-      <c r="AK19" s="57"/>
-      <c r="AL19" s="57"/>
+      <c r="B19" s="48"/>
+      <c r="C19" s="48"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="48"/>
+      <c r="G19" s="48"/>
+      <c r="H19" s="48"/>
+      <c r="I19" s="48"/>
+      <c r="J19" s="48"/>
+      <c r="K19" s="48"/>
+      <c r="L19" s="48"/>
+      <c r="M19" s="48"/>
+      <c r="N19" s="48"/>
+      <c r="O19" s="48"/>
+      <c r="P19" s="48"/>
+      <c r="Q19" s="48"/>
+      <c r="R19" s="48"/>
+      <c r="S19" s="48"/>
+      <c r="T19" s="48"/>
+      <c r="U19" s="48"/>
+      <c r="V19" s="48"/>
+      <c r="W19" s="48"/>
+      <c r="X19" s="48"/>
+      <c r="Y19" s="48"/>
+      <c r="Z19" s="48"/>
+      <c r="AA19" s="48"/>
+      <c r="AB19" s="48"/>
+      <c r="AC19" s="48"/>
+      <c r="AD19" s="48"/>
+      <c r="AE19" s="48"/>
+      <c r="AF19" s="48"/>
+      <c r="AG19" s="48"/>
+      <c r="AH19" s="48"/>
+      <c r="AI19" s="48"/>
+      <c r="AJ19" s="48"/>
+      <c r="AK19" s="48"/>
+      <c r="AL19" s="48"/>
     </row>
     <row r="20" spans="1:38" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
@@ -20281,11 +20304,11 @@
       </c>
       <c r="D21" s="45">
         <f t="shared" ref="D21:D30" si="3">AG7</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E21" s="6">
         <f t="shared" ref="E21:E30" si="4">AK7</f>
-        <v>0</v>
+        <v>451612.9</v>
       </c>
       <c r="F21" s="46">
         <f t="shared" ref="F21:F30" si="5">AH7</f>
@@ -20297,7 +20320,7 @@
       </c>
       <c r="H21" s="39">
         <f t="shared" ref="H21:H30" si="7">AL7</f>
-        <v>7233333.3300000001</v>
+        <v>6781720.4299999997</v>
       </c>
     </row>
     <row r="22" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20355,15 +20378,15 @@
       </c>
       <c r="F23" s="46">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="G23" s="37" t="str">
+        <v>-0.5</v>
+      </c>
+      <c r="G23" s="37">
         <f t="shared" si="6"/>
-        <v>-</v>
+        <v>-4480.29</v>
       </c>
       <c r="H23" s="39">
         <f t="shared" si="7"/>
-        <v>2583333.33</v>
+        <v>2578853.04</v>
       </c>
     </row>
     <row r="24" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20388,15 +20411,15 @@
       </c>
       <c r="F24" s="46">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="G24" s="37" t="str">
+        <v>1</v>
+      </c>
+      <c r="G24" s="37">
         <f t="shared" si="6"/>
-        <v>-</v>
+        <v>2867.38</v>
       </c>
       <c r="H24" s="39">
         <f t="shared" si="7"/>
-        <v>826666.67</v>
+        <v>829534.05</v>
       </c>
     </row>
     <row r="25" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20421,15 +20444,15 @@
       </c>
       <c r="F25" s="46">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="G25" s="37" t="str">
+        <v>-2</v>
+      </c>
+      <c r="G25" s="37">
         <f t="shared" si="6"/>
-        <v>-</v>
+        <v>-14336.92</v>
       </c>
       <c r="H25" s="39">
         <f t="shared" si="7"/>
-        <v>2066666.67</v>
+        <v>2052329.75</v>
       </c>
     </row>
     <row r="26" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20598,33 +20621,33 @@
       </c>
     </row>
     <row r="31" spans="1:38" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="58" t="s">
+      <c r="A31" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="B31" s="58"/>
+      <c r="B31" s="49"/>
       <c r="C31" s="11">
         <f t="shared" ref="C31:H31" si="8">SUM(C21:C30)</f>
         <v>15300000</v>
       </c>
       <c r="D31" s="47">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E31" s="12">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>451612.9</v>
       </c>
       <c r="F31" s="47">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>-1.5</v>
       </c>
       <c r="G31" s="12">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>-15949.83</v>
       </c>
       <c r="H31" s="12">
         <f t="shared" si="8"/>
-        <v>15810000</v>
+        <v>15342437.27</v>
       </c>
     </row>
   </sheetData>

--- a/ضبط_رواتب_الموظفين.xlsx
+++ b/ضبط_رواتب_الموظفين.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DeLL\Desktop\ملفات خاصة بالمعمل ووظائفه\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E71CCEFA-02BA-442B-B2A6-E831F6111005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{695BA1AE-CFA5-437A-929E-65B2C226B4BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="8">يوليو!$1:$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">يونيو!$1:$5</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="706" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="102">
   <si>
     <t>الملخص السنوي الشامل — 2026</t>
   </si>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="J5" s="5">
         <f>IF(ISNUMBER(يوليو!AL7),يوليو!AL7,"")</f>
-        <v>6781720.4299999997</v>
+        <v>6555913.9800000004</v>
       </c>
       <c r="K5" s="5">
         <f>IF(ISNUMBER(أغسطس!AL7),أغسطس!AL7,"")</f>
@@ -1387,11 +1387,11 @@
       </c>
       <c r="P5" s="6">
         <f>IF(ISNUMBER(يناير!AK7),يناير!AK7,0)+IF(ISNUMBER(فبراير!AH7),فبراير!AH7,0)+IF(ISNUMBER(مارس!AK7),مارس!AK7,0)+IF(ISNUMBER(أبريل!AJ7),أبريل!AJ7,0)+IF(ISNUMBER(مايو!AK7),مايو!AK7,0)+IF(ISNUMBER(يونيو!AJ7),يونيو!AJ7,0)+IF(ISNUMBER(يوليو!AK7),يوليو!AK7,0)+IF(ISNUMBER(أغسطس!AK7),أغسطس!AK7,0)+IF(ISNUMBER(سبتمبر!AJ7),سبتمبر!AJ7,0)+IF(ISNUMBER(أكتوبر!AK7),أكتوبر!AK7,0)+IF(ISNUMBER(نوفمبر!AJ7),نوفمبر!AJ7,0)+IF(ISNUMBER(ديسمبر!AK7),ديسمبر!AK7,0)</f>
-        <v>1151612.8999999999</v>
+        <v>1377419.35</v>
       </c>
       <c r="Q5" s="7">
         <f t="shared" ref="Q5:Q14" si="0">IFERROR(SUM(D5:O5),"")</f>
-        <v>84481720.409999996</v>
+        <v>84255913.959999993</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="J15" s="11">
         <f t="shared" si="1"/>
-        <v>15342437.27</v>
+        <v>15116630.82</v>
       </c>
       <c r="K15" s="11">
         <f t="shared" si="1"/>
@@ -2074,11 +2074,11 @@
       </c>
       <c r="P15" s="12">
         <f t="shared" si="1"/>
-        <v>3304946.2399999998</v>
+        <v>3530752.69</v>
       </c>
       <c r="Q15" s="12">
         <f t="shared" si="1"/>
-        <v>183822252.06999999</v>
+        <v>183596445.62</v>
       </c>
     </row>
   </sheetData>
@@ -19458,7 +19458,9 @@
       <c r="G7" s="33"/>
       <c r="H7" s="33"/>
       <c r="I7" s="33"/>
-      <c r="J7" s="33"/>
+      <c r="J7" s="33" t="s">
+        <v>39</v>
+      </c>
       <c r="K7" s="34"/>
       <c r="L7" s="33"/>
       <c r="M7" s="33"/>
@@ -19483,7 +19485,7 @@
       <c r="AF7" s="34"/>
       <c r="AG7" s="35">
         <f t="shared" ref="AG7:AG16" si="0">COUNTIF(B7:AF7,"غ")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH7" s="36">
         <f t="shared" ref="AH7:AH16" si="1">SUMIF(B7:AF7,"&gt;"&amp;0)+SUMIF(B7:AF7,"&lt;"&amp;0)</f>
@@ -19495,15 +19497,15 @@
       </c>
       <c r="AJ7" s="38">
         <f>IF('بيانات الموظفين'!C5="","-",31-AG7)</f>
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK7" s="6">
         <f>IF('بيانات الموظفين'!C5="","-",ROUND(('بيانات الموظفين'!C5/31)*AG7,2))</f>
-        <v>451612.9</v>
+        <v>677419.35</v>
       </c>
       <c r="AL7" s="39">
         <f>IF('بيانات الموظفين'!C5="","-",ROUND('بيانات الموظفين'!C5+ROUND('بيانات الموظفين'!C5/30,2)+IF(ISNUMBER(AI7),AI7,0)-IF(ISNUMBER(AK7),AK7,0),2))</f>
-        <v>6781720.4299999997</v>
+        <v>6555913.9800000004</v>
       </c>
     </row>
     <row r="8" spans="1:38" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -20109,7 +20111,7 @@
       </c>
       <c r="J17" s="41">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" s="41">
         <f t="shared" si="2"/>
@@ -20201,7 +20203,7 @@
       </c>
       <c r="AG17" s="41">
         <f>SUM(AG7:AG16)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH17" s="42">
         <f>SUM(AH7:AH16)</f>
@@ -20214,11 +20216,11 @@
       <c r="AJ17" s="44"/>
       <c r="AK17" s="43">
         <f>SUM(AK7:AK16)</f>
-        <v>451612.9</v>
+        <v>677419.35</v>
       </c>
       <c r="AL17" s="43">
         <f>SUM(AL7:AL16)</f>
-        <v>15342437.27</v>
+        <v>15116630.82</v>
       </c>
     </row>
     <row r="18" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -20304,11 +20306,11 @@
       </c>
       <c r="D21" s="45">
         <f t="shared" ref="D21:D30" si="3">AG7</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E21" s="6">
         <f t="shared" ref="E21:E30" si="4">AK7</f>
-        <v>451612.9</v>
+        <v>677419.35</v>
       </c>
       <c r="F21" s="46">
         <f t="shared" ref="F21:F30" si="5">AH7</f>
@@ -20320,7 +20322,7 @@
       </c>
       <c r="H21" s="39">
         <f t="shared" ref="H21:H30" si="7">AL7</f>
-        <v>6781720.4299999997</v>
+        <v>6555913.9800000004</v>
       </c>
     </row>
     <row r="22" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20631,11 +20633,11 @@
       </c>
       <c r="D31" s="47">
         <f t="shared" si="8"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E31" s="12">
         <f t="shared" si="8"/>
-        <v>451612.9</v>
+        <v>677419.35</v>
       </c>
       <c r="F31" s="47">
         <f t="shared" si="8"/>
@@ -20647,7 +20649,7 @@
       </c>
       <c r="H31" s="12">
         <f t="shared" si="8"/>
-        <v>15342437.27</v>
+        <v>15116630.82</v>
       </c>
     </row>
   </sheetData>

--- a/ضبط_رواتب_الموظفين.xlsx
+++ b/ضبط_رواتب_الموظفين.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DeLL\Desktop\ملفات خاصة بالمعمل ووظائفه\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{695BA1AE-CFA5-437A-929E-65B2C226B4BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D50CA868-BD58-4775-AFE3-8468B44BDCF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" firstSheet="7" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="الملخص السنوي" sheetId="1" r:id="rId1"/>
@@ -27,6 +27,7 @@
     <sheet name="أكتوبر" sheetId="12" r:id="rId12"/>
     <sheet name="نوفمبر" sheetId="13" r:id="rId13"/>
     <sheet name="ديسمبر" sheetId="14" r:id="rId14"/>
+    <sheet name="ورقة1" sheetId="15" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">أبريل!$1:$5</definedName>
@@ -61,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="120">
   <si>
     <t>الملخص السنوي الشامل — 2026</t>
   </si>
@@ -373,6 +374,60 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>خصومات</t>
+  </si>
+  <si>
+    <t xml:space="preserve">هيثم </t>
+  </si>
+  <si>
+    <t xml:space="preserve">حسام </t>
+  </si>
+  <si>
+    <t>عمار</t>
+  </si>
+  <si>
+    <t xml:space="preserve">التاريخ </t>
+  </si>
+  <si>
+    <t>المبلغ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ملاحظة </t>
+  </si>
+  <si>
+    <t>9 الشهر السابع</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 9 الشهر السابع</t>
+  </si>
+  <si>
+    <t>25 الف</t>
+  </si>
+  <si>
+    <t>سبب تأخير دوام</t>
+  </si>
+  <si>
+    <t>6 الشهر السابع</t>
+  </si>
+  <si>
+    <t>7 الشهر السابع</t>
+  </si>
+  <si>
+    <t>8 الشهر السابع</t>
+  </si>
+  <si>
+    <t xml:space="preserve">انس </t>
+  </si>
+  <si>
+    <t>13 الشهر السابع</t>
+  </si>
+  <si>
+    <t>45 الف</t>
+  </si>
+  <si>
+    <t>ثمن كوستيك</t>
   </si>
 </sst>
 </file>
@@ -1432,7 +1487,7 @@
       </c>
       <c r="J6" s="10">
         <f>IF(ISNUMBER(يوليو!AL8),يوليو!AL8,"")</f>
-        <v>3100000</v>
+        <v>2906451.62</v>
       </c>
       <c r="K6" s="10">
         <f>IF(ISNUMBER(أغسطس!AL8),أغسطس!AL8,"")</f>
@@ -1456,11 +1511,11 @@
       </c>
       <c r="P6" s="6">
         <f>IF(ISNUMBER(يناير!AK8),يناير!AK8,0)+IF(ISNUMBER(فبراير!AH8),فبراير!AH8,0)+IF(ISNUMBER(مارس!AK8),مارس!AK8,0)+IF(ISNUMBER(أبريل!AJ8),أبريل!AJ8,0)+IF(ISNUMBER(مايو!AK8),مايو!AK8,0)+IF(ISNUMBER(يونيو!AJ8),يونيو!AJ8,0)+IF(ISNUMBER(يوليو!AK8),يوليو!AK8,0)+IF(ISNUMBER(أغسطس!AK8),أغسطس!AK8,0)+IF(ISNUMBER(سبتمبر!AJ8),سبتمبر!AJ8,0)+IF(ISNUMBER(أكتوبر!AK8),أكتوبر!AK8,0)+IF(ISNUMBER(نوفمبر!AJ8),نوفمبر!AJ8,0)+IF(ISNUMBER(ديسمبر!AK8),ديسمبر!AK8,0)</f>
-        <v>200000</v>
+        <v>296774.19</v>
       </c>
       <c r="Q6" s="7">
         <f t="shared" si="0"/>
-        <v>36538888.890000001</v>
+        <v>36345340.510000005</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -1501,7 +1556,7 @@
       </c>
       <c r="J7" s="5">
         <f>IF(ISNUMBER(يوليو!AL9),يوليو!AL9,"")</f>
-        <v>2578853.04</v>
+        <v>2525089.6</v>
       </c>
       <c r="K7" s="5">
         <f>IF(ISNUMBER(أغسطس!AL9),أغسطس!AL9,"")</f>
@@ -1529,7 +1584,7 @@
       </c>
       <c r="Q7" s="7">
         <f t="shared" si="0"/>
-        <v>30379778.939999998</v>
+        <v>30326015.5</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -1570,7 +1625,7 @@
       </c>
       <c r="J8" s="10">
         <f>IF(ISNUMBER(يوليو!AL10),يوليو!AL10,"")</f>
-        <v>829534.05</v>
+        <v>752114.7</v>
       </c>
       <c r="K8" s="10">
         <f>IF(ISNUMBER(أغسطس!AL10),أغسطس!AL10,"")</f>
@@ -1594,11 +1649,11 @@
       </c>
       <c r="P8" s="6">
         <f>IF(ISNUMBER(يناير!AK10),يناير!AK10,0)+IF(ISNUMBER(فبراير!AH10),فبراير!AH10,0)+IF(ISNUMBER(مارس!AK10),مارس!AK10,0)+IF(ISNUMBER(أبريل!AJ10),أبريل!AJ10,0)+IF(ISNUMBER(مايو!AK10),مايو!AK10,0)+IF(ISNUMBER(يونيو!AJ10),يونيو!AJ10,0)+IF(ISNUMBER(يوليو!AK10),يوليو!AK10,0)+IF(ISNUMBER(أغسطس!AK10),أغسطس!AK10,0)+IF(ISNUMBER(سبتمبر!AJ10),سبتمبر!AJ10,0)+IF(ISNUMBER(أكتوبر!AK10),أكتوبر!AK10,0)+IF(ISNUMBER(نوفمبر!AJ10),نوفمبر!AJ10,0)+IF(ISNUMBER(ديسمبر!AK10),ديسمبر!AK10,0)</f>
-        <v>320000</v>
+        <v>397419.35</v>
       </c>
       <c r="Q8" s="7">
         <f t="shared" si="0"/>
-        <v>9462126.6599999983</v>
+        <v>9384707.3100000005</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -1639,7 +1694,7 @@
       </c>
       <c r="J9" s="5">
         <f>IF(ISNUMBER(يوليو!AL11),يوليو!AL11,"")</f>
-        <v>2052329.75</v>
+        <v>1923297.49</v>
       </c>
       <c r="K9" s="5">
         <f>IF(ISNUMBER(أغسطس!AL11),أغسطس!AL11,"")</f>
@@ -1663,11 +1718,11 @@
       </c>
       <c r="P9" s="6">
         <f>IF(ISNUMBER(يناير!AK11),يناير!AK11,0)+IF(ISNUMBER(فبراير!AH11),فبراير!AH11,0)+IF(ISNUMBER(مارس!AK11),مارس!AK11,0)+IF(ISNUMBER(أبريل!AJ11),أبريل!AJ11,0)+IF(ISNUMBER(مايو!AK11),مايو!AK11,0)+IF(ISNUMBER(يونيو!AJ11),يونيو!AJ11,0)+IF(ISNUMBER(يوليو!AK11),يوليو!AK11,0)+IF(ISNUMBER(أغسطس!AK11),أغسطس!AK11,0)+IF(ISNUMBER(سبتمبر!AJ11),سبتمبر!AJ11,0)+IF(ISNUMBER(أكتوبر!AK11),أكتوبر!AK11,0)+IF(ISNUMBER(نوفمبر!AJ11),نوفمبر!AJ11,0)+IF(ISNUMBER(ديسمبر!AK11),ديسمبر!AK11,0)</f>
-        <v>1466666.67</v>
+        <v>1531182.7999999998</v>
       </c>
       <c r="Q9" s="7">
         <f t="shared" si="0"/>
-        <v>22959737.170000002</v>
+        <v>22830704.910000004</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -2050,7 +2105,7 @@
       </c>
       <c r="J15" s="11">
         <f t="shared" si="1"/>
-        <v>15116630.82</v>
+        <v>14662867.390000001</v>
       </c>
       <c r="K15" s="11">
         <f t="shared" si="1"/>
@@ -2074,11 +2129,11 @@
       </c>
       <c r="P15" s="12">
         <f t="shared" si="1"/>
-        <v>3530752.69</v>
+        <v>3769462.36</v>
       </c>
       <c r="Q15" s="12">
         <f t="shared" si="1"/>
-        <v>183596445.62</v>
+        <v>183142682.19</v>
       </c>
     </row>
   </sheetData>
@@ -9668,6 +9723,215 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6D7BA86-F234-4A97-A072-67EE9B67B976}">
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="4" width="21.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>103</v>
+      </c>
+      <c r="B5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B6" t="s">
+        <v>114</v>
+      </c>
+      <c r="C6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D6" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>105</v>
+      </c>
+      <c r="B7" t="s">
+        <v>114</v>
+      </c>
+      <c r="C7" t="s">
+        <v>111</v>
+      </c>
+      <c r="D7" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>103</v>
+      </c>
+      <c r="B8" t="s">
+        <v>115</v>
+      </c>
+      <c r="C8" t="s">
+        <v>111</v>
+      </c>
+      <c r="D8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>104</v>
+      </c>
+      <c r="B9" t="s">
+        <v>115</v>
+      </c>
+      <c r="C9" t="s">
+        <v>111</v>
+      </c>
+      <c r="D9" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>105</v>
+      </c>
+      <c r="B10" t="s">
+        <v>115</v>
+      </c>
+      <c r="C10" t="s">
+        <v>111</v>
+      </c>
+      <c r="D10" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>103</v>
+      </c>
+      <c r="B11" t="s">
+        <v>109</v>
+      </c>
+      <c r="C11" t="s">
+        <v>111</v>
+      </c>
+      <c r="D11" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>104</v>
+      </c>
+      <c r="B12" t="s">
+        <v>110</v>
+      </c>
+      <c r="C12" t="s">
+        <v>111</v>
+      </c>
+      <c r="D12" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>105</v>
+      </c>
+      <c r="B13" t="s">
+        <v>109</v>
+      </c>
+      <c r="C13" t="s">
+        <v>111</v>
+      </c>
+      <c r="D13" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>116</v>
+      </c>
+      <c r="B14" t="s">
+        <v>117</v>
+      </c>
+      <c r="C14" t="s">
+        <v>118</v>
+      </c>
+      <c r="D14" t="s">
+        <v>119</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -19531,11 +19795,19 @@
       <c r="I8" s="40"/>
       <c r="J8" s="40"/>
       <c r="K8" s="34"/>
-      <c r="L8" s="40"/>
-      <c r="M8" s="40"/>
+      <c r="L8" s="40">
+        <v>-3</v>
+      </c>
+      <c r="M8" s="40">
+        <v>-3</v>
+      </c>
       <c r="N8" s="40"/>
-      <c r="O8" s="40"/>
-      <c r="P8" s="40"/>
+      <c r="O8" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="P8" s="40">
+        <v>-3</v>
+      </c>
       <c r="Q8" s="40"/>
       <c r="R8" s="34"/>
       <c r="S8" s="40"/>
@@ -19554,27 +19826,27 @@
       <c r="AF8" s="34"/>
       <c r="AG8" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH8" s="36">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AI8" s="37" t="str">
+        <v>-9</v>
+      </c>
+      <c r="AI8" s="37">
         <f>IF(OR('بيانات الموظفين'!C6="",NOT(ISNUMBER('بيانات الموظفين'!G2)),AH8=0),"-",ROUND(AH8*(('بيانات الموظفين'!C6/31)/'بيانات الموظفين'!G2),2))</f>
-        <v>-</v>
+        <v>-96774.19</v>
       </c>
       <c r="AJ8" s="38">
         <f>IF('بيانات الموظفين'!C6="","-",31-AG8)</f>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AK8" s="6">
         <f>IF('بيانات الموظفين'!C6="","-",ROUND(('بيانات الموظفين'!C6/31)*AG8,2))</f>
-        <v>0</v>
+        <v>96774.19</v>
       </c>
       <c r="AL8" s="39">
         <f>IF('بيانات الموظفين'!C6="","-",ROUND('بيانات الموظفين'!C6+ROUND('بيانات الموظفين'!C6/30,2)+IF(ISNUMBER(AI8),AI8,0)-IF(ISNUMBER(AK8),AK8,0),2))</f>
-        <v>3100000</v>
+        <v>2906451.62</v>
       </c>
     </row>
     <row r="9" spans="1:38" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -19596,8 +19868,12 @@
       <c r="I9" s="33"/>
       <c r="J9" s="33"/>
       <c r="K9" s="34"/>
-      <c r="L9" s="33"/>
-      <c r="M9" s="33"/>
+      <c r="L9" s="33">
+        <v>-3</v>
+      </c>
+      <c r="M9" s="33">
+        <v>-3</v>
+      </c>
       <c r="N9" s="33"/>
       <c r="O9" s="33"/>
       <c r="P9" s="33"/>
@@ -19623,11 +19899,11 @@
       </c>
       <c r="AH9" s="36">
         <f t="shared" si="1"/>
-        <v>-0.5</v>
+        <v>-6.5</v>
       </c>
       <c r="AI9" s="37">
         <f>IF(OR('بيانات الموظفين'!C7="",NOT(ISNUMBER('بيانات الموظفين'!G2)),AH9=0),"-",ROUND(AH9*(('بيانات الموظفين'!C7/31)/'بيانات الموظفين'!G2),2))</f>
-        <v>-4480.29</v>
+        <v>-58243.73</v>
       </c>
       <c r="AJ9" s="38">
         <f>IF('بيانات الموظفين'!C7="","-",31-AG9)</f>
@@ -19639,7 +19915,7 @@
       </c>
       <c r="AL9" s="39">
         <f>IF('بيانات الموظفين'!C7="","-",ROUND('بيانات الموظفين'!C7+ROUND('بيانات الموظفين'!C7/30,2)+IF(ISNUMBER(AI9),AI9,0)-IF(ISNUMBER(AK9),AK9,0),2))</f>
-        <v>2578853.04</v>
+        <v>2525089.6</v>
       </c>
     </row>
     <row r="10" spans="1:38" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -19659,9 +19935,15 @@
       <c r="I10" s="40"/>
       <c r="J10" s="40"/>
       <c r="K10" s="34"/>
-      <c r="L10" s="40"/>
-      <c r="M10" s="40"/>
-      <c r="N10" s="40"/>
+      <c r="L10" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="M10" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="N10" s="40" t="s">
+        <v>39</v>
+      </c>
       <c r="O10" s="40"/>
       <c r="P10" s="40"/>
       <c r="Q10" s="40"/>
@@ -19682,7 +19964,7 @@
       <c r="AF10" s="34"/>
       <c r="AG10" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH10" s="36">
         <f t="shared" si="1"/>
@@ -19694,15 +19976,15 @@
       </c>
       <c r="AJ10" s="38">
         <f>IF('بيانات الموظفين'!C8="","-",31-AG10)</f>
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="AK10" s="6">
         <f>IF('بيانات الموظفين'!C8="","-",ROUND(('بيانات الموظفين'!C8/31)*AG10,2))</f>
-        <v>0</v>
+        <v>77419.350000000006</v>
       </c>
       <c r="AL10" s="39">
         <f>IF('بيانات الموظفين'!C8="","-",ROUND('بيانات الموظفين'!C8+ROUND('بيانات الموظفين'!C8/30,2)+IF(ISNUMBER(AI10),AI10,0)-IF(ISNUMBER(AK10),AK10,0),2))</f>
-        <v>829534.05</v>
+        <v>752114.7</v>
       </c>
     </row>
     <row r="11" spans="1:38" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -19722,11 +20004,19 @@
       <c r="I11" s="33"/>
       <c r="J11" s="33"/>
       <c r="K11" s="34"/>
-      <c r="L11" s="33"/>
-      <c r="M11" s="33"/>
+      <c r="L11" s="33">
+        <v>-3</v>
+      </c>
+      <c r="M11" s="33">
+        <v>-3</v>
+      </c>
       <c r="N11" s="33"/>
-      <c r="O11" s="33"/>
-      <c r="P11" s="33"/>
+      <c r="O11" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="P11" s="33">
+        <v>-3</v>
+      </c>
       <c r="Q11" s="33"/>
       <c r="R11" s="34"/>
       <c r="S11" s="33"/>
@@ -19745,27 +20035,27 @@
       <c r="AF11" s="34"/>
       <c r="AG11" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH11" s="36">
         <f t="shared" si="1"/>
-        <v>-2</v>
+        <v>-11</v>
       </c>
       <c r="AI11" s="37">
         <f>IF(OR('بيانات الموظفين'!C9="",NOT(ISNUMBER('بيانات الموظفين'!G2)),AH11=0),"-",ROUND(AH11*(('بيانات الموظفين'!C9/31)/'بيانات الموظفين'!G2),2))</f>
-        <v>-14336.92</v>
+        <v>-78853.05</v>
       </c>
       <c r="AJ11" s="38">
         <f>IF('بيانات الموظفين'!C9="","-",31-AG11)</f>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AK11" s="6">
         <f>IF('بيانات الموظفين'!C9="","-",ROUND(('بيانات الموظفين'!C9/31)*AG11,2))</f>
-        <v>0</v>
+        <v>64516.13</v>
       </c>
       <c r="AL11" s="39">
         <f>IF('بيانات الموظفين'!C9="","-",ROUND('بيانات الموظفين'!C9+ROUND('بيانات الموظفين'!C9/30,2)+IF(ISNUMBER(AI11),AI11,0)-IF(ISNUMBER(AK11),AK11,0),2))</f>
-        <v>2052329.75</v>
+        <v>1923297.49</v>
       </c>
     </row>
     <row r="12" spans="1:38" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -20119,19 +20409,19 @@
       </c>
       <c r="L17" s="41">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" s="41">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N17" s="41">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O17" s="41">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P17" s="41">
         <f t="shared" si="2"/>
@@ -20203,24 +20493,24 @@
       </c>
       <c r="AG17" s="41">
         <f>SUM(AG7:AG16)</f>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AH17" s="42">
         <f>SUM(AH7:AH16)</f>
-        <v>-1.5</v>
+        <v>-25.5</v>
       </c>
       <c r="AI17" s="43">
         <f>SUM(AI7:AI16)</f>
-        <v>-15949.83</v>
+        <v>-231003.59000000003</v>
       </c>
       <c r="AJ17" s="44"/>
       <c r="AK17" s="43">
         <f>SUM(AK7:AK16)</f>
-        <v>677419.35</v>
+        <v>916129.02</v>
       </c>
       <c r="AL17" s="43">
         <f>SUM(AL7:AL16)</f>
-        <v>15116630.82</v>
+        <v>14662867.390000001</v>
       </c>
     </row>
     <row r="18" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -20339,23 +20629,23 @@
       </c>
       <c r="D22" s="45">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>96774.19</v>
       </c>
       <c r="F22" s="46">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="G22" s="37" t="str">
+        <v>-9</v>
+      </c>
+      <c r="G22" s="37">
         <f t="shared" si="6"/>
-        <v>-</v>
+        <v>-96774.19</v>
       </c>
       <c r="H22" s="39">
         <f t="shared" si="7"/>
-        <v>3100000</v>
+        <v>2906451.62</v>
       </c>
     </row>
     <row r="23" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20380,15 +20670,15 @@
       </c>
       <c r="F23" s="46">
         <f t="shared" si="5"/>
-        <v>-0.5</v>
+        <v>-6.5</v>
       </c>
       <c r="G23" s="37">
         <f t="shared" si="6"/>
-        <v>-4480.29</v>
+        <v>-58243.73</v>
       </c>
       <c r="H23" s="39">
         <f t="shared" si="7"/>
-        <v>2578853.04</v>
+        <v>2525089.6</v>
       </c>
     </row>
     <row r="24" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20405,11 +20695,11 @@
       </c>
       <c r="D24" s="45">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E24" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>77419.350000000006</v>
       </c>
       <c r="F24" s="46">
         <f t="shared" si="5"/>
@@ -20421,7 +20711,7 @@
       </c>
       <c r="H24" s="39">
         <f t="shared" si="7"/>
-        <v>829534.05</v>
+        <v>752114.7</v>
       </c>
     </row>
     <row r="25" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20438,23 +20728,23 @@
       </c>
       <c r="D25" s="45">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>64516.13</v>
       </c>
       <c r="F25" s="46">
         <f t="shared" si="5"/>
-        <v>-2</v>
+        <v>-11</v>
       </c>
       <c r="G25" s="37">
         <f t="shared" si="6"/>
-        <v>-14336.92</v>
+        <v>-78853.05</v>
       </c>
       <c r="H25" s="39">
         <f t="shared" si="7"/>
-        <v>2052329.75</v>
+        <v>1923297.49</v>
       </c>
     </row>
     <row r="26" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20633,23 +20923,23 @@
       </c>
       <c r="D31" s="47">
         <f t="shared" si="8"/>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E31" s="12">
         <f t="shared" si="8"/>
-        <v>677419.35</v>
+        <v>916129.02</v>
       </c>
       <c r="F31" s="47">
         <f t="shared" si="8"/>
-        <v>-1.5</v>
+        <v>-25.5</v>
       </c>
       <c r="G31" s="12">
         <f t="shared" si="8"/>
-        <v>-15949.83</v>
+        <v>-231003.59000000003</v>
       </c>
       <c r="H31" s="12">
         <f t="shared" si="8"/>
-        <v>15116630.82</v>
+        <v>14662867.390000001</v>
       </c>
     </row>
   </sheetData>

--- a/ضبط_رواتب_الموظفين.xlsx
+++ b/ضبط_رواتب_الموظفين.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DeLL\Desktop\ملفات خاصة بالمعمل ووظائفه\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D50CA868-BD58-4775-AFE3-8468B44BDCF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE8D3A1D-798C-495D-8735-414C3C0D6135}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" firstSheet="7" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="J6" s="10">
         <f>IF(ISNUMBER(يوليو!AL8),يوليو!AL8,"")</f>
-        <v>2906451.62</v>
+        <v>2922580.65</v>
       </c>
       <c r="K6" s="10">
         <f>IF(ISNUMBER(أغسطس!AL8),أغسطس!AL8,"")</f>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="Q6" s="7">
         <f t="shared" si="0"/>
-        <v>36345340.510000005</v>
+        <v>36361469.539999999</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="J7" s="5">
         <f>IF(ISNUMBER(يوليو!AL9),يوليو!AL9,"")</f>
-        <v>2525089.6</v>
+        <v>2538530.46</v>
       </c>
       <c r="K7" s="5">
         <f>IF(ISNUMBER(أغسطس!AL9),أغسطس!AL9,"")</f>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="Q7" s="7">
         <f t="shared" si="0"/>
-        <v>30326015.5</v>
+        <v>30339456.359999999</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="J8" s="10">
         <f>IF(ISNUMBER(يوليو!AL10),يوليو!AL10,"")</f>
-        <v>752114.7</v>
+        <v>746379.94</v>
       </c>
       <c r="K8" s="10">
         <f>IF(ISNUMBER(أغسطس!AL10),أغسطس!AL10,"")</f>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="Q8" s="7">
         <f t="shared" si="0"/>
-        <v>9384707.3100000005</v>
+        <v>9378972.5499999989</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="J9" s="5">
         <f>IF(ISNUMBER(يوليو!AL11),يوليو!AL11,"")</f>
-        <v>1923297.49</v>
+        <v>1934050.18</v>
       </c>
       <c r="K9" s="5">
         <f>IF(ISNUMBER(أغسطس!AL11),أغسطس!AL11,"")</f>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="Q9" s="7">
         <f t="shared" si="0"/>
-        <v>22830704.910000004</v>
+        <v>22841457.600000001</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="J15" s="11">
         <f t="shared" si="1"/>
-        <v>14662867.390000001</v>
+        <v>14697455.209999999</v>
       </c>
       <c r="K15" s="11">
         <f t="shared" si="1"/>
@@ -2133,7 +2133,7 @@
       </c>
       <c r="Q15" s="12">
         <f t="shared" si="1"/>
-        <v>183142682.19</v>
+        <v>183177270.01000002</v>
       </c>
     </row>
   </sheetData>
@@ -19808,7 +19808,9 @@
       <c r="P8" s="40">
         <v>-3</v>
       </c>
-      <c r="Q8" s="40"/>
+      <c r="Q8" s="40">
+        <v>1.5</v>
+      </c>
       <c r="R8" s="34"/>
       <c r="S8" s="40"/>
       <c r="T8" s="40"/>
@@ -19830,11 +19832,11 @@
       </c>
       <c r="AH8" s="36">
         <f t="shared" si="1"/>
-        <v>-9</v>
+        <v>-7.5</v>
       </c>
       <c r="AI8" s="37">
         <f>IF(OR('بيانات الموظفين'!C6="",NOT(ISNUMBER('بيانات الموظفين'!G2)),AH8=0),"-",ROUND(AH8*(('بيانات الموظفين'!C6/31)/'بيانات الموظفين'!G2),2))</f>
-        <v>-96774.19</v>
+        <v>-80645.16</v>
       </c>
       <c r="AJ8" s="38">
         <f>IF('بيانات الموظفين'!C6="","-",31-AG8)</f>
@@ -19846,7 +19848,7 @@
       </c>
       <c r="AL8" s="39">
         <f>IF('بيانات الموظفين'!C6="","-",ROUND('بيانات الموظفين'!C6+ROUND('بيانات الموظفين'!C6/30,2)+IF(ISNUMBER(AI8),AI8,0)-IF(ISNUMBER(AK8),AK8,0),2))</f>
-        <v>2906451.62</v>
+        <v>2922580.65</v>
       </c>
     </row>
     <row r="9" spans="1:38" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -19877,7 +19879,9 @@
       <c r="N9" s="33"/>
       <c r="O9" s="33"/>
       <c r="P9" s="33"/>
-      <c r="Q9" s="33"/>
+      <c r="Q9" s="33">
+        <v>1.5</v>
+      </c>
       <c r="R9" s="34"/>
       <c r="S9" s="33"/>
       <c r="T9" s="33"/>
@@ -19899,11 +19903,11 @@
       </c>
       <c r="AH9" s="36">
         <f t="shared" si="1"/>
-        <v>-6.5</v>
+        <v>-5</v>
       </c>
       <c r="AI9" s="37">
         <f>IF(OR('بيانات الموظفين'!C7="",NOT(ISNUMBER('بيانات الموظفين'!G2)),AH9=0),"-",ROUND(AH9*(('بيانات الموظفين'!C7/31)/'بيانات الموظفين'!G2),2))</f>
-        <v>-58243.73</v>
+        <v>-44802.87</v>
       </c>
       <c r="AJ9" s="38">
         <f>IF('بيانات الموظفين'!C7="","-",31-AG9)</f>
@@ -19915,7 +19919,7 @@
       </c>
       <c r="AL9" s="39">
         <f>IF('بيانات الموظفين'!C7="","-",ROUND('بيانات الموظفين'!C7+ROUND('بيانات الموظفين'!C7/30,2)+IF(ISNUMBER(AI9),AI9,0)-IF(ISNUMBER(AK9),AK9,0),2))</f>
-        <v>2525089.6</v>
+        <v>2538530.46</v>
       </c>
     </row>
     <row r="10" spans="1:38" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -19946,7 +19950,9 @@
       </c>
       <c r="O10" s="40"/>
       <c r="P10" s="40"/>
-      <c r="Q10" s="40"/>
+      <c r="Q10" s="40">
+        <v>-2</v>
+      </c>
       <c r="R10" s="34"/>
       <c r="S10" s="40"/>
       <c r="T10" s="40"/>
@@ -19968,11 +19974,11 @@
       </c>
       <c r="AH10" s="36">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AI10" s="37">
         <f>IF(OR('بيانات الموظفين'!C8="",NOT(ISNUMBER('بيانات الموظفين'!G2)),AH10=0),"-",ROUND(AH10*(('بيانات الموظفين'!C8/31)/'بيانات الموظفين'!G2),2))</f>
-        <v>2867.38</v>
+        <v>-2867.38</v>
       </c>
       <c r="AJ10" s="38">
         <f>IF('بيانات الموظفين'!C8="","-",31-AG10)</f>
@@ -19984,7 +19990,7 @@
       </c>
       <c r="AL10" s="39">
         <f>IF('بيانات الموظفين'!C8="","-",ROUND('بيانات الموظفين'!C8+ROUND('بيانات الموظفين'!C8/30,2)+IF(ISNUMBER(AI10),AI10,0)-IF(ISNUMBER(AK10),AK10,0),2))</f>
-        <v>752114.7</v>
+        <v>746379.94</v>
       </c>
     </row>
     <row r="11" spans="1:38" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -20017,7 +20023,9 @@
       <c r="P11" s="33">
         <v>-3</v>
       </c>
-      <c r="Q11" s="33"/>
+      <c r="Q11" s="33">
+        <v>1.5</v>
+      </c>
       <c r="R11" s="34"/>
       <c r="S11" s="33"/>
       <c r="T11" s="33"/>
@@ -20039,11 +20047,11 @@
       </c>
       <c r="AH11" s="36">
         <f t="shared" si="1"/>
-        <v>-11</v>
+        <v>-9.5</v>
       </c>
       <c r="AI11" s="37">
         <f>IF(OR('بيانات الموظفين'!C9="",NOT(ISNUMBER('بيانات الموظفين'!G2)),AH11=0),"-",ROUND(AH11*(('بيانات الموظفين'!C9/31)/'بيانات الموظفين'!G2),2))</f>
-        <v>-78853.05</v>
+        <v>-68100.36</v>
       </c>
       <c r="AJ11" s="38">
         <f>IF('بيانات الموظفين'!C9="","-",31-AG11)</f>
@@ -20055,7 +20063,7 @@
       </c>
       <c r="AL11" s="39">
         <f>IF('بيانات الموظفين'!C9="","-",ROUND('بيانات الموظفين'!C9+ROUND('بيانات الموظفين'!C9/30,2)+IF(ISNUMBER(AI11),AI11,0)-IF(ISNUMBER(AK11),AK11,0),2))</f>
-        <v>1923297.49</v>
+        <v>1934050.18</v>
       </c>
     </row>
     <row r="12" spans="1:38" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -20497,11 +20505,11 @@
       </c>
       <c r="AH17" s="42">
         <f>SUM(AH7:AH16)</f>
-        <v>-25.5</v>
+        <v>-23</v>
       </c>
       <c r="AI17" s="43">
         <f>SUM(AI7:AI16)</f>
-        <v>-231003.59000000003</v>
+        <v>-196415.77000000002</v>
       </c>
       <c r="AJ17" s="44"/>
       <c r="AK17" s="43">
@@ -20510,7 +20518,7 @@
       </c>
       <c r="AL17" s="43">
         <f>SUM(AL7:AL16)</f>
-        <v>14662867.390000001</v>
+        <v>14697455.209999999</v>
       </c>
     </row>
     <row r="18" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -20637,15 +20645,15 @@
       </c>
       <c r="F22" s="46">
         <f t="shared" si="5"/>
-        <v>-9</v>
+        <v>-7.5</v>
       </c>
       <c r="G22" s="37">
         <f t="shared" si="6"/>
-        <v>-96774.19</v>
+        <v>-80645.16</v>
       </c>
       <c r="H22" s="39">
         <f t="shared" si="7"/>
-        <v>2906451.62</v>
+        <v>2922580.65</v>
       </c>
     </row>
     <row r="23" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20670,15 +20678,15 @@
       </c>
       <c r="F23" s="46">
         <f t="shared" si="5"/>
-        <v>-6.5</v>
+        <v>-5</v>
       </c>
       <c r="G23" s="37">
         <f t="shared" si="6"/>
-        <v>-58243.73</v>
+        <v>-44802.87</v>
       </c>
       <c r="H23" s="39">
         <f t="shared" si="7"/>
-        <v>2525089.6</v>
+        <v>2538530.46</v>
       </c>
     </row>
     <row r="24" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20703,15 +20711,15 @@
       </c>
       <c r="F24" s="46">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G24" s="37">
         <f t="shared" si="6"/>
-        <v>2867.38</v>
+        <v>-2867.38</v>
       </c>
       <c r="H24" s="39">
         <f t="shared" si="7"/>
-        <v>752114.7</v>
+        <v>746379.94</v>
       </c>
     </row>
     <row r="25" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20736,15 +20744,15 @@
       </c>
       <c r="F25" s="46">
         <f t="shared" si="5"/>
-        <v>-11</v>
+        <v>-9.5</v>
       </c>
       <c r="G25" s="37">
         <f t="shared" si="6"/>
-        <v>-78853.05</v>
+        <v>-68100.36</v>
       </c>
       <c r="H25" s="39">
         <f t="shared" si="7"/>
-        <v>1923297.49</v>
+        <v>1934050.18</v>
       </c>
     </row>
     <row r="26" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20931,15 +20939,15 @@
       </c>
       <c r="F31" s="47">
         <f t="shared" si="8"/>
-        <v>-25.5</v>
+        <v>-23</v>
       </c>
       <c r="G31" s="12">
         <f t="shared" si="8"/>
-        <v>-231003.59000000003</v>
+        <v>-196415.77000000002</v>
       </c>
       <c r="H31" s="12">
         <f t="shared" si="8"/>
-        <v>14662867.390000001</v>
+        <v>14697455.209999999</v>
       </c>
     </row>
   </sheetData>

--- a/ضبط_رواتب_الموظفين.xlsx
+++ b/ضبط_رواتب_الموظفين.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DeLL\Desktop\ملفات خاصة بالمعمل ووظائفه\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE8D3A1D-798C-495D-8735-414C3C0D6135}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD2D5CBC-1E26-4E95-8FB2-FBFEAF5C357F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" firstSheet="7" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="120">
   <si>
     <t>الملخص السنوي الشامل — 2026</t>
   </si>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="J5" s="5">
         <f>IF(ISNUMBER(يوليو!AL7),يوليو!AL7,"")</f>
-        <v>6555913.9800000004</v>
+        <v>6104301.0700000003</v>
       </c>
       <c r="K5" s="5">
         <f>IF(ISNUMBER(أغسطس!AL7),أغسطس!AL7,"")</f>
@@ -1442,11 +1442,11 @@
       </c>
       <c r="P5" s="6">
         <f>IF(ISNUMBER(يناير!AK7),يناير!AK7,0)+IF(ISNUMBER(فبراير!AH7),فبراير!AH7,0)+IF(ISNUMBER(مارس!AK7),مارس!AK7,0)+IF(ISNUMBER(أبريل!AJ7),أبريل!AJ7,0)+IF(ISNUMBER(مايو!AK7),مايو!AK7,0)+IF(ISNUMBER(يونيو!AJ7),يونيو!AJ7,0)+IF(ISNUMBER(يوليو!AK7),يوليو!AK7,0)+IF(ISNUMBER(أغسطس!AK7),أغسطس!AK7,0)+IF(ISNUMBER(سبتمبر!AJ7),سبتمبر!AJ7,0)+IF(ISNUMBER(أكتوبر!AK7),أكتوبر!AK7,0)+IF(ISNUMBER(نوفمبر!AJ7),نوفمبر!AJ7,0)+IF(ISNUMBER(ديسمبر!AK7),ديسمبر!AK7,0)</f>
-        <v>1377419.35</v>
+        <v>1829032.26</v>
       </c>
       <c r="Q5" s="7">
         <f t="shared" ref="Q5:Q14" si="0">IFERROR(SUM(D5:O5),"")</f>
-        <v>84255913.959999993</v>
+        <v>83804301.049999997</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="J6" s="10">
         <f>IF(ISNUMBER(يوليو!AL8),يوليو!AL8,"")</f>
-        <v>2922580.65</v>
+        <v>2702150.54</v>
       </c>
       <c r="K6" s="10">
         <f>IF(ISNUMBER(أغسطس!AL8),أغسطس!AL8,"")</f>
@@ -1511,11 +1511,11 @@
       </c>
       <c r="P6" s="6">
         <f>IF(ISNUMBER(يناير!AK8),يناير!AK8,0)+IF(ISNUMBER(فبراير!AH8),فبراير!AH8,0)+IF(ISNUMBER(مارس!AK8),مارس!AK8,0)+IF(ISNUMBER(أبريل!AJ8),أبريل!AJ8,0)+IF(ISNUMBER(مايو!AK8),مايو!AK8,0)+IF(ISNUMBER(يونيو!AJ8),يونيو!AJ8,0)+IF(ISNUMBER(يوليو!AK8),يوليو!AK8,0)+IF(ISNUMBER(أغسطس!AK8),أغسطس!AK8,0)+IF(ISNUMBER(سبتمبر!AJ8),سبتمبر!AJ8,0)+IF(ISNUMBER(أكتوبر!AK8),أكتوبر!AK8,0)+IF(ISNUMBER(نوفمبر!AJ8),نوفمبر!AJ8,0)+IF(ISNUMBER(ديسمبر!AK8),ديسمبر!AK8,0)</f>
-        <v>296774.19</v>
+        <v>490322.58</v>
       </c>
       <c r="Q6" s="7">
         <f t="shared" si="0"/>
-        <v>36361469.539999999</v>
+        <v>36141039.43</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="J7" s="5">
         <f>IF(ISNUMBER(يوليو!AL9),يوليو!AL9,"")</f>
-        <v>2538530.46</v>
+        <v>2368279.5699999998</v>
       </c>
       <c r="K7" s="5">
         <f>IF(ISNUMBER(أغسطس!AL9),أغسطس!AL9,"")</f>
@@ -1580,11 +1580,11 @@
       </c>
       <c r="P7" s="6">
         <f>IF(ISNUMBER(يناير!AK9),يناير!AK9,0)+IF(ISNUMBER(فبراير!AH9),فبراير!AH9,0)+IF(ISNUMBER(مارس!AK9),مارس!AK9,0)+IF(ISNUMBER(أبريل!AJ9),أبريل!AJ9,0)+IF(ISNUMBER(مايو!AK9),مايو!AK9,0)+IF(ISNUMBER(يونيو!AJ9),يونيو!AJ9,0)+IF(ISNUMBER(يوليو!AK9),يوليو!AK9,0)+IF(ISNUMBER(أغسطس!AK9),أغسطس!AK9,0)+IF(ISNUMBER(سبتمبر!AJ9),سبتمبر!AJ9,0)+IF(ISNUMBER(أكتوبر!AK9),أكتوبر!AK9,0)+IF(ISNUMBER(نوفمبر!AJ9),نوفمبر!AJ9,0)+IF(ISNUMBER(ديسمبر!AK9),ديسمبر!AK9,0)</f>
-        <v>166666.67000000001</v>
+        <v>247311.83000000002</v>
       </c>
       <c r="Q7" s="7">
         <f t="shared" si="0"/>
-        <v>30339456.359999999</v>
+        <v>30169205.469999999</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="J8" s="10">
         <f>IF(ISNUMBER(يوليو!AL10),يوليو!AL10,"")</f>
-        <v>746379.94</v>
+        <v>666093.18999999994</v>
       </c>
       <c r="K8" s="10">
         <f>IF(ISNUMBER(أغسطس!AL10),أغسطس!AL10,"")</f>
@@ -1649,11 +1649,11 @@
       </c>
       <c r="P8" s="6">
         <f>IF(ISNUMBER(يناير!AK10),يناير!AK10,0)+IF(ISNUMBER(فبراير!AH10),فبراير!AH10,0)+IF(ISNUMBER(مارس!AK10),مارس!AK10,0)+IF(ISNUMBER(أبريل!AJ10),أبريل!AJ10,0)+IF(ISNUMBER(مايو!AK10),مايو!AK10,0)+IF(ISNUMBER(يونيو!AJ10),يونيو!AJ10,0)+IF(ISNUMBER(يوليو!AK10),يوليو!AK10,0)+IF(ISNUMBER(أغسطس!AK10),أغسطس!AK10,0)+IF(ISNUMBER(سبتمبر!AJ10),سبتمبر!AJ10,0)+IF(ISNUMBER(أكتوبر!AK10),أكتوبر!AK10,0)+IF(ISNUMBER(نوفمبر!AJ10),نوفمبر!AJ10,0)+IF(ISNUMBER(ديسمبر!AK10),ديسمبر!AK10,0)</f>
-        <v>397419.35</v>
+        <v>423225.81</v>
       </c>
       <c r="Q8" s="7">
         <f t="shared" si="0"/>
-        <v>9378972.5499999989</v>
+        <v>9298685.7999999989</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="J9" s="5">
         <f>IF(ISNUMBER(يوليو!AL11),يوليو!AL11,"")</f>
-        <v>1934050.18</v>
+        <v>1632974.91</v>
       </c>
       <c r="K9" s="5">
         <f>IF(ISNUMBER(أغسطس!AL11),أغسطس!AL11,"")</f>
@@ -1718,11 +1718,11 @@
       </c>
       <c r="P9" s="6">
         <f>IF(ISNUMBER(يناير!AK11),يناير!AK11,0)+IF(ISNUMBER(فبراير!AH11),فبراير!AH11,0)+IF(ISNUMBER(مارس!AK11),مارس!AK11,0)+IF(ISNUMBER(أبريل!AJ11),أبريل!AJ11,0)+IF(ISNUMBER(مايو!AK11),مايو!AK11,0)+IF(ISNUMBER(يونيو!AJ11),يونيو!AJ11,0)+IF(ISNUMBER(يوليو!AK11),يوليو!AK11,0)+IF(ISNUMBER(أغسطس!AK11),أغسطس!AK11,0)+IF(ISNUMBER(سبتمبر!AJ11),سبتمبر!AJ11,0)+IF(ISNUMBER(أكتوبر!AK11),أكتوبر!AK11,0)+IF(ISNUMBER(نوفمبر!AJ11),نوفمبر!AJ11,0)+IF(ISNUMBER(ديسمبر!AK11),ديسمبر!AK11,0)</f>
-        <v>1531182.7999999998</v>
+        <v>1789247.3199999998</v>
       </c>
       <c r="Q9" s="7">
         <f t="shared" si="0"/>
-        <v>22841457.600000001</v>
+        <v>22540382.329999998</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="J15" s="11">
         <f t="shared" si="1"/>
-        <v>14697455.209999999</v>
+        <v>13473799.279999999</v>
       </c>
       <c r="K15" s="11">
         <f t="shared" si="1"/>
@@ -2129,11 +2129,11 @@
       </c>
       <c r="P15" s="12">
         <f t="shared" si="1"/>
-        <v>3769462.36</v>
+        <v>4779139.8</v>
       </c>
       <c r="Q15" s="12">
         <f t="shared" si="1"/>
-        <v>183177270.01000002</v>
+        <v>181953614.07999998</v>
       </c>
     </row>
   </sheetData>
@@ -19397,7 +19397,14 @@
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
-    <col min="2" max="32" width="10" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="14.85546875" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="24" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="21" customWidth="1"/>
+    <col min="8" max="8" width="18.85546875" customWidth="1"/>
+    <col min="9" max="32" width="10" customWidth="1"/>
     <col min="33" max="38" width="15" customWidth="1"/>
   </cols>
   <sheetData>
@@ -19735,8 +19742,12 @@
       <c r="R7" s="34"/>
       <c r="S7" s="33"/>
       <c r="T7" s="33"/>
-      <c r="U7" s="33"/>
-      <c r="V7" s="33"/>
+      <c r="U7" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="V7" s="33" t="s">
+        <v>39</v>
+      </c>
       <c r="W7" s="33"/>
       <c r="X7" s="33"/>
       <c r="Y7" s="34"/>
@@ -19749,7 +19760,7 @@
       <c r="AF7" s="34"/>
       <c r="AG7" s="35">
         <f t="shared" ref="AG7:AG16" si="0">COUNTIF(B7:AF7,"غ")</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AH7" s="36">
         <f t="shared" ref="AH7:AH16" si="1">SUMIF(B7:AF7,"&gt;"&amp;0)+SUMIF(B7:AF7,"&lt;"&amp;0)</f>
@@ -19761,15 +19772,15 @@
       </c>
       <c r="AJ7" s="38">
         <f>IF('بيانات الموظفين'!C5="","-",31-AG7)</f>
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AK7" s="6">
         <f>IF('بيانات الموظفين'!C5="","-",ROUND(('بيانات الموظفين'!C5/31)*AG7,2))</f>
-        <v>677419.35</v>
+        <v>1129032.26</v>
       </c>
       <c r="AL7" s="39">
         <f>IF('بيانات الموظفين'!C5="","-",ROUND('بيانات الموظفين'!C5+ROUND('بيانات الموظفين'!C5/30,2)+IF(ISNUMBER(AI7),AI7,0)-IF(ISNUMBER(AK7),AK7,0),2))</f>
-        <v>6555913.9800000004</v>
+        <v>6104301.0700000003</v>
       </c>
     </row>
     <row r="8" spans="1:38" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -19796,7 +19807,7 @@
       <c r="J8" s="40"/>
       <c r="K8" s="34"/>
       <c r="L8" s="40">
-        <v>-3</v>
+        <v>-2.5</v>
       </c>
       <c r="M8" s="40">
         <v>-3</v>
@@ -19813,42 +19824,52 @@
       </c>
       <c r="R8" s="34"/>
       <c r="S8" s="40"/>
-      <c r="T8" s="40"/>
-      <c r="U8" s="40"/>
+      <c r="T8" s="40">
+        <v>1</v>
+      </c>
+      <c r="U8" s="40" t="s">
+        <v>39</v>
+      </c>
       <c r="V8" s="40"/>
       <c r="W8" s="40"/>
       <c r="X8" s="40"/>
       <c r="Y8" s="34"/>
-      <c r="Z8" s="40"/>
-      <c r="AA8" s="40"/>
+      <c r="Z8" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA8" s="40">
+        <v>-3</v>
+      </c>
       <c r="AB8" s="40"/>
-      <c r="AC8" s="40"/>
+      <c r="AC8" s="40">
+        <v>-1</v>
+      </c>
       <c r="AD8" s="40"/>
       <c r="AE8" s="40"/>
       <c r="AF8" s="34"/>
       <c r="AG8" s="35">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AH8" s="36">
         <f t="shared" si="1"/>
-        <v>-7.5</v>
+        <v>-10</v>
       </c>
       <c r="AI8" s="37">
         <f>IF(OR('بيانات الموظفين'!C6="",NOT(ISNUMBER('بيانات الموظفين'!G2)),AH8=0),"-",ROUND(AH8*(('بيانات الموظفين'!C6/31)/'بيانات الموظفين'!G2),2))</f>
-        <v>-80645.16</v>
+        <v>-107526.88</v>
       </c>
       <c r="AJ8" s="38">
         <f>IF('بيانات الموظفين'!C6="","-",31-AG8)</f>
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AK8" s="6">
         <f>IF('بيانات الموظفين'!C6="","-",ROUND(('بيانات الموظفين'!C6/31)*AG8,2))</f>
-        <v>96774.19</v>
+        <v>290322.58</v>
       </c>
       <c r="AL8" s="39">
         <f>IF('بيانات الموظفين'!C6="","-",ROUND('بيانات الموظفين'!C6+ROUND('بيانات الموظفين'!C6/30,2)+IF(ISNUMBER(AI8),AI8,0)-IF(ISNUMBER(AK8),AK8,0),2))</f>
-        <v>2922580.65</v>
+        <v>2702150.54</v>
       </c>
     </row>
     <row r="9" spans="1:38" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -19865,18 +19886,28 @@
       <c r="F9" s="33">
         <v>-1</v>
       </c>
-      <c r="G9" s="33"/>
-      <c r="H9" s="33"/>
-      <c r="I9" s="33"/>
-      <c r="J9" s="33"/>
+      <c r="G9" s="33">
+        <v>1</v>
+      </c>
+      <c r="H9" s="33">
+        <v>0.5</v>
+      </c>
+      <c r="I9" s="33">
+        <v>-1</v>
+      </c>
+      <c r="J9" s="33">
+        <v>-0.5</v>
+      </c>
       <c r="K9" s="34"/>
       <c r="L9" s="33">
-        <v>-3</v>
+        <v>-2.5</v>
       </c>
       <c r="M9" s="33">
         <v>-3</v>
       </c>
-      <c r="N9" s="33"/>
+      <c r="N9" s="33">
+        <v>-2</v>
+      </c>
       <c r="O9" s="33"/>
       <c r="P9" s="33"/>
       <c r="Q9" s="33">
@@ -19885,41 +19916,49 @@
       <c r="R9" s="34"/>
       <c r="S9" s="33"/>
       <c r="T9" s="33"/>
-      <c r="U9" s="33"/>
+      <c r="U9" s="33">
+        <v>-4.5</v>
+      </c>
       <c r="V9" s="33"/>
       <c r="W9" s="33"/>
       <c r="X9" s="33"/>
       <c r="Y9" s="34"/>
       <c r="Z9" s="33"/>
-      <c r="AA9" s="33"/>
-      <c r="AB9" s="33"/>
-      <c r="AC9" s="33"/>
+      <c r="AA9" s="33">
+        <v>-2</v>
+      </c>
+      <c r="AB9" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC9" s="33">
+        <v>-2</v>
+      </c>
       <c r="AD9" s="33"/>
       <c r="AE9" s="33"/>
       <c r="AF9" s="34"/>
       <c r="AG9" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH9" s="36">
         <f t="shared" si="1"/>
-        <v>-5</v>
+        <v>-15</v>
       </c>
       <c r="AI9" s="37">
         <f>IF(OR('بيانات الموظفين'!C7="",NOT(ISNUMBER('بيانات الموظفين'!G2)),AH9=0),"-",ROUND(AH9*(('بيانات الموظفين'!C7/31)/'بيانات الموظفين'!G2),2))</f>
-        <v>-44802.87</v>
+        <v>-134408.6</v>
       </c>
       <c r="AJ9" s="38">
         <f>IF('بيانات الموظفين'!C7="","-",31-AG9)</f>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AK9" s="6">
         <f>IF('بيانات الموظفين'!C7="","-",ROUND(('بيانات الموظفين'!C7/31)*AG9,2))</f>
-        <v>0</v>
+        <v>80645.16</v>
       </c>
       <c r="AL9" s="39">
         <f>IF('بيانات الموظفين'!C7="","-",ROUND('بيانات الموظفين'!C7+ROUND('بيانات الموظفين'!C7/30,2)+IF(ISNUMBER(AI9),AI9,0)-IF(ISNUMBER(AK9),AK9,0),2))</f>
-        <v>2538530.46</v>
+        <v>2368279.5699999998</v>
       </c>
     </row>
     <row r="10" spans="1:38" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -19955,42 +19994,54 @@
       </c>
       <c r="R10" s="34"/>
       <c r="S10" s="40"/>
-      <c r="T10" s="40"/>
-      <c r="U10" s="40"/>
+      <c r="T10" s="40">
+        <v>1</v>
+      </c>
+      <c r="U10" s="40">
+        <v>-4.5</v>
+      </c>
       <c r="V10" s="40"/>
       <c r="W10" s="40"/>
       <c r="X10" s="40"/>
       <c r="Y10" s="34"/>
-      <c r="Z10" s="40"/>
-      <c r="AA10" s="40"/>
-      <c r="AB10" s="40"/>
-      <c r="AC10" s="40"/>
+      <c r="Z10" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA10" s="40">
+        <v>-5</v>
+      </c>
+      <c r="AB10" s="40">
+        <v>-5.5</v>
+      </c>
+      <c r="AC10" s="40">
+        <v>-5</v>
+      </c>
       <c r="AD10" s="40"/>
       <c r="AE10" s="40"/>
       <c r="AF10" s="34"/>
       <c r="AG10" s="35">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH10" s="36">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-20</v>
       </c>
       <c r="AI10" s="37">
         <f>IF(OR('بيانات الموظفين'!C8="",NOT(ISNUMBER('بيانات الموظفين'!G2)),AH10=0),"-",ROUND(AH10*(('بيانات الموظفين'!C8/31)/'بيانات الموظفين'!G2),2))</f>
-        <v>-2867.38</v>
+        <v>-57347.67</v>
       </c>
       <c r="AJ10" s="38">
         <f>IF('بيانات الموظفين'!C8="","-",31-AG10)</f>
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK10" s="6">
         <f>IF('بيانات الموظفين'!C8="","-",ROUND(('بيانات الموظفين'!C8/31)*AG10,2))</f>
-        <v>77419.350000000006</v>
+        <v>103225.81</v>
       </c>
       <c r="AL10" s="39">
         <f>IF('بيانات الموظفين'!C8="","-",ROUND('بيانات الموظفين'!C8+ROUND('بيانات الموظفين'!C8/30,2)+IF(ISNUMBER(AI10),AI10,0)-IF(ISNUMBER(AK10),AK10,0),2))</f>
-        <v>746379.94</v>
+        <v>666093.18999999994</v>
       </c>
     </row>
     <row r="11" spans="1:38" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -20011,7 +20062,7 @@
       <c r="J11" s="33"/>
       <c r="K11" s="34"/>
       <c r="L11" s="33">
-        <v>-3</v>
+        <v>-2.5</v>
       </c>
       <c r="M11" s="33">
         <v>-3</v>
@@ -20029,41 +20080,53 @@
       <c r="R11" s="34"/>
       <c r="S11" s="33"/>
       <c r="T11" s="33"/>
-      <c r="U11" s="33"/>
+      <c r="U11" s="33">
+        <v>-4.5</v>
+      </c>
       <c r="V11" s="33"/>
       <c r="W11" s="33"/>
       <c r="X11" s="33"/>
       <c r="Y11" s="34"/>
       <c r="Z11" s="33"/>
-      <c r="AA11" s="33"/>
-      <c r="AB11" s="33"/>
-      <c r="AC11" s="33"/>
-      <c r="AD11" s="33"/>
-      <c r="AE11" s="33"/>
+      <c r="AA11" s="33">
+        <v>-2</v>
+      </c>
+      <c r="AB11" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC11" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD11" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE11" s="33" t="s">
+        <v>39</v>
+      </c>
       <c r="AF11" s="34"/>
       <c r="AG11" s="35">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AH11" s="36">
         <f t="shared" si="1"/>
-        <v>-9.5</v>
+        <v>-15.5</v>
       </c>
       <c r="AI11" s="37">
         <f>IF(OR('بيانات الموظفين'!C9="",NOT(ISNUMBER('بيانات الموظفين'!G2)),AH11=0),"-",ROUND(AH11*(('بيانات الموظفين'!C9/31)/'بيانات الموظفين'!G2),2))</f>
-        <v>-68100.36</v>
+        <v>-111111.11</v>
       </c>
       <c r="AJ11" s="38">
         <f>IF('بيانات الموظفين'!C9="","-",31-AG11)</f>
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AK11" s="6">
         <f>IF('بيانات الموظفين'!C9="","-",ROUND(('بيانات الموظفين'!C9/31)*AG11,2))</f>
-        <v>64516.13</v>
+        <v>322580.65000000002</v>
       </c>
       <c r="AL11" s="39">
         <f>IF('بيانات الموظفين'!C9="","-",ROUND('بيانات الموظفين'!C9+ROUND('بيانات الموظفين'!C9/30,2)+IF(ISNUMBER(AI11),AI11,0)-IF(ISNUMBER(AK11),AK11,0),2))</f>
-        <v>1934050.18</v>
+        <v>1632974.91</v>
       </c>
     </row>
     <row r="12" spans="1:38" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -20453,11 +20516,11 @@
       </c>
       <c r="U17" s="41">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V17" s="41">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W17" s="41">
         <f t="shared" si="2"/>
@@ -20473,7 +20536,7 @@
       </c>
       <c r="Z17" s="41">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA17" s="41">
         <f t="shared" si="2"/>
@@ -20481,19 +20544,19 @@
       </c>
       <c r="AB17" s="41">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC17" s="41">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD17" s="41">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE17" s="41">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF17" s="41">
         <f t="shared" si="2"/>
@@ -20501,24 +20564,24 @@
       </c>
       <c r="AG17" s="41">
         <f>SUM(AG7:AG16)</f>
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="AH17" s="42">
         <f>SUM(AH7:AH16)</f>
-        <v>-23</v>
+        <v>-60.5</v>
       </c>
       <c r="AI17" s="43">
         <f>SUM(AI7:AI16)</f>
-        <v>-196415.77000000002</v>
+        <v>-410394.26</v>
       </c>
       <c r="AJ17" s="44"/>
       <c r="AK17" s="43">
         <f>SUM(AK7:AK16)</f>
-        <v>916129.02</v>
+        <v>1925806.46</v>
       </c>
       <c r="AL17" s="43">
         <f>SUM(AL7:AL16)</f>
-        <v>14697455.209999999</v>
+        <v>13473799.279999999</v>
       </c>
     </row>
     <row r="18" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -20604,11 +20667,11 @@
       </c>
       <c r="D21" s="45">
         <f t="shared" ref="D21:D30" si="3">AG7</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E21" s="6">
         <f t="shared" ref="E21:E30" si="4">AK7</f>
-        <v>677419.35</v>
+        <v>1129032.26</v>
       </c>
       <c r="F21" s="46">
         <f t="shared" ref="F21:F30" si="5">AH7</f>
@@ -20620,7 +20683,7 @@
       </c>
       <c r="H21" s="39">
         <f t="shared" ref="H21:H30" si="7">AL7</f>
-        <v>6555913.9800000004</v>
+        <v>6104301.0700000003</v>
       </c>
     </row>
     <row r="22" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20637,23 +20700,23 @@
       </c>
       <c r="D22" s="45">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E22" s="6">
         <f t="shared" si="4"/>
-        <v>96774.19</v>
+        <v>290322.58</v>
       </c>
       <c r="F22" s="46">
         <f t="shared" si="5"/>
-        <v>-7.5</v>
+        <v>-10</v>
       </c>
       <c r="G22" s="37">
         <f t="shared" si="6"/>
-        <v>-80645.16</v>
+        <v>-107526.88</v>
       </c>
       <c r="H22" s="39">
         <f t="shared" si="7"/>
-        <v>2922580.65</v>
+        <v>2702150.54</v>
       </c>
     </row>
     <row r="23" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20670,23 +20733,23 @@
       </c>
       <c r="D23" s="45">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>80645.16</v>
       </c>
       <c r="F23" s="46">
         <f t="shared" si="5"/>
-        <v>-5</v>
+        <v>-15</v>
       </c>
       <c r="G23" s="37">
         <f t="shared" si="6"/>
-        <v>-44802.87</v>
+        <v>-134408.6</v>
       </c>
       <c r="H23" s="39">
         <f t="shared" si="7"/>
-        <v>2538530.46</v>
+        <v>2368279.5699999998</v>
       </c>
     </row>
     <row r="24" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20703,23 +20766,23 @@
       </c>
       <c r="D24" s="45">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E24" s="6">
         <f t="shared" si="4"/>
-        <v>77419.350000000006</v>
+        <v>103225.81</v>
       </c>
       <c r="F24" s="46">
         <f t="shared" si="5"/>
-        <v>-1</v>
+        <v>-20</v>
       </c>
       <c r="G24" s="37">
         <f t="shared" si="6"/>
-        <v>-2867.38</v>
+        <v>-57347.67</v>
       </c>
       <c r="H24" s="39">
         <f t="shared" si="7"/>
-        <v>746379.94</v>
+        <v>666093.18999999994</v>
       </c>
     </row>
     <row r="25" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20736,23 +20799,23 @@
       </c>
       <c r="D25" s="45">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E25" s="6">
         <f t="shared" si="4"/>
-        <v>64516.13</v>
+        <v>322580.65000000002</v>
       </c>
       <c r="F25" s="46">
         <f t="shared" si="5"/>
-        <v>-9.5</v>
+        <v>-15.5</v>
       </c>
       <c r="G25" s="37">
         <f t="shared" si="6"/>
-        <v>-68100.36</v>
+        <v>-111111.11</v>
       </c>
       <c r="H25" s="39">
         <f t="shared" si="7"/>
-        <v>1934050.18</v>
+        <v>1632974.91</v>
       </c>
     </row>
     <row r="26" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20931,23 +20994,23 @@
       </c>
       <c r="D31" s="47">
         <f t="shared" si="8"/>
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E31" s="12">
         <f t="shared" si="8"/>
-        <v>916129.02</v>
+        <v>1925806.46</v>
       </c>
       <c r="F31" s="47">
         <f t="shared" si="8"/>
-        <v>-23</v>
+        <v>-60.5</v>
       </c>
       <c r="G31" s="12">
         <f t="shared" si="8"/>
-        <v>-196415.77000000002</v>
+        <v>-410394.26</v>
       </c>
       <c r="H31" s="12">
         <f t="shared" si="8"/>
-        <v>14697455.209999999</v>
+        <v>13473799.279999999</v>
       </c>
     </row>
   </sheetData>

--- a/ضبط_رواتب_الموظفين.xlsx
+++ b/ضبط_رواتب_الموظفين.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DeLL\Desktop\ملفات خاصة بالمعمل ووظائفه\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD2D5CBC-1E26-4E95-8FB2-FBFEAF5C357F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{396BA878-C3E3-40B6-995A-282E69C54093}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" firstSheet="7" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" firstSheet="2" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="الملخص السنوي" sheetId="1" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="812" uniqueCount="120">
   <si>
     <t>الملخص السنوي الشامل — 2026</t>
   </si>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="K5" s="5">
         <f>IF(ISNUMBER(أغسطس!AL7),أغسطس!AL7,"")</f>
-        <v>7233333.3300000001</v>
+        <v>7007526.8799999999</v>
       </c>
       <c r="L5" s="5">
         <f>IF(ISNUMBER(سبتمبر!AK7),سبتمبر!AK7,"")</f>
@@ -1442,11 +1442,11 @@
       </c>
       <c r="P5" s="6">
         <f>IF(ISNUMBER(يناير!AK7),يناير!AK7,0)+IF(ISNUMBER(فبراير!AH7),فبراير!AH7,0)+IF(ISNUMBER(مارس!AK7),مارس!AK7,0)+IF(ISNUMBER(أبريل!AJ7),أبريل!AJ7,0)+IF(ISNUMBER(مايو!AK7),مايو!AK7,0)+IF(ISNUMBER(يونيو!AJ7),يونيو!AJ7,0)+IF(ISNUMBER(يوليو!AK7),يوليو!AK7,0)+IF(ISNUMBER(أغسطس!AK7),أغسطس!AK7,0)+IF(ISNUMBER(سبتمبر!AJ7),سبتمبر!AJ7,0)+IF(ISNUMBER(أكتوبر!AK7),أكتوبر!AK7,0)+IF(ISNUMBER(نوفمبر!AJ7),نوفمبر!AJ7,0)+IF(ISNUMBER(ديسمبر!AK7),ديسمبر!AK7,0)</f>
-        <v>1829032.26</v>
+        <v>2054838.71</v>
       </c>
       <c r="Q5" s="7">
         <f t="shared" ref="Q5:Q14" si="0">IFERROR(SUM(D5:O5),"")</f>
-        <v>83804301.049999997</v>
+        <v>83578494.600000009</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -1483,11 +1483,11 @@
       </c>
       <c r="I6" s="10">
         <f>IF(ISNUMBER(يونيو!AK8),يونيو!AK8,"")</f>
-        <v>2838888.89</v>
+        <v>2843750</v>
       </c>
       <c r="J6" s="10">
         <f>IF(ISNUMBER(يوليو!AL8),يوليو!AL8,"")</f>
-        <v>2702150.54</v>
+        <v>2688709.68</v>
       </c>
       <c r="K6" s="10">
         <f>IF(ISNUMBER(أغسطس!AL8),أغسطس!AL8,"")</f>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="Q6" s="7">
         <f t="shared" si="0"/>
-        <v>36141039.43</v>
+        <v>36132459.68</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -1552,15 +1552,15 @@
       </c>
       <c r="I7" s="5">
         <f>IF(ISNUMBER(يونيو!AK9),يونيو!AK9,"")</f>
-        <v>2300925.92</v>
+        <v>2296875</v>
       </c>
       <c r="J7" s="5">
         <f>IF(ISNUMBER(يوليو!AL9),يوليو!AL9,"")</f>
-        <v>2368279.5699999998</v>
+        <v>2351478.4900000002</v>
       </c>
       <c r="K7" s="5">
         <f>IF(ISNUMBER(أغسطس!AL9),أغسطس!AL9,"")</f>
-        <v>2583333.33</v>
+        <v>83333.33</v>
       </c>
       <c r="L7" s="5">
         <f>IF(ISNUMBER(سبتمبر!AK9),سبتمبر!AK9,"")</f>
@@ -1580,11 +1580,11 @@
       </c>
       <c r="P7" s="6">
         <f>IF(ISNUMBER(يناير!AK9),يناير!AK9,0)+IF(ISNUMBER(فبراير!AH9),فبراير!AH9,0)+IF(ISNUMBER(مارس!AK9),مارس!AK9,0)+IF(ISNUMBER(أبريل!AJ9),أبريل!AJ9,0)+IF(ISNUMBER(مايو!AK9),مايو!AK9,0)+IF(ISNUMBER(يونيو!AJ9),يونيو!AJ9,0)+IF(ISNUMBER(يوليو!AK9),يوليو!AK9,0)+IF(ISNUMBER(أغسطس!AK9),أغسطس!AK9,0)+IF(ISNUMBER(سبتمبر!AJ9),سبتمبر!AJ9,0)+IF(ISNUMBER(أكتوبر!AK9),أكتوبر!AK9,0)+IF(ISNUMBER(نوفمبر!AJ9),نوفمبر!AJ9,0)+IF(ISNUMBER(ديسمبر!AK9),ديسمبر!AK9,0)</f>
-        <v>247311.83000000002</v>
+        <v>2747311.83</v>
       </c>
       <c r="Q7" s="7">
         <f t="shared" si="0"/>
-        <v>30169205.469999999</v>
+        <v>27648353.469999999</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -1621,11 +1621,11 @@
       </c>
       <c r="I8" s="10">
         <f>IF(ISNUMBER(يونيو!AK10),يونيو!AK10,"")</f>
-        <v>472592.59</v>
+        <v>471666.67</v>
       </c>
       <c r="J8" s="10">
         <f>IF(ISNUMBER(يوليو!AL10),يوليو!AL10,"")</f>
-        <v>666093.18999999994</v>
+        <v>658924.73</v>
       </c>
       <c r="K8" s="10">
         <f>IF(ISNUMBER(أغسطس!AL10),أغسطس!AL10,"")</f>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="Q8" s="7">
         <f t="shared" si="0"/>
-        <v>9298685.7999999989</v>
+        <v>9290591.4199999999</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -1690,15 +1690,15 @@
       </c>
       <c r="I9" s="5">
         <f>IF(ISNUMBER(يونيو!AK11),يونيو!AK11,"")</f>
-        <v>507407.4</v>
+        <v>504166.66</v>
       </c>
       <c r="J9" s="5">
         <f>IF(ISNUMBER(يوليو!AL11),يوليو!AL11,"")</f>
-        <v>1632974.91</v>
+        <v>1619086.02</v>
       </c>
       <c r="K9" s="5">
         <f>IF(ISNUMBER(أغسطس!AL11),أغسطس!AL11,"")</f>
-        <v>2066666.67</v>
+        <v>1937634.41</v>
       </c>
       <c r="L9" s="5">
         <f>IF(ISNUMBER(سبتمبر!AK11),سبتمبر!AK11,"")</f>
@@ -1718,11 +1718,11 @@
       </c>
       <c r="P9" s="6">
         <f>IF(ISNUMBER(يناير!AK11),يناير!AK11,0)+IF(ISNUMBER(فبراير!AH11),فبراير!AH11,0)+IF(ISNUMBER(مارس!AK11),مارس!AK11,0)+IF(ISNUMBER(أبريل!AJ11),أبريل!AJ11,0)+IF(ISNUMBER(مايو!AK11),مايو!AK11,0)+IF(ISNUMBER(يونيو!AJ11),يونيو!AJ11,0)+IF(ISNUMBER(يوليو!AK11),يوليو!AK11,0)+IF(ISNUMBER(أغسطس!AK11),أغسطس!AK11,0)+IF(ISNUMBER(سبتمبر!AJ11),سبتمبر!AJ11,0)+IF(ISNUMBER(أكتوبر!AK11),أكتوبر!AK11,0)+IF(ISNUMBER(نوفمبر!AJ11),نوفمبر!AJ11,0)+IF(ISNUMBER(ديسمبر!AK11),ديسمبر!AK11,0)</f>
-        <v>1789247.3199999998</v>
+        <v>1918279.5799999998</v>
       </c>
       <c r="Q9" s="7">
         <f t="shared" si="0"/>
-        <v>22540382.329999998</v>
+        <v>22394220.439999998</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -2101,15 +2101,15 @@
       </c>
       <c r="I15" s="11">
         <f t="shared" si="1"/>
-        <v>12419814.800000001</v>
+        <v>12416458.33</v>
       </c>
       <c r="J15" s="11">
         <f t="shared" si="1"/>
-        <v>13473799.279999999</v>
+        <v>13422499.99</v>
       </c>
       <c r="K15" s="11">
         <f t="shared" si="1"/>
-        <v>15810000</v>
+        <v>12955161.289999999</v>
       </c>
       <c r="L15" s="11">
         <f t="shared" si="1"/>
@@ -2129,11 +2129,11 @@
       </c>
       <c r="P15" s="12">
         <f t="shared" si="1"/>
-        <v>4779139.8</v>
+        <v>7633978.5099999998</v>
       </c>
       <c r="Q15" s="12">
         <f t="shared" si="1"/>
-        <v>181953614.07999998</v>
+        <v>179044119.60999998</v>
       </c>
     </row>
   </sheetData>
@@ -2156,7 +2156,12 @@
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
-    <col min="2" max="32" width="10" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" customWidth="1"/>
+    <col min="3" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="22.140625" customWidth="1"/>
+    <col min="6" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="26.85546875" customWidth="1"/>
+    <col min="9" max="32" width="10" customWidth="1"/>
     <col min="33" max="38" width="15" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2470,7 +2475,9 @@
         <v xml:space="preserve">أبو بكر </v>
       </c>
       <c r="B7" s="33"/>
-      <c r="C7" s="33"/>
+      <c r="C7" s="33" t="s">
+        <v>39</v>
+      </c>
       <c r="D7" s="33"/>
       <c r="E7" s="33"/>
       <c r="F7" s="33"/>
@@ -2502,7 +2509,7 @@
       <c r="AF7" s="33"/>
       <c r="AG7" s="35">
         <f t="shared" ref="AG7:AG16" si="0">COUNTIF(B7:AF7,"غ")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH7" s="36">
         <f t="shared" ref="AH7:AH16" si="1">SUMIF(B7:AF7,"&gt;"&amp;0)+SUMIF(B7:AF7,"&lt;"&amp;0)</f>
@@ -2514,15 +2521,15 @@
       </c>
       <c r="AJ7" s="38">
         <f>IF('بيانات الموظفين'!C5="","-",31-AG7)</f>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AK7" s="6">
         <f>IF('بيانات الموظفين'!C5="","-",ROUND(('بيانات الموظفين'!C5/31)*AG7,2))</f>
-        <v>0</v>
+        <v>225806.45</v>
       </c>
       <c r="AL7" s="39">
         <f>IF('بيانات الموظفين'!C5="","-",ROUND('بيانات الموظفين'!C5+ROUND('بيانات الموظفين'!C5/30,2)+IF(ISNUMBER(AI7),AI7,0)-IF(ISNUMBER(AK7),AK7,0),2))</f>
-        <v>7233333.3300000001</v>
+        <v>7007526.8799999999</v>
       </c>
     </row>
     <row r="8" spans="1:38" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2591,40 +2598,102 @@
         <f>'بيانات الموظفين'!B7</f>
         <v>حسام كبريتة</v>
       </c>
-      <c r="B9" s="33"/>
-      <c r="C9" s="33"/>
-      <c r="D9" s="33"/>
-      <c r="E9" s="33"/>
-      <c r="F9" s="33"/>
-      <c r="G9" s="33"/>
-      <c r="H9" s="34"/>
-      <c r="I9" s="33"/>
-      <c r="J9" s="33"/>
-      <c r="K9" s="33"/>
-      <c r="L9" s="33"/>
-      <c r="M9" s="33"/>
-      <c r="N9" s="33"/>
-      <c r="O9" s="34"/>
-      <c r="P9" s="33"/>
-      <c r="Q9" s="33"/>
-      <c r="R9" s="33"/>
-      <c r="S9" s="33"/>
-      <c r="T9" s="33"/>
-      <c r="U9" s="33"/>
-      <c r="V9" s="34"/>
-      <c r="W9" s="33"/>
-      <c r="X9" s="33"/>
-      <c r="Y9" s="33"/>
-      <c r="Z9" s="33"/>
-      <c r="AA9" s="33"/>
-      <c r="AB9" s="33"/>
-      <c r="AC9" s="34"/>
-      <c r="AD9" s="33"/>
-      <c r="AE9" s="33"/>
-      <c r="AF9" s="33"/>
+      <c r="B9" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="H9" s="34" t="s">
+        <v>39</v>
+      </c>
+      <c r="I9" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="J9" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="K9" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="L9" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="M9" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="N9" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="O9" s="34" t="s">
+        <v>39</v>
+      </c>
+      <c r="P9" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q9" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="R9" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="S9" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="T9" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="U9" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="V9" s="34" t="s">
+        <v>39</v>
+      </c>
+      <c r="W9" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="X9" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y9" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z9" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA9" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB9" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC9" s="34" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD9" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE9" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF9" s="33" t="s">
+        <v>39</v>
+      </c>
       <c r="AG9" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AH9" s="36">
         <f t="shared" si="1"/>
@@ -2636,15 +2705,15 @@
       </c>
       <c r="AJ9" s="38">
         <f>IF('بيانات الموظفين'!C7="","-",31-AG9)</f>
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="AK9" s="6">
         <f>IF('بيانات الموظفين'!C7="","-",ROUND(('بيانات الموظفين'!C7/31)*AG9,2))</f>
-        <v>0</v>
+        <v>2500000</v>
       </c>
       <c r="AL9" s="39">
         <f>IF('بيانات الموظفين'!C7="","-",ROUND('بيانات الموظفين'!C7+ROUND('بيانات الموظفين'!C7/30,2)+IF(ISNUMBER(AI9),AI9,0)-IF(ISNUMBER(AK9),AK9,0),2))</f>
-        <v>2583333.33</v>
+        <v>83333.33</v>
       </c>
     </row>
     <row r="10" spans="1:38" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2713,8 +2782,12 @@
         <f>'بيانات الموظفين'!B9</f>
         <v>عمار مجيد</v>
       </c>
-      <c r="B11" s="33"/>
-      <c r="C11" s="33"/>
+      <c r="B11" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="33" t="s">
+        <v>39</v>
+      </c>
       <c r="D11" s="33"/>
       <c r="E11" s="33"/>
       <c r="F11" s="33"/>
@@ -2746,7 +2819,7 @@
       <c r="AF11" s="33"/>
       <c r="AG11" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH11" s="36">
         <f t="shared" si="1"/>
@@ -2758,15 +2831,15 @@
       </c>
       <c r="AJ11" s="38">
         <f>IF('بيانات الموظفين'!C9="","-",31-AG11)</f>
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="AK11" s="6">
         <f>IF('بيانات الموظفين'!C9="","-",ROUND(('بيانات الموظفين'!C9/31)*AG11,2))</f>
-        <v>0</v>
+        <v>129032.26</v>
       </c>
       <c r="AL11" s="39">
         <f>IF('بيانات الموظفين'!C9="","-",ROUND('بيانات الموظفين'!C9+ROUND('بيانات الموظفين'!C9/30,2)+IF(ISNUMBER(AI11),AI11,0)-IF(ISNUMBER(AK11),AK11,0),2))</f>
-        <v>2066666.67</v>
+        <v>1937634.41</v>
       </c>
     </row>
     <row r="12" spans="1:38" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3080,131 +3153,131 @@
       </c>
       <c r="B17" s="41">
         <f t="shared" ref="B17:AF17" si="2">COUNTIF(B7:B16,"غ")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C17" s="41">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D17" s="41">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" s="41">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" s="41">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" s="41">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" s="41">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" s="41">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" s="41">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" s="41">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" s="41">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" s="41">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N17" s="41">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O17" s="41">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P17" s="41">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q17" s="41">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" s="41">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" s="41">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T17" s="41">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U17" s="41">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="41">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W17" s="41">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X17" s="41">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y17" s="41">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z17" s="41">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA17" s="41">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB17" s="41">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC17" s="41">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD17" s="41">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE17" s="41">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF17" s="41">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG17" s="41">
         <f>SUM(AG7:AG16)</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AH17" s="42">
         <f>SUM(AH7:AH16)</f>
@@ -3217,11 +3290,11 @@
       <c r="AJ17" s="44"/>
       <c r="AK17" s="43">
         <f>SUM(AK7:AK16)</f>
-        <v>0</v>
+        <v>2854838.71</v>
       </c>
       <c r="AL17" s="43">
         <f>SUM(AL7:AL16)</f>
-        <v>15810000</v>
+        <v>12955161.289999999</v>
       </c>
     </row>
     <row r="18" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3307,11 +3380,11 @@
       </c>
       <c r="D21" s="45">
         <f t="shared" ref="D21:D30" si="3">AG7</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21" s="6">
         <f t="shared" ref="E21:E30" si="4">AK7</f>
-        <v>0</v>
+        <v>225806.45</v>
       </c>
       <c r="F21" s="46">
         <f t="shared" ref="F21:F30" si="5">AH7</f>
@@ -3323,7 +3396,7 @@
       </c>
       <c r="H21" s="39">
         <f t="shared" ref="H21:H30" si="7">AL7</f>
-        <v>7233333.3300000001</v>
+        <v>7007526.8799999999</v>
       </c>
     </row>
     <row r="22" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -3373,11 +3446,11 @@
       </c>
       <c r="D23" s="45">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="E23" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2500000</v>
       </c>
       <c r="F23" s="46">
         <f t="shared" si="5"/>
@@ -3389,7 +3462,7 @@
       </c>
       <c r="H23" s="39">
         <f t="shared" si="7"/>
-        <v>2583333.33</v>
+        <v>83333.33</v>
       </c>
     </row>
     <row r="24" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -3439,11 +3512,11 @@
       </c>
       <c r="D25" s="45">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E25" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>129032.26</v>
       </c>
       <c r="F25" s="46">
         <f t="shared" si="5"/>
@@ -3455,7 +3528,7 @@
       </c>
       <c r="H25" s="39">
         <f t="shared" si="7"/>
-        <v>2066666.67</v>
+        <v>1937634.41</v>
       </c>
     </row>
     <row r="26" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -3634,11 +3707,11 @@
       </c>
       <c r="D31" s="47">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="E31" s="12">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2854838.71</v>
       </c>
       <c r="F31" s="47">
         <f t="shared" si="8"/>
@@ -3650,7 +3723,7 @@
       </c>
       <c r="H31" s="12">
         <f t="shared" si="8"/>
-        <v>15810000</v>
+        <v>12955161.289999999</v>
       </c>
     </row>
   </sheetData>
@@ -9976,7 +10049,7 @@
       <c r="E2" s="63"/>
       <c r="F2" s="63"/>
       <c r="G2" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H2" s="15" t="s">
         <v>24</v>
@@ -18210,7 +18283,7 @@
       </c>
       <c r="AH8" s="37">
         <f>IF(OR('بيانات الموظفين'!C6="",NOT(ISNUMBER('بيانات الموظفين'!G2)),AG8=0),"-",ROUND(AG8*(('بيانات الموظفين'!C6/30)/'بيانات الموظفين'!G2),2))</f>
-        <v>38888.89</v>
+        <v>43750</v>
       </c>
       <c r="AI8" s="38">
         <f>IF('بيانات الموظفين'!C6="","-",30-AF8)</f>
@@ -18222,7 +18295,7 @@
       </c>
       <c r="AK8" s="39">
         <f>IF('بيانات الموظفين'!C6="","-",ROUND('بيانات الموظفين'!C6+IF(ISNUMBER(AH8),AH8,0)-IF(ISNUMBER(AJ8),AJ8,0),2))</f>
-        <v>2838888.89</v>
+        <v>2843750</v>
       </c>
     </row>
     <row r="9" spans="1:37" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -18284,7 +18357,7 @@
       </c>
       <c r="AH9" s="37">
         <f>IF(OR('بيانات الموظفين'!C7="",NOT(ISNUMBER('بيانات الموظفين'!G2)),AG9=0),"-",ROUND(AG9*(('بيانات الموظفين'!C7/30)/'بيانات الموظفين'!G2),2))</f>
-        <v>-32407.41</v>
+        <v>-36458.33</v>
       </c>
       <c r="AI9" s="38">
         <f>IF('بيانات الموظفين'!C7="","-",30-AF9)</f>
@@ -18296,7 +18369,7 @@
       </c>
       <c r="AK9" s="39">
         <f>IF('بيانات الموظفين'!C7="","-",ROUND('بيانات الموظفين'!C7+IF(ISNUMBER(AH9),AH9,0)-IF(ISNUMBER(AJ9),AJ9,0),2))</f>
-        <v>2300925.92</v>
+        <v>2296875</v>
       </c>
     </row>
     <row r="10" spans="1:37" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -18370,7 +18443,7 @@
       </c>
       <c r="AH10" s="37">
         <f>IF(OR('بيانات الموظفين'!C8="",NOT(ISNUMBER('بيانات الموظفين'!G2)),AG10=0),"-",ROUND(AG10*(('بيانات الموظفين'!C8/30)/'بيانات الموظفين'!G2),2))</f>
-        <v>-7407.41</v>
+        <v>-8333.33</v>
       </c>
       <c r="AI10" s="38">
         <f>IF('بيانات الموظفين'!C8="","-",30-AF10)</f>
@@ -18382,7 +18455,7 @@
       </c>
       <c r="AK10" s="39">
         <f>IF('بيانات الموظفين'!C8="","-",ROUND('بيانات الموظفين'!C8+IF(ISNUMBER(AH10),AH10,0)-IF(ISNUMBER(AJ10),AJ10,0),2))</f>
-        <v>472592.59</v>
+        <v>471666.67</v>
       </c>
     </row>
     <row r="11" spans="1:37" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -18480,7 +18553,7 @@
       </c>
       <c r="AH11" s="37">
         <f>IF(OR('بيانات الموظفين'!C9="",NOT(ISNUMBER('بيانات الموظفين'!G2)),AG11=0),"-",ROUND(AG11*(('بيانات الموظفين'!C9/30)/'بيانات الموظفين'!G2),2))</f>
-        <v>-25925.93</v>
+        <v>-29166.67</v>
       </c>
       <c r="AI11" s="38">
         <f>IF('بيانات الموظفين'!C9="","-",30-AF11)</f>
@@ -18492,7 +18565,7 @@
       </c>
       <c r="AK11" s="39">
         <f>IF('بيانات الموظفين'!C9="","-",ROUND('بيانات الموظفين'!C9+IF(ISNUMBER(AH11),AH11,0)-IF(ISNUMBER(AJ11),AJ11,0),2))</f>
-        <v>507407.4</v>
+        <v>504166.66</v>
       </c>
     </row>
     <row r="12" spans="1:37" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -18929,7 +19002,7 @@
       </c>
       <c r="AH17" s="43">
         <f>SUM(AH7:AH16)</f>
-        <v>-26851.86</v>
+        <v>-30208.33</v>
       </c>
       <c r="AI17" s="44"/>
       <c r="AJ17" s="43">
@@ -18938,7 +19011,7 @@
       </c>
       <c r="AK17" s="43">
         <f>SUM(AK7:AK16)</f>
-        <v>12419814.800000001</v>
+        <v>12416458.33</v>
       </c>
     </row>
     <row r="18" spans="1:37" ht="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -19068,11 +19141,11 @@
       </c>
       <c r="G22" s="37">
         <f t="shared" si="6"/>
-        <v>38888.89</v>
+        <v>43750</v>
       </c>
       <c r="H22" s="39">
         <f t="shared" si="7"/>
-        <v>2838888.89</v>
+        <v>2843750</v>
       </c>
     </row>
     <row r="23" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19101,11 +19174,11 @@
       </c>
       <c r="G23" s="37">
         <f t="shared" si="6"/>
-        <v>-32407.41</v>
+        <v>-36458.33</v>
       </c>
       <c r="H23" s="39">
         <f t="shared" si="7"/>
-        <v>2300925.92</v>
+        <v>2296875</v>
       </c>
     </row>
     <row r="24" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19134,11 +19207,11 @@
       </c>
       <c r="G24" s="37">
         <f t="shared" si="6"/>
-        <v>-7407.41</v>
+        <v>-8333.33</v>
       </c>
       <c r="H24" s="39">
         <f t="shared" si="7"/>
-        <v>472592.59</v>
+        <v>471666.67</v>
       </c>
     </row>
     <row r="25" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19167,11 +19240,11 @@
       </c>
       <c r="G25" s="37">
         <f t="shared" si="6"/>
-        <v>-25925.93</v>
+        <v>-29166.67</v>
       </c>
       <c r="H25" s="39">
         <f t="shared" si="7"/>
-        <v>507407.4</v>
+        <v>504166.66</v>
       </c>
     </row>
     <row r="26" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19362,11 +19435,11 @@
       </c>
       <c r="G31" s="12">
         <f t="shared" si="8"/>
-        <v>-26851.86</v>
+        <v>-30208.33</v>
       </c>
       <c r="H31" s="12">
         <f t="shared" si="8"/>
-        <v>12419814.800000001</v>
+        <v>12416458.33</v>
       </c>
     </row>
   </sheetData>
@@ -19857,7 +19930,7 @@
       </c>
       <c r="AI8" s="37">
         <f>IF(OR('بيانات الموظفين'!C6="",NOT(ISNUMBER('بيانات الموظفين'!G2)),AH8=0),"-",ROUND(AH8*(('بيانات الموظفين'!C6/31)/'بيانات الموظفين'!G2),2))</f>
-        <v>-107526.88</v>
+        <v>-120967.74</v>
       </c>
       <c r="AJ8" s="38">
         <f>IF('بيانات الموظفين'!C6="","-",31-AG8)</f>
@@ -19869,7 +19942,7 @@
       </c>
       <c r="AL8" s="39">
         <f>IF('بيانات الموظفين'!C6="","-",ROUND('بيانات الموظفين'!C6+ROUND('بيانات الموظفين'!C6/30,2)+IF(ISNUMBER(AI8),AI8,0)-IF(ISNUMBER(AK8),AK8,0),2))</f>
-        <v>2702150.54</v>
+        <v>2688709.68</v>
       </c>
     </row>
     <row r="9" spans="1:38" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -19946,7 +20019,7 @@
       </c>
       <c r="AI9" s="37">
         <f>IF(OR('بيانات الموظفين'!C7="",NOT(ISNUMBER('بيانات الموظفين'!G2)),AH9=0),"-",ROUND(AH9*(('بيانات الموظفين'!C7/31)/'بيانات الموظفين'!G2),2))</f>
-        <v>-134408.6</v>
+        <v>-151209.68</v>
       </c>
       <c r="AJ9" s="38">
         <f>IF('بيانات الموظفين'!C7="","-",31-AG9)</f>
@@ -19958,7 +20031,7 @@
       </c>
       <c r="AL9" s="39">
         <f>IF('بيانات الموظفين'!C7="","-",ROUND('بيانات الموظفين'!C7+ROUND('بيانات الموظفين'!C7/30,2)+IF(ISNUMBER(AI9),AI9,0)-IF(ISNUMBER(AK9),AK9,0),2))</f>
-        <v>2368279.5699999998</v>
+        <v>2351478.4900000002</v>
       </c>
     </row>
     <row r="10" spans="1:38" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -20029,7 +20102,7 @@
       </c>
       <c r="AI10" s="37">
         <f>IF(OR('بيانات الموظفين'!C8="",NOT(ISNUMBER('بيانات الموظفين'!G2)),AH10=0),"-",ROUND(AH10*(('بيانات الموظفين'!C8/31)/'بيانات الموظفين'!G2),2))</f>
-        <v>-57347.67</v>
+        <v>-64516.13</v>
       </c>
       <c r="AJ10" s="38">
         <f>IF('بيانات الموظفين'!C8="","-",31-AG10)</f>
@@ -20041,7 +20114,7 @@
       </c>
       <c r="AL10" s="39">
         <f>IF('بيانات الموظفين'!C8="","-",ROUND('بيانات الموظفين'!C8+ROUND('بيانات الموظفين'!C8/30,2)+IF(ISNUMBER(AI10),AI10,0)-IF(ISNUMBER(AK10),AK10,0),2))</f>
-        <v>666093.18999999994</v>
+        <v>658924.73</v>
       </c>
     </row>
     <row r="11" spans="1:38" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -20114,7 +20187,7 @@
       </c>
       <c r="AI11" s="37">
         <f>IF(OR('بيانات الموظفين'!C9="",NOT(ISNUMBER('بيانات الموظفين'!G2)),AH11=0),"-",ROUND(AH11*(('بيانات الموظفين'!C9/31)/'بيانات الموظفين'!G2),2))</f>
-        <v>-111111.11</v>
+        <v>-125000</v>
       </c>
       <c r="AJ11" s="38">
         <f>IF('بيانات الموظفين'!C9="","-",31-AG11)</f>
@@ -20126,7 +20199,7 @@
       </c>
       <c r="AL11" s="39">
         <f>IF('بيانات الموظفين'!C9="","-",ROUND('بيانات الموظفين'!C9+ROUND('بيانات الموظفين'!C9/30,2)+IF(ISNUMBER(AI11),AI11,0)-IF(ISNUMBER(AK11),AK11,0),2))</f>
-        <v>1632974.91</v>
+        <v>1619086.02</v>
       </c>
     </row>
     <row r="12" spans="1:38" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -20572,7 +20645,7 @@
       </c>
       <c r="AI17" s="43">
         <f>SUM(AI7:AI16)</f>
-        <v>-410394.26</v>
+        <v>-461693.55</v>
       </c>
       <c r="AJ17" s="44"/>
       <c r="AK17" s="43">
@@ -20581,7 +20654,7 @@
       </c>
       <c r="AL17" s="43">
         <f>SUM(AL7:AL16)</f>
-        <v>13473799.279999999</v>
+        <v>13422499.99</v>
       </c>
     </row>
     <row r="18" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -20712,11 +20785,11 @@
       </c>
       <c r="G22" s="37">
         <f t="shared" si="6"/>
-        <v>-107526.88</v>
+        <v>-120967.74</v>
       </c>
       <c r="H22" s="39">
         <f t="shared" si="7"/>
-        <v>2702150.54</v>
+        <v>2688709.68</v>
       </c>
     </row>
     <row r="23" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20745,11 +20818,11 @@
       </c>
       <c r="G23" s="37">
         <f t="shared" si="6"/>
-        <v>-134408.6</v>
+        <v>-151209.68</v>
       </c>
       <c r="H23" s="39">
         <f t="shared" si="7"/>
-        <v>2368279.5699999998</v>
+        <v>2351478.4900000002</v>
       </c>
     </row>
     <row r="24" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20778,11 +20851,11 @@
       </c>
       <c r="G24" s="37">
         <f t="shared" si="6"/>
-        <v>-57347.67</v>
+        <v>-64516.13</v>
       </c>
       <c r="H24" s="39">
         <f t="shared" si="7"/>
-        <v>666093.18999999994</v>
+        <v>658924.73</v>
       </c>
     </row>
     <row r="25" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20811,11 +20884,11 @@
       </c>
       <c r="G25" s="37">
         <f t="shared" si="6"/>
-        <v>-111111.11</v>
+        <v>-125000</v>
       </c>
       <c r="H25" s="39">
         <f t="shared" si="7"/>
-        <v>1632974.91</v>
+        <v>1619086.02</v>
       </c>
     </row>
     <row r="26" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21006,11 +21079,11 @@
       </c>
       <c r="G31" s="12">
         <f t="shared" si="8"/>
-        <v>-410394.26</v>
+        <v>-461693.55</v>
       </c>
       <c r="H31" s="12">
         <f t="shared" si="8"/>
-        <v>13473799.279999999</v>
+        <v>13422499.99</v>
       </c>
     </row>
   </sheetData>

--- a/ضبط_رواتب_الموظفين.xlsx
+++ b/ضبط_رواتب_الموظفين.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DeLL\Desktop\ملفات خاصة بالمعمل ووظائفه\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{396BA878-C3E3-40B6-995A-282E69C54093}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{735D413B-52A4-44F6-85BA-B8DFC8EF7221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" firstSheet="2" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="812" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="120">
   <si>
     <t>الملخص السنوي الشامل — 2026</t>
   </si>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="K5" s="5">
         <f>IF(ISNUMBER(أغسطس!AL7),أغسطس!AL7,"")</f>
-        <v>7007526.8799999999</v>
+        <v>6781720.4299999997</v>
       </c>
       <c r="L5" s="5">
         <f>IF(ISNUMBER(سبتمبر!AK7),سبتمبر!AK7,"")</f>
@@ -1442,11 +1442,11 @@
       </c>
       <c r="P5" s="6">
         <f>IF(ISNUMBER(يناير!AK7),يناير!AK7,0)+IF(ISNUMBER(فبراير!AH7),فبراير!AH7,0)+IF(ISNUMBER(مارس!AK7),مارس!AK7,0)+IF(ISNUMBER(أبريل!AJ7),أبريل!AJ7,0)+IF(ISNUMBER(مايو!AK7),مايو!AK7,0)+IF(ISNUMBER(يونيو!AJ7),يونيو!AJ7,0)+IF(ISNUMBER(يوليو!AK7),يوليو!AK7,0)+IF(ISNUMBER(أغسطس!AK7),أغسطس!AK7,0)+IF(ISNUMBER(سبتمبر!AJ7),سبتمبر!AJ7,0)+IF(ISNUMBER(أكتوبر!AK7),أكتوبر!AK7,0)+IF(ISNUMBER(نوفمبر!AJ7),نوفمبر!AJ7,0)+IF(ISNUMBER(ديسمبر!AK7),ديسمبر!AK7,0)</f>
-        <v>2054838.71</v>
+        <v>2280645.16</v>
       </c>
       <c r="Q5" s="7">
         <f t="shared" ref="Q5:Q14" si="0">IFERROR(SUM(D5:O5),"")</f>
-        <v>83578494.600000009</v>
+        <v>83352688.150000006</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="K15" s="11">
         <f t="shared" si="1"/>
-        <v>12955161.289999999</v>
+        <v>12729354.84</v>
       </c>
       <c r="L15" s="11">
         <f t="shared" si="1"/>
@@ -2129,11 +2129,11 @@
       </c>
       <c r="P15" s="12">
         <f t="shared" si="1"/>
-        <v>7633978.5099999998</v>
+        <v>7859784.96</v>
       </c>
       <c r="Q15" s="12">
         <f t="shared" si="1"/>
-        <v>179044119.60999998</v>
+        <v>178818313.16</v>
       </c>
     </row>
   </sheetData>
@@ -2484,7 +2484,9 @@
       <c r="G7" s="33"/>
       <c r="H7" s="34"/>
       <c r="I7" s="33"/>
-      <c r="J7" s="33"/>
+      <c r="J7" s="33" t="s">
+        <v>39</v>
+      </c>
       <c r="K7" s="33"/>
       <c r="L7" s="33"/>
       <c r="M7" s="33"/>
@@ -2509,7 +2511,7 @@
       <c r="AF7" s="33"/>
       <c r="AG7" s="35">
         <f t="shared" ref="AG7:AG16" si="0">COUNTIF(B7:AF7,"غ")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH7" s="36">
         <f t="shared" ref="AH7:AH16" si="1">SUMIF(B7:AF7,"&gt;"&amp;0)+SUMIF(B7:AF7,"&lt;"&amp;0)</f>
@@ -2521,15 +2523,15 @@
       </c>
       <c r="AJ7" s="38">
         <f>IF('بيانات الموظفين'!C5="","-",31-AG7)</f>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK7" s="6">
         <f>IF('بيانات الموظفين'!C5="","-",ROUND(('بيانات الموظفين'!C5/31)*AG7,2))</f>
-        <v>225806.45</v>
+        <v>451612.9</v>
       </c>
       <c r="AL7" s="39">
         <f>IF('بيانات الموظفين'!C5="","-",ROUND('بيانات الموظفين'!C5+ROUND('بيانات الموظفين'!C5/30,2)+IF(ISNUMBER(AI7),AI7,0)-IF(ISNUMBER(AK7),AK7,0),2))</f>
-        <v>7007526.8799999999</v>
+        <v>6781720.4299999997</v>
       </c>
     </row>
     <row r="8" spans="1:38" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3185,7 +3187,7 @@
       </c>
       <c r="J17" s="41">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K17" s="41">
         <f t="shared" si="2"/>
@@ -3277,7 +3279,7 @@
       </c>
       <c r="AG17" s="41">
         <f>SUM(AG7:AG16)</f>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AH17" s="42">
         <f>SUM(AH7:AH16)</f>
@@ -3290,11 +3292,11 @@
       <c r="AJ17" s="44"/>
       <c r="AK17" s="43">
         <f>SUM(AK7:AK16)</f>
-        <v>2854838.71</v>
+        <v>3080645.1599999997</v>
       </c>
       <c r="AL17" s="43">
         <f>SUM(AL7:AL16)</f>
-        <v>12955161.289999999</v>
+        <v>12729354.84</v>
       </c>
     </row>
     <row r="18" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3380,11 +3382,11 @@
       </c>
       <c r="D21" s="45">
         <f t="shared" ref="D21:D30" si="3">AG7</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21" s="6">
         <f t="shared" ref="E21:E30" si="4">AK7</f>
-        <v>225806.45</v>
+        <v>451612.9</v>
       </c>
       <c r="F21" s="46">
         <f t="shared" ref="F21:F30" si="5">AH7</f>
@@ -3396,7 +3398,7 @@
       </c>
       <c r="H21" s="39">
         <f t="shared" ref="H21:H30" si="7">AL7</f>
-        <v>7007526.8799999999</v>
+        <v>6781720.4299999997</v>
       </c>
     </row>
     <row r="22" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -3707,11 +3709,11 @@
       </c>
       <c r="D31" s="47">
         <f t="shared" si="8"/>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E31" s="12">
         <f t="shared" si="8"/>
-        <v>2854838.71</v>
+        <v>3080645.1599999997</v>
       </c>
       <c r="F31" s="47">
         <f t="shared" si="8"/>
@@ -3723,7 +3725,7 @@
       </c>
       <c r="H31" s="12">
         <f t="shared" si="8"/>
-        <v>12955161.289999999</v>
+        <v>12729354.84</v>
       </c>
     </row>
   </sheetData>

--- a/ضبط_رواتب_الموظفين.xlsx
+++ b/ضبط_رواتب_الموظفين.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DeLL\Desktop\ملفات خاصة بالمعمل ووظائفه\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{735D413B-52A4-44F6-85BA-B8DFC8EF7221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AFB6B45-DFFA-4895-9AEA-B3DE9404DF72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" firstSheet="2" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="821" uniqueCount="120">
   <si>
     <t>الملخص السنوي الشامل — 2026</t>
   </si>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="K5" s="5">
         <f>IF(ISNUMBER(أغسطس!AL7),أغسطس!AL7,"")</f>
-        <v>6781720.4299999997</v>
+        <v>4975268.8099999996</v>
       </c>
       <c r="L5" s="5">
         <f>IF(ISNUMBER(سبتمبر!AK7),سبتمبر!AK7,"")</f>
@@ -1442,11 +1442,11 @@
       </c>
       <c r="P5" s="6">
         <f>IF(ISNUMBER(يناير!AK7),يناير!AK7,0)+IF(ISNUMBER(فبراير!AH7),فبراير!AH7,0)+IF(ISNUMBER(مارس!AK7),مارس!AK7,0)+IF(ISNUMBER(أبريل!AJ7),أبريل!AJ7,0)+IF(ISNUMBER(مايو!AK7),مايو!AK7,0)+IF(ISNUMBER(يونيو!AJ7),يونيو!AJ7,0)+IF(ISNUMBER(يوليو!AK7),يوليو!AK7,0)+IF(ISNUMBER(أغسطس!AK7),أغسطس!AK7,0)+IF(ISNUMBER(سبتمبر!AJ7),سبتمبر!AJ7,0)+IF(ISNUMBER(أكتوبر!AK7),أكتوبر!AK7,0)+IF(ISNUMBER(نوفمبر!AJ7),نوفمبر!AJ7,0)+IF(ISNUMBER(ديسمبر!AK7),ديسمبر!AK7,0)</f>
-        <v>2280645.16</v>
+        <v>4087096.7800000003</v>
       </c>
       <c r="Q5" s="7">
         <f t="shared" ref="Q5:Q14" si="0">IFERROR(SUM(D5:O5),"")</f>
-        <v>83352688.150000006</v>
+        <v>81546236.530000001</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="K15" s="11">
         <f t="shared" si="1"/>
-        <v>12729354.84</v>
+        <v>10922903.220000001</v>
       </c>
       <c r="L15" s="11">
         <f t="shared" si="1"/>
@@ -2129,11 +2129,11 @@
       </c>
       <c r="P15" s="12">
         <f t="shared" si="1"/>
-        <v>7859784.96</v>
+        <v>9666236.5800000001</v>
       </c>
       <c r="Q15" s="12">
         <f t="shared" si="1"/>
-        <v>178818313.16</v>
+        <v>177011861.53999999</v>
       </c>
     </row>
   </sheetData>
@@ -2492,15 +2492,31 @@
       <c r="M7" s="33"/>
       <c r="N7" s="33"/>
       <c r="O7" s="34"/>
-      <c r="P7" s="33"/>
-      <c r="Q7" s="33"/>
-      <c r="R7" s="33"/>
-      <c r="S7" s="33"/>
-      <c r="T7" s="33"/>
-      <c r="U7" s="33"/>
+      <c r="P7" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q7" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="R7" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="S7" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="T7" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="U7" s="33" t="s">
+        <v>39</v>
+      </c>
       <c r="V7" s="34"/>
-      <c r="W7" s="33"/>
-      <c r="X7" s="33"/>
+      <c r="W7" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="X7" s="33" t="s">
+        <v>39</v>
+      </c>
       <c r="Y7" s="33"/>
       <c r="Z7" s="33"/>
       <c r="AA7" s="33"/>
@@ -2511,7 +2527,7 @@
       <c r="AF7" s="33"/>
       <c r="AG7" s="35">
         <f t="shared" ref="AG7:AG16" si="0">COUNTIF(B7:AF7,"غ")</f>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AH7" s="36">
         <f t="shared" ref="AH7:AH16" si="1">SUMIF(B7:AF7,"&gt;"&amp;0)+SUMIF(B7:AF7,"&lt;"&amp;0)</f>
@@ -2523,15 +2539,15 @@
       </c>
       <c r="AJ7" s="38">
         <f>IF('بيانات الموظفين'!C5="","-",31-AG7)</f>
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="AK7" s="6">
         <f>IF('بيانات الموظفين'!C5="","-",ROUND(('بيانات الموظفين'!C5/31)*AG7,2))</f>
-        <v>451612.9</v>
+        <v>2258064.52</v>
       </c>
       <c r="AL7" s="39">
         <f>IF('بيانات الموظفين'!C5="","-",ROUND('بيانات الموظفين'!C5+ROUND('بيانات الموظفين'!C5/30,2)+IF(ISNUMBER(AI7),AI7,0)-IF(ISNUMBER(AK7),AK7,0),2))</f>
-        <v>6781720.4299999997</v>
+        <v>4975268.8099999996</v>
       </c>
     </row>
     <row r="8" spans="1:38" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3211,39 +3227,39 @@
       </c>
       <c r="P17" s="41">
         <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="Q17" s="41">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="R17" s="41">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="S17" s="41">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="T17" s="41">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="U17" s="41">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="V17" s="41">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="Q17" s="41">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="R17" s="41">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="S17" s="41">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="T17" s="41">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="U17" s="41">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="V17" s="41">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
       <c r="W17" s="41">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X17" s="41">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y17" s="41">
         <f t="shared" si="2"/>
@@ -3279,7 +3295,7 @@
       </c>
       <c r="AG17" s="41">
         <f>SUM(AG7:AG16)</f>
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="AH17" s="42">
         <f>SUM(AH7:AH16)</f>
@@ -3292,11 +3308,11 @@
       <c r="AJ17" s="44"/>
       <c r="AK17" s="43">
         <f>SUM(AK7:AK16)</f>
-        <v>3080645.1599999997</v>
+        <v>4887096.7799999993</v>
       </c>
       <c r="AL17" s="43">
         <f>SUM(AL7:AL16)</f>
-        <v>12729354.84</v>
+        <v>10922903.220000001</v>
       </c>
     </row>
     <row r="18" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3382,11 +3398,11 @@
       </c>
       <c r="D21" s="45">
         <f t="shared" ref="D21:D30" si="3">AG7</f>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E21" s="6">
         <f t="shared" ref="E21:E30" si="4">AK7</f>
-        <v>451612.9</v>
+        <v>2258064.52</v>
       </c>
       <c r="F21" s="46">
         <f t="shared" ref="F21:F30" si="5">AH7</f>
@@ -3398,7 +3414,7 @@
       </c>
       <c r="H21" s="39">
         <f t="shared" ref="H21:H30" si="7">AL7</f>
-        <v>6781720.4299999997</v>
+        <v>4975268.8099999996</v>
       </c>
     </row>
     <row r="22" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -3709,11 +3725,11 @@
       </c>
       <c r="D31" s="47">
         <f t="shared" si="8"/>
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="E31" s="12">
         <f t="shared" si="8"/>
-        <v>3080645.1599999997</v>
+        <v>4887096.7799999993</v>
       </c>
       <c r="F31" s="47">
         <f t="shared" si="8"/>
@@ -3725,7 +3741,7 @@
       </c>
       <c r="H31" s="12">
         <f t="shared" si="8"/>
-        <v>12729354.84</v>
+        <v>10922903.220000001</v>
       </c>
     </row>
   </sheetData>

--- a/ضبط_رواتب_الموظفين.xlsx
+++ b/ضبط_رواتب_الموظفين.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DeLL\Desktop\ملفات خاصة بالمعمل ووظائفه\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AFB6B45-DFFA-4895-9AEA-B3DE9404DF72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0E9F075-D840-4165-83BD-5B2D9F38AE8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" firstSheet="2" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" firstSheet="3" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="الملخص السنوي" sheetId="1" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="821" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="120">
   <si>
     <t>الملخص السنوي الشامل — 2026</t>
   </si>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="L5" s="5">
         <f>IF(ISNUMBER(سبتمبر!AK7),سبتمبر!AK7,"")</f>
-        <v>7000000</v>
+        <v>6300000</v>
       </c>
       <c r="M5" s="5">
         <f>IF(ISNUMBER(أكتوبر!AL7),أكتوبر!AL7,"")</f>
@@ -1442,11 +1442,11 @@
       </c>
       <c r="P5" s="6">
         <f>IF(ISNUMBER(يناير!AK7),يناير!AK7,0)+IF(ISNUMBER(فبراير!AH7),فبراير!AH7,0)+IF(ISNUMBER(مارس!AK7),مارس!AK7,0)+IF(ISNUMBER(أبريل!AJ7),أبريل!AJ7,0)+IF(ISNUMBER(مايو!AK7),مايو!AK7,0)+IF(ISNUMBER(يونيو!AJ7),يونيو!AJ7,0)+IF(ISNUMBER(يوليو!AK7),يوليو!AK7,0)+IF(ISNUMBER(أغسطس!AK7),أغسطس!AK7,0)+IF(ISNUMBER(سبتمبر!AJ7),سبتمبر!AJ7,0)+IF(ISNUMBER(أكتوبر!AK7),أكتوبر!AK7,0)+IF(ISNUMBER(نوفمبر!AJ7),نوفمبر!AJ7,0)+IF(ISNUMBER(ديسمبر!AK7),ديسمبر!AK7,0)</f>
-        <v>4087096.7800000003</v>
+        <v>4787096.78</v>
       </c>
       <c r="Q5" s="7">
         <f t="shared" ref="Q5:Q14" si="0">IFERROR(SUM(D5:O5),"")</f>
-        <v>81546236.530000001</v>
+        <v>80846236.530000001</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="L15" s="11">
         <f t="shared" si="1"/>
-        <v>15300000</v>
+        <v>14600000</v>
       </c>
       <c r="M15" s="11">
         <f t="shared" si="1"/>
@@ -2129,11 +2129,11 @@
       </c>
       <c r="P15" s="12">
         <f t="shared" si="1"/>
-        <v>9666236.5800000001</v>
+        <v>10366236.58</v>
       </c>
       <c r="Q15" s="12">
         <f t="shared" si="1"/>
-        <v>177011861.53999999</v>
+        <v>176311861.53999999</v>
       </c>
     </row>
   </sheetData>
@@ -4083,12 +4083,18 @@
       <c r="E7" s="34"/>
       <c r="F7" s="33"/>
       <c r="G7" s="33"/>
-      <c r="H7" s="33"/>
+      <c r="H7" s="33" t="s">
+        <v>39</v>
+      </c>
       <c r="I7" s="33"/>
-      <c r="J7" s="33"/>
+      <c r="J7" s="33" t="s">
+        <v>39</v>
+      </c>
       <c r="K7" s="33"/>
       <c r="L7" s="34"/>
-      <c r="M7" s="33"/>
+      <c r="M7" s="33" t="s">
+        <v>39</v>
+      </c>
       <c r="N7" s="33"/>
       <c r="O7" s="33"/>
       <c r="P7" s="33"/>
@@ -4109,7 +4115,7 @@
       <c r="AE7" s="33"/>
       <c r="AF7" s="35">
         <f t="shared" ref="AF7:AF16" si="0">COUNTIF(B7:AE7,"غ")</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AG7" s="36">
         <f t="shared" ref="AG7:AG16" si="1">SUMIF(B7:AE7,"&gt;"&amp;0)+SUMIF(B7:AE7,"&lt;"&amp;0)</f>
@@ -4121,15 +4127,15 @@
       </c>
       <c r="AI7" s="38">
         <f>IF('بيانات الموظفين'!C5="","-",30-AF7)</f>
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AJ7" s="6">
         <f>IF('بيانات الموظفين'!C5="","-",ROUND(('بيانات الموظفين'!C5/30)*AF7,2))</f>
-        <v>0</v>
+        <v>700000</v>
       </c>
       <c r="AK7" s="39">
         <f>IF('بيانات الموظفين'!C5="","-",ROUND('بيانات الموظفين'!C5+IF(ISNUMBER(AH7),AH7,0)-IF(ISNUMBER(AJ7),AJ7,0),2))</f>
-        <v>7000000</v>
+        <v>6300000</v>
       </c>
     </row>
     <row r="8" spans="1:37" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4145,7 +4151,9 @@
       <c r="G8" s="40"/>
       <c r="H8" s="40"/>
       <c r="I8" s="40"/>
-      <c r="J8" s="40"/>
+      <c r="J8" s="40" t="s">
+        <v>101</v>
+      </c>
       <c r="K8" s="40"/>
       <c r="L8" s="34"/>
       <c r="M8" s="40"/>
@@ -4702,7 +4710,7 @@
       </c>
       <c r="H17" s="41">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" s="41">
         <f t="shared" si="2"/>
@@ -4710,7 +4718,7 @@
       </c>
       <c r="J17" s="41">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" s="41">
         <f t="shared" si="2"/>
@@ -4722,7 +4730,7 @@
       </c>
       <c r="M17" s="41">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N17" s="41">
         <f t="shared" si="2"/>
@@ -4798,7 +4806,7 @@
       </c>
       <c r="AF17" s="41">
         <f>SUM(AF7:AF16)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AG17" s="42">
         <f>SUM(AG7:AG16)</f>
@@ -4811,11 +4819,11 @@
       <c r="AI17" s="44"/>
       <c r="AJ17" s="43">
         <f>SUM(AJ7:AJ16)</f>
-        <v>0</v>
+        <v>700000</v>
       </c>
       <c r="AK17" s="43">
         <f>SUM(AK7:AK16)</f>
-        <v>15300000</v>
+        <v>14600000</v>
       </c>
     </row>
     <row r="18" spans="1:37" ht="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -4900,11 +4908,11 @@
       </c>
       <c r="D21" s="45">
         <f t="shared" ref="D21:D30" si="3">AF7</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E21" s="6">
         <f t="shared" ref="E21:E30" si="4">AJ7</f>
-        <v>0</v>
+        <v>700000</v>
       </c>
       <c r="F21" s="46">
         <f t="shared" ref="F21:F30" si="5">AG7</f>
@@ -4916,7 +4924,7 @@
       </c>
       <c r="H21" s="39">
         <f t="shared" ref="H21:H30" si="7">AK7</f>
-        <v>7000000</v>
+        <v>6300000</v>
       </c>
     </row>
     <row r="22" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -5227,11 +5235,11 @@
       </c>
       <c r="D31" s="47">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E31" s="12">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>700000</v>
       </c>
       <c r="F31" s="47">
         <f t="shared" si="8"/>
@@ -5243,7 +5251,7 @@
       </c>
       <c r="H31" s="12">
         <f t="shared" si="8"/>
-        <v>15300000</v>
+        <v>14600000</v>
       </c>
     </row>
   </sheetData>
